--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -8493,38 +8493,46 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127172331</v>
+        <v>127172142</v>
       </c>
       <c r="B61" t="n">
-        <v>97239</v>
+        <v>57657</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8532,10 +8540,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>363170</v>
+        <v>363196</v>
       </c>
       <c r="R61" t="n">
-        <v>6882973</v>
+        <v>6882950</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -8567,7 +8575,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8577,7 +8585,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8604,46 +8617,38 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127172142</v>
+        <v>127172331</v>
       </c>
       <c r="B62" t="n">
-        <v>57657</v>
+        <v>97314</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8651,10 +8656,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>363196</v>
+        <v>363170</v>
       </c>
       <c r="R62" t="n">
-        <v>6882950</v>
+        <v>6882973</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8686,7 +8691,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8696,12 +8701,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackmärken.</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8731,7 +8731,7 @@
         <v>127171152</v>
       </c>
       <c r="B63" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8842,10 +8842,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127172542</v>
+        <v>127171838</v>
       </c>
       <c r="B64" t="n">
-        <v>91263</v>
+        <v>79011</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8853,26 +8853,30 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8880,13 +8884,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>363093</v>
+        <v>363302</v>
       </c>
       <c r="R64" t="n">
-        <v>6882868</v>
+        <v>6882938</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8915,7 +8919,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8925,7 +8929,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8952,10 +8956,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127172219</v>
+        <v>127172542</v>
       </c>
       <c r="B65" t="n">
-        <v>78980</v>
+        <v>91337</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8963,21 +8967,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8990,10 +8994,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>363195</v>
+        <v>363093</v>
       </c>
       <c r="R65" t="n">
-        <v>6882944</v>
+        <v>6882868</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -9025,7 +9029,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9035,7 +9039,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9062,10 +9066,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127171838</v>
+        <v>127172219</v>
       </c>
       <c r="B66" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9092,11 +9096,7 @@
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -9104,13 +9104,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>363302</v>
+        <v>363195</v>
       </c>
       <c r="R66" t="n">
-        <v>6882938</v>
+        <v>6882944</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9176,10 +9176,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127170642</v>
+        <v>127170708</v>
       </c>
       <c r="B67" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9263,12 +9263,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Garnlavsdraperade granar.</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9298,7 +9293,7 @@
         <v>127172322</v>
       </c>
       <c r="B68" t="n">
-        <v>79059</v>
+        <v>79090</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9408,7 +9403,7 @@
         <v>127170420</v>
       </c>
       <c r="B69" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9523,7 +9518,7 @@
         <v>127170947</v>
       </c>
       <c r="B70" t="n">
-        <v>79059</v>
+        <v>79090</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9633,7 +9628,7 @@
         <v>127172203</v>
       </c>
       <c r="B71" t="n">
-        <v>97239</v>
+        <v>97314</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9744,7 +9739,7 @@
         <v>127171879</v>
       </c>
       <c r="B72" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9854,7 +9849,7 @@
         <v>127170500</v>
       </c>
       <c r="B73" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9966,38 +9961,46 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127171558</v>
+        <v>127170971</v>
       </c>
       <c r="B74" t="n">
-        <v>97239</v>
+        <v>57657</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -10005,10 +10008,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>363325</v>
+        <v>363315</v>
       </c>
       <c r="R74" t="n">
-        <v>6882909</v>
+        <v>6882898</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -10040,7 +10043,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10050,7 +10053,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10077,46 +10080,38 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127170971</v>
+        <v>127171558</v>
       </c>
       <c r="B75" t="n">
-        <v>57657</v>
+        <v>97314</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10124,10 +10119,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>363315</v>
+        <v>363325</v>
       </c>
       <c r="R75" t="n">
-        <v>6882898</v>
+        <v>6882909</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -10159,7 +10154,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10169,7 +10164,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10199,7 +10194,7 @@
         <v>127170911</v>
       </c>
       <c r="B76" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10314,7 +10309,7 @@
         <v>127172403</v>
       </c>
       <c r="B77" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY77"/>
+  <dimension ref="A1:AY79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8493,10 +8493,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127172142</v>
+        <v>127171152</v>
       </c>
       <c r="B61" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8504,33 +8504,28 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -8540,10 +8535,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>363196</v>
+        <v>363314</v>
       </c>
       <c r="R61" t="n">
-        <v>6882950</v>
+        <v>6882905</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -8575,7 +8570,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8585,12 +8580,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackmärken.</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8620,7 +8610,7 @@
         <v>127172331</v>
       </c>
       <c r="B62" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8728,10 +8718,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127171152</v>
+        <v>127172142</v>
       </c>
       <c r="B63" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8739,28 +8729,33 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -8770,10 +8765,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>363314</v>
+        <v>363196</v>
       </c>
       <c r="R63" t="n">
-        <v>6882905</v>
+        <v>6882950</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8805,7 +8800,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8815,7 +8810,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8842,10 +8842,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127171838</v>
+        <v>127172542</v>
       </c>
       <c r="B64" t="n">
-        <v>79011</v>
+        <v>91343</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8853,30 +8853,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8884,13 +8880,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>363302</v>
+        <v>363093</v>
       </c>
       <c r="R64" t="n">
-        <v>6882938</v>
+        <v>6882868</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8919,7 +8915,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8929,7 +8925,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8956,10 +8952,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127172542</v>
+        <v>127171838</v>
       </c>
       <c r="B65" t="n">
-        <v>91337</v>
+        <v>79014</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8967,26 +8963,30 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8994,13 +8994,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>363093</v>
+        <v>363302</v>
       </c>
       <c r="R65" t="n">
-        <v>6882868</v>
+        <v>6882938</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9069,7 +9069,7 @@
         <v>127172219</v>
       </c>
       <c r="B66" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>127170708</v>
       </c>
       <c r="B67" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>127172322</v>
       </c>
       <c r="B68" t="n">
-        <v>79090</v>
+        <v>79093</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>127170420</v>
       </c>
       <c r="B69" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>127170947</v>
       </c>
       <c r="B70" t="n">
-        <v>79090</v>
+        <v>79093</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>127172203</v>
       </c>
       <c r="B71" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>127171879</v>
       </c>
       <c r="B72" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>127170500</v>
       </c>
       <c r="B73" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>127171558</v>
       </c>
       <c r="B75" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>127170911</v>
       </c>
       <c r="B76" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>127172403</v>
       </c>
       <c r="B77" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10417,6 +10417,263 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>127315773</v>
+      </c>
+      <c r="B78" t="n">
+        <v>57761</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>363120</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6882934</v>
+      </c>
+      <c r="S78" t="n">
+        <v>25</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Marcus Hansson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Marcus Hansson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>127315676</v>
+      </c>
+      <c r="B79" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>363122</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6882946</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Marcus Hansson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Marcus Hansson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -8493,10 +8493,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127171152</v>
+        <v>127172142</v>
       </c>
       <c r="B61" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8504,28 +8504,33 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -8535,10 +8540,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>363314</v>
+        <v>363196</v>
       </c>
       <c r="R61" t="n">
-        <v>6882905</v>
+        <v>6882950</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -8570,7 +8575,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8580,7 +8585,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8718,10 +8728,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127172142</v>
+        <v>127171152</v>
       </c>
       <c r="B63" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8729,33 +8739,28 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -8765,10 +8770,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>363196</v>
+        <v>363314</v>
       </c>
       <c r="R63" t="n">
-        <v>6882950</v>
+        <v>6882905</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8800,7 +8805,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8810,12 +8815,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackmärken.</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8842,10 +8842,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127172542</v>
+        <v>127171838</v>
       </c>
       <c r="B64" t="n">
-        <v>91343</v>
+        <v>79014</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8853,26 +8853,30 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8880,13 +8884,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>363093</v>
+        <v>363302</v>
       </c>
       <c r="R64" t="n">
-        <v>6882868</v>
+        <v>6882938</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8915,7 +8919,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8925,7 +8929,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8952,10 +8956,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127171838</v>
+        <v>127172542</v>
       </c>
       <c r="B65" t="n">
-        <v>79014</v>
+        <v>91343</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8963,30 +8967,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8994,13 +8994,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>363302</v>
+        <v>363093</v>
       </c>
       <c r="R65" t="n">
-        <v>6882938</v>
+        <v>6882868</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9961,46 +9961,38 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127170971</v>
+        <v>127171558</v>
       </c>
       <c r="B74" t="n">
-        <v>57657</v>
+        <v>97320</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -10008,10 +10000,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>363315</v>
+        <v>363325</v>
       </c>
       <c r="R74" t="n">
-        <v>6882898</v>
+        <v>6882909</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -10043,7 +10035,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10053,7 +10045,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10080,38 +10072,46 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127171558</v>
+        <v>127170971</v>
       </c>
       <c r="B75" t="n">
-        <v>97320</v>
+        <v>57657</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10119,10 +10119,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>363325</v>
+        <v>363315</v>
       </c>
       <c r="R75" t="n">
-        <v>6882909</v>
+        <v>6882898</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -10154,7 +10154,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -8842,7 +8842,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127171838</v>
+        <v>127172219</v>
       </c>
       <c r="B64" t="n">
         <v>79014</v>
@@ -8872,11 +8872,7 @@
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8884,13 +8880,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>363302</v>
+        <v>363195</v>
       </c>
       <c r="R64" t="n">
-        <v>6882938</v>
+        <v>6882944</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8919,7 +8915,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8929,7 +8925,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8956,10 +8952,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127172542</v>
+        <v>127171838</v>
       </c>
       <c r="B65" t="n">
-        <v>91343</v>
+        <v>79014</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8967,26 +8963,30 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8994,13 +8994,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>363093</v>
+        <v>363302</v>
       </c>
       <c r="R65" t="n">
-        <v>6882868</v>
+        <v>6882938</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9066,10 +9066,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127172219</v>
+        <v>127172542</v>
       </c>
       <c r="B66" t="n">
-        <v>79014</v>
+        <v>91343</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9077,21 +9077,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9104,10 +9104,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>363195</v>
+        <v>363093</v>
       </c>
       <c r="R66" t="n">
-        <v>6882944</v>
+        <v>6882868</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -8617,38 +8617,41 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127172331</v>
+        <v>127171152</v>
       </c>
       <c r="B62" t="n">
-        <v>97320</v>
+        <v>79014</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8656,10 +8659,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>363170</v>
+        <v>363314</v>
       </c>
       <c r="R62" t="n">
-        <v>6882973</v>
+        <v>6882905</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8691,7 +8694,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8701,7 +8704,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8728,41 +8731,38 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127171152</v>
+        <v>127172331</v>
       </c>
       <c r="B63" t="n">
-        <v>79014</v>
+        <v>97321</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8770,10 +8770,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>363314</v>
+        <v>363170</v>
       </c>
       <c r="R63" t="n">
-        <v>6882905</v>
+        <v>6882973</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8842,10 +8842,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127172219</v>
+        <v>127172542</v>
       </c>
       <c r="B64" t="n">
-        <v>79014</v>
+        <v>91344</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8853,21 +8853,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8880,10 +8880,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>363195</v>
+        <v>363093</v>
       </c>
       <c r="R64" t="n">
-        <v>6882944</v>
+        <v>6882868</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -8915,7 +8915,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9066,10 +9066,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127172542</v>
+        <v>127172219</v>
       </c>
       <c r="B66" t="n">
-        <v>91343</v>
+        <v>79014</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9077,21 +9077,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9104,10 +9104,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>363093</v>
+        <v>363195</v>
       </c>
       <c r="R66" t="n">
-        <v>6882868</v>
+        <v>6882944</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9628,7 +9628,7 @@
         <v>127172203</v>
       </c>
       <c r="B71" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>127171558</v>
       </c>
       <c r="B74" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>127172403</v>
       </c>
       <c r="B77" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -8493,10 +8493,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127172142</v>
+        <v>127171152</v>
       </c>
       <c r="B61" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8504,33 +8504,28 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -8540,10 +8535,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>363196</v>
+        <v>363314</v>
       </c>
       <c r="R61" t="n">
-        <v>6882950</v>
+        <v>6882905</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -8575,7 +8570,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8585,12 +8580,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackmärken.</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8617,10 +8607,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127171152</v>
+        <v>127172142</v>
       </c>
       <c r="B62" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8628,28 +8618,33 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8659,10 +8654,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>363314</v>
+        <v>363196</v>
       </c>
       <c r="R62" t="n">
-        <v>6882905</v>
+        <v>6882950</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8694,7 +8689,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8704,7 +8699,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8842,10 +8842,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127172542</v>
+        <v>127171838</v>
       </c>
       <c r="B64" t="n">
-        <v>91344</v>
+        <v>79014</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8853,26 +8853,30 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8880,13 +8884,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>363093</v>
+        <v>363302</v>
       </c>
       <c r="R64" t="n">
-        <v>6882868</v>
+        <v>6882938</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8915,7 +8919,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8925,7 +8929,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8952,7 +8956,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127171838</v>
+        <v>127172219</v>
       </c>
       <c r="B65" t="n">
         <v>79014</v>
@@ -8982,11 +8986,7 @@
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8994,13 +8994,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>363302</v>
+        <v>363195</v>
       </c>
       <c r="R65" t="n">
-        <v>6882938</v>
+        <v>6882944</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9066,10 +9066,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127172219</v>
+        <v>127172542</v>
       </c>
       <c r="B66" t="n">
-        <v>79014</v>
+        <v>91344</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9077,21 +9077,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9104,10 +9104,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>363195</v>
+        <v>363093</v>
       </c>
       <c r="R66" t="n">
-        <v>6882944</v>
+        <v>6882868</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9961,38 +9961,46 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127171558</v>
+        <v>127170971</v>
       </c>
       <c r="B74" t="n">
-        <v>97321</v>
+        <v>57657</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -10000,10 +10008,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>363325</v>
+        <v>363315</v>
       </c>
       <c r="R74" t="n">
-        <v>6882909</v>
+        <v>6882898</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -10035,7 +10043,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10045,7 +10053,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10072,46 +10080,38 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127170971</v>
+        <v>127171558</v>
       </c>
       <c r="B75" t="n">
-        <v>57657</v>
+        <v>97321</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10119,10 +10119,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>363315</v>
+        <v>363325</v>
       </c>
       <c r="R75" t="n">
-        <v>6882898</v>
+        <v>6882909</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -10154,7 +10154,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -8493,10 +8493,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127171152</v>
+        <v>127172142</v>
       </c>
       <c r="B61" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8504,28 +8504,33 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -8535,10 +8540,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>363314</v>
+        <v>363196</v>
       </c>
       <c r="R61" t="n">
-        <v>6882905</v>
+        <v>6882950</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -8570,7 +8575,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8580,7 +8585,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8607,10 +8617,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127172142</v>
+        <v>127171152</v>
       </c>
       <c r="B62" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8618,33 +8628,28 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8654,10 +8659,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>363196</v>
+        <v>363314</v>
       </c>
       <c r="R62" t="n">
-        <v>6882950</v>
+        <v>6882905</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8689,7 +8694,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8699,12 +8704,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackmärken.</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8956,10 +8956,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127172219</v>
+        <v>127172542</v>
       </c>
       <c r="B65" t="n">
-        <v>79014</v>
+        <v>91344</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8967,21 +8967,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8994,10 +8994,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>363195</v>
+        <v>363093</v>
       </c>
       <c r="R65" t="n">
-        <v>6882944</v>
+        <v>6882868</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9066,10 +9066,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127172542</v>
+        <v>127172219</v>
       </c>
       <c r="B66" t="n">
-        <v>91344</v>
+        <v>79014</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9077,21 +9077,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9104,10 +9104,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>363093</v>
+        <v>363195</v>
       </c>
       <c r="R66" t="n">
-        <v>6882868</v>
+        <v>6882944</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -8493,10 +8493,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127172142</v>
+        <v>127171152</v>
       </c>
       <c r="B61" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8504,33 +8504,28 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -8540,10 +8535,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>363196</v>
+        <v>363314</v>
       </c>
       <c r="R61" t="n">
-        <v>6882950</v>
+        <v>6882905</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -8575,7 +8570,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8585,12 +8580,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackmärken.</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8617,10 +8607,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127171152</v>
+        <v>127172142</v>
       </c>
       <c r="B62" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8628,28 +8618,33 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8659,10 +8654,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>363314</v>
+        <v>363196</v>
       </c>
       <c r="R62" t="n">
-        <v>6882905</v>
+        <v>6882950</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8694,7 +8689,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8704,7 +8699,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken.</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -8493,41 +8493,38 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127171152</v>
+        <v>127172331</v>
       </c>
       <c r="B61" t="n">
-        <v>79014</v>
+        <v>97325</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8535,10 +8532,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>363314</v>
+        <v>363170</v>
       </c>
       <c r="R61" t="n">
-        <v>6882905</v>
+        <v>6882973</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -8570,7 +8567,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8580,7 +8577,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8607,10 +8604,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127172142</v>
+        <v>127171152</v>
       </c>
       <c r="B62" t="n">
-        <v>57657</v>
+        <v>79018</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8618,33 +8615,28 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8654,10 +8646,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>363196</v>
+        <v>363314</v>
       </c>
       <c r="R62" t="n">
-        <v>6882950</v>
+        <v>6882905</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8689,7 +8681,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8699,12 +8691,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackmärken.</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8731,38 +8718,46 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127172331</v>
+        <v>127172142</v>
       </c>
       <c r="B63" t="n">
-        <v>97321</v>
+        <v>57661</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8770,10 +8765,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>363170</v>
+        <v>363196</v>
       </c>
       <c r="R63" t="n">
-        <v>6882973</v>
+        <v>6882950</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8805,7 +8800,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8815,7 +8810,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8842,10 +8842,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127171838</v>
+        <v>127172542</v>
       </c>
       <c r="B64" t="n">
-        <v>79014</v>
+        <v>91348</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8853,30 +8853,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8884,13 +8880,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>363302</v>
+        <v>363093</v>
       </c>
       <c r="R64" t="n">
-        <v>6882938</v>
+        <v>6882868</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8919,7 +8915,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8929,7 +8925,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8956,10 +8952,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127172542</v>
+        <v>127172219</v>
       </c>
       <c r="B65" t="n">
-        <v>91344</v>
+        <v>79018</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8967,21 +8963,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8994,10 +8990,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>363093</v>
+        <v>363195</v>
       </c>
       <c r="R65" t="n">
-        <v>6882868</v>
+        <v>6882944</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -9029,7 +9025,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9039,7 +9035,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9066,10 +9062,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127172219</v>
+        <v>127171838</v>
       </c>
       <c r="B66" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9096,7 +9092,11 @@
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -9104,13 +9104,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>363195</v>
+        <v>363302</v>
       </c>
       <c r="R66" t="n">
-        <v>6882944</v>
+        <v>6882938</v>
       </c>
       <c r="S66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9179,7 +9179,7 @@
         <v>127170708</v>
       </c>
       <c r="B67" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>127172322</v>
       </c>
       <c r="B68" t="n">
-        <v>79093</v>
+        <v>79097</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>127170420</v>
       </c>
       <c r="B69" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>127170947</v>
       </c>
       <c r="B70" t="n">
-        <v>79093</v>
+        <v>79097</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>127172203</v>
       </c>
       <c r="B71" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>127171879</v>
       </c>
       <c r="B72" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>127170500</v>
       </c>
       <c r="B73" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>127170971</v>
       </c>
       <c r="B74" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>127171558</v>
       </c>
       <c r="B75" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>127170911</v>
       </c>
       <c r="B76" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>127172403</v>
       </c>
       <c r="B77" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>127315773</v>
       </c>
       <c r="B78" t="n">
-        <v>57761</v>
+        <v>57765</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>127315676</v>
       </c>
       <c r="B79" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -8493,38 +8493,46 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127172331</v>
+        <v>127172142</v>
       </c>
       <c r="B61" t="n">
-        <v>97325</v>
+        <v>57661</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8532,10 +8540,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>363170</v>
+        <v>363196</v>
       </c>
       <c r="R61" t="n">
-        <v>6882973</v>
+        <v>6882950</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -8567,7 +8575,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8577,7 +8585,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8604,41 +8617,38 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127171152</v>
+        <v>127172331</v>
       </c>
       <c r="B62" t="n">
-        <v>79018</v>
+        <v>97325</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8646,10 +8656,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>363314</v>
+        <v>363170</v>
       </c>
       <c r="R62" t="n">
-        <v>6882905</v>
+        <v>6882973</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8681,7 +8691,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8691,7 +8701,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8718,10 +8728,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127172142</v>
+        <v>127171152</v>
       </c>
       <c r="B63" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8729,33 +8739,28 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -8765,10 +8770,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>363196</v>
+        <v>363314</v>
       </c>
       <c r="R63" t="n">
-        <v>6882950</v>
+        <v>6882905</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8800,7 +8805,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8810,12 +8815,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackmärken.</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8842,10 +8842,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127172542</v>
+        <v>127171838</v>
       </c>
       <c r="B64" t="n">
-        <v>91348</v>
+        <v>79018</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8853,26 +8853,30 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8880,13 +8884,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>363093</v>
+        <v>363302</v>
       </c>
       <c r="R64" t="n">
-        <v>6882868</v>
+        <v>6882938</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8915,7 +8919,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8925,7 +8929,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8952,10 +8956,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127172219</v>
+        <v>127172542</v>
       </c>
       <c r="B65" t="n">
-        <v>79018</v>
+        <v>91348</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8963,21 +8967,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8990,10 +8994,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>363195</v>
+        <v>363093</v>
       </c>
       <c r="R65" t="n">
-        <v>6882944</v>
+        <v>6882868</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -9025,7 +9029,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9035,7 +9039,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9062,7 +9066,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127171838</v>
+        <v>127172219</v>
       </c>
       <c r="B66" t="n">
         <v>79018</v>
@@ -9092,11 +9096,7 @@
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -9104,13 +9104,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>363302</v>
+        <v>363195</v>
       </c>
       <c r="R66" t="n">
-        <v>6882938</v>
+        <v>6882944</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -8617,38 +8617,41 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127172331</v>
+        <v>127171152</v>
       </c>
       <c r="B62" t="n">
-        <v>97325</v>
+        <v>79018</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8656,10 +8659,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>363170</v>
+        <v>363314</v>
       </c>
       <c r="R62" t="n">
-        <v>6882973</v>
+        <v>6882905</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8691,7 +8694,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8701,7 +8704,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8728,41 +8731,38 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127171152</v>
+        <v>127172331</v>
       </c>
       <c r="B63" t="n">
-        <v>79018</v>
+        <v>97325</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8770,10 +8770,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>363314</v>
+        <v>363170</v>
       </c>
       <c r="R63" t="n">
-        <v>6882905</v>
+        <v>6882973</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -8493,10 +8493,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127172142</v>
+        <v>127171152</v>
       </c>
       <c r="B61" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8504,33 +8504,28 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -8540,10 +8535,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>363196</v>
+        <v>363314</v>
       </c>
       <c r="R61" t="n">
-        <v>6882950</v>
+        <v>6882905</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -8575,7 +8570,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8585,12 +8580,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackmärken.</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8617,10 +8607,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127171152</v>
+        <v>127172142</v>
       </c>
       <c r="B62" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8628,28 +8618,33 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8659,10 +8654,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>363314</v>
+        <v>363196</v>
       </c>
       <c r="R62" t="n">
-        <v>6882905</v>
+        <v>6882950</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8694,7 +8689,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8704,7 +8699,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8734,7 +8734,7 @@
         <v>127172331</v>
       </c>
       <c r="B63" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8842,10 +8842,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127171838</v>
+        <v>127172542</v>
       </c>
       <c r="B64" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8853,30 +8853,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8884,13 +8880,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>363302</v>
+        <v>363093</v>
       </c>
       <c r="R64" t="n">
-        <v>6882938</v>
+        <v>6882868</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8919,7 +8915,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8929,7 +8925,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8956,10 +8952,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127172542</v>
+        <v>127172219</v>
       </c>
       <c r="B65" t="n">
-        <v>91348</v>
+        <v>79020</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8967,21 +8963,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8994,10 +8990,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>363093</v>
+        <v>363195</v>
       </c>
       <c r="R65" t="n">
-        <v>6882868</v>
+        <v>6882944</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -9029,7 +9025,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9039,7 +9035,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9066,10 +9062,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127172219</v>
+        <v>127171838</v>
       </c>
       <c r="B66" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9096,7 +9092,11 @@
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -9104,13 +9104,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>363195</v>
+        <v>363302</v>
       </c>
       <c r="R66" t="n">
-        <v>6882944</v>
+        <v>6882938</v>
       </c>
       <c r="S66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9179,7 +9179,7 @@
         <v>127170708</v>
       </c>
       <c r="B67" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>127172322</v>
       </c>
       <c r="B68" t="n">
-        <v>79097</v>
+        <v>79099</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>127170420</v>
       </c>
       <c r="B69" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>127170947</v>
       </c>
       <c r="B70" t="n">
-        <v>79097</v>
+        <v>79099</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>127172203</v>
       </c>
       <c r="B71" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>127171879</v>
       </c>
       <c r="B72" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>127170500</v>
       </c>
       <c r="B73" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>127170971</v>
       </c>
       <c r="B74" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>127171558</v>
       </c>
       <c r="B75" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>127170911</v>
       </c>
       <c r="B76" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>127172403</v>
       </c>
       <c r="B77" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>127315773</v>
       </c>
       <c r="B78" t="n">
-        <v>57765</v>
+        <v>57767</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>127315676</v>
       </c>
       <c r="B79" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -8493,41 +8493,38 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127171152</v>
+        <v>127172331</v>
       </c>
       <c r="B61" t="n">
-        <v>79020</v>
+        <v>97327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8535,10 +8532,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>363314</v>
+        <v>363170</v>
       </c>
       <c r="R61" t="n">
-        <v>6882905</v>
+        <v>6882973</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -8570,7 +8567,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8580,7 +8577,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8607,10 +8604,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127172142</v>
+        <v>127171152</v>
       </c>
       <c r="B62" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8618,33 +8615,28 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8654,10 +8646,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>363196</v>
+        <v>363314</v>
       </c>
       <c r="R62" t="n">
-        <v>6882950</v>
+        <v>6882905</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8689,7 +8681,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8699,12 +8691,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackmärken.</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8731,38 +8718,46 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127172331</v>
+        <v>127172142</v>
       </c>
       <c r="B63" t="n">
-        <v>97327</v>
+        <v>57663</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8770,10 +8765,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>363170</v>
+        <v>363196</v>
       </c>
       <c r="R63" t="n">
-        <v>6882973</v>
+        <v>6882950</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8805,7 +8800,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8815,7 +8810,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8842,10 +8842,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127172542</v>
+        <v>127171838</v>
       </c>
       <c r="B64" t="n">
-        <v>91350</v>
+        <v>79020</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8853,26 +8853,30 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8880,13 +8884,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>363093</v>
+        <v>363302</v>
       </c>
       <c r="R64" t="n">
-        <v>6882868</v>
+        <v>6882938</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8915,7 +8919,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8925,7 +8929,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9062,10 +9066,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127171838</v>
+        <v>127172542</v>
       </c>
       <c r="B66" t="n">
-        <v>79020</v>
+        <v>91350</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9073,30 +9077,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -9104,13 +9104,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>363302</v>
+        <v>363093</v>
       </c>
       <c r="R66" t="n">
-        <v>6882938</v>
+        <v>6882868</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -8493,38 +8493,41 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127172331</v>
+        <v>127171152</v>
       </c>
       <c r="B61" t="n">
-        <v>97327</v>
+        <v>79020</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8532,10 +8535,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>363170</v>
+        <v>363314</v>
       </c>
       <c r="R61" t="n">
-        <v>6882973</v>
+        <v>6882905</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -8567,7 +8570,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8577,7 +8580,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8604,10 +8607,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127171152</v>
+        <v>127172142</v>
       </c>
       <c r="B62" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8615,28 +8618,33 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8646,10 +8654,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>363314</v>
+        <v>363196</v>
       </c>
       <c r="R62" t="n">
-        <v>6882905</v>
+        <v>6882950</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8681,7 +8689,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8691,7 +8699,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8718,46 +8731,38 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127172142</v>
+        <v>127172331</v>
       </c>
       <c r="B63" t="n">
-        <v>57663</v>
+        <v>97327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8765,10 +8770,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>363196</v>
+        <v>363170</v>
       </c>
       <c r="R63" t="n">
-        <v>6882950</v>
+        <v>6882973</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8800,7 +8805,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8810,12 +8815,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackmärken.</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -9961,46 +9961,38 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127170971</v>
+        <v>127171558</v>
       </c>
       <c r="B74" t="n">
-        <v>57663</v>
+        <v>97327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -10008,10 +10000,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>363315</v>
+        <v>363325</v>
       </c>
       <c r="R74" t="n">
-        <v>6882898</v>
+        <v>6882909</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -10043,7 +10035,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10053,7 +10045,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10080,38 +10072,46 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127171558</v>
+        <v>127170971</v>
       </c>
       <c r="B75" t="n">
-        <v>97327</v>
+        <v>57663</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10119,10 +10119,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>363325</v>
+        <v>363315</v>
       </c>
       <c r="R75" t="n">
-        <v>6882909</v>
+        <v>6882898</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -10154,7 +10154,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -8493,41 +8493,38 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127171152</v>
+        <v>127172331</v>
       </c>
       <c r="B61" t="n">
-        <v>79020</v>
+        <v>97327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8535,10 +8532,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>363314</v>
+        <v>363170</v>
       </c>
       <c r="R61" t="n">
-        <v>6882905</v>
+        <v>6882973</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -8570,7 +8567,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8580,7 +8577,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8607,10 +8604,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127172142</v>
+        <v>127171152</v>
       </c>
       <c r="B62" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8618,33 +8615,28 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8654,10 +8646,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>363196</v>
+        <v>363314</v>
       </c>
       <c r="R62" t="n">
-        <v>6882950</v>
+        <v>6882905</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8689,7 +8681,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8699,12 +8691,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackmärken.</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8731,38 +8718,46 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127172331</v>
+        <v>127172142</v>
       </c>
       <c r="B63" t="n">
-        <v>97327</v>
+        <v>57663</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8770,10 +8765,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>363170</v>
+        <v>363196</v>
       </c>
       <c r="R63" t="n">
-        <v>6882973</v>
+        <v>6882950</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8805,7 +8800,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8815,7 +8810,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8842,10 +8842,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127171838</v>
+        <v>127172542</v>
       </c>
       <c r="B64" t="n">
-        <v>79020</v>
+        <v>91350</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8853,30 +8853,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8884,13 +8880,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>363302</v>
+        <v>363093</v>
       </c>
       <c r="R64" t="n">
-        <v>6882938</v>
+        <v>6882868</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8919,7 +8915,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8929,7 +8925,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9066,10 +9062,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127172542</v>
+        <v>127171838</v>
       </c>
       <c r="B66" t="n">
-        <v>91350</v>
+        <v>79020</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9077,26 +9073,30 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -9104,13 +9104,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>363093</v>
+        <v>363302</v>
       </c>
       <c r="R66" t="n">
-        <v>6882868</v>
+        <v>6882938</v>
       </c>
       <c r="S66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9176,7 +9176,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127170708</v>
+        <v>127170642</v>
       </c>
       <c r="B67" t="n">
         <v>79020</v>
@@ -9253,7 +9253,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9263,7 +9263,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Garnlavsdraperade granar.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9961,38 +9966,46 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127171558</v>
+        <v>127170971</v>
       </c>
       <c r="B74" t="n">
-        <v>97327</v>
+        <v>57663</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -10000,10 +10013,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>363325</v>
+        <v>363315</v>
       </c>
       <c r="R74" t="n">
-        <v>6882909</v>
+        <v>6882898</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -10035,7 +10048,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10045,7 +10058,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10072,46 +10085,38 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127170971</v>
+        <v>127171558</v>
       </c>
       <c r="B75" t="n">
-        <v>57663</v>
+        <v>97327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10119,10 +10124,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>363315</v>
+        <v>363325</v>
       </c>
       <c r="R75" t="n">
-        <v>6882898</v>
+        <v>6882909</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -10154,7 +10159,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10164,7 +10169,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -8496,7 +8496,7 @@
         <v>127172331</v>
       </c>
       <c r="B61" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>127172542</v>
       </c>
       <c r="B64" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127172219</v>
+        <v>127171838</v>
       </c>
       <c r="B65" t="n">
         <v>79020</v>
@@ -8982,7 +8982,11 @@
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8990,13 +8994,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>363195</v>
+        <v>363302</v>
       </c>
       <c r="R65" t="n">
-        <v>6882944</v>
+        <v>6882938</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9025,7 +9029,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9035,7 +9039,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9062,7 +9066,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127171838</v>
+        <v>127172219</v>
       </c>
       <c r="B66" t="n">
         <v>79020</v>
@@ -9092,11 +9096,7 @@
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -9104,13 +9104,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>363302</v>
+        <v>363195</v>
       </c>
       <c r="R66" t="n">
-        <v>6882938</v>
+        <v>6882944</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9176,7 +9176,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127170642</v>
+        <v>127170708</v>
       </c>
       <c r="B67" t="n">
         <v>79020</v>
@@ -9253,7 +9253,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9263,12 +9263,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:43</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Garnlavsdraperade granar.</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9633,7 +9628,7 @@
         <v>127172203</v>
       </c>
       <c r="B71" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10088,7 +10083,7 @@
         <v>127171558</v>
       </c>
       <c r="B75" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10314,7 +10309,7 @@
         <v>127172403</v>
       </c>
       <c r="B77" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -8493,38 +8493,41 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127172331</v>
+        <v>127171152</v>
       </c>
       <c r="B61" t="n">
-        <v>97333</v>
+        <v>79023</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8532,10 +8535,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>363170</v>
+        <v>363314</v>
       </c>
       <c r="R61" t="n">
-        <v>6882973</v>
+        <v>6882905</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -8567,7 +8570,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8577,7 +8580,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8604,10 +8607,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127171152</v>
+        <v>127172142</v>
       </c>
       <c r="B62" t="n">
-        <v>79020</v>
+        <v>57666</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8615,28 +8618,33 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8646,10 +8654,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>363314</v>
+        <v>363196</v>
       </c>
       <c r="R62" t="n">
-        <v>6882905</v>
+        <v>6882950</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8681,7 +8689,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8691,7 +8699,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8718,46 +8731,38 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127172142</v>
+        <v>127172331</v>
       </c>
       <c r="B63" t="n">
-        <v>57663</v>
+        <v>97336</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8765,10 +8770,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>363196</v>
+        <v>363170</v>
       </c>
       <c r="R63" t="n">
-        <v>6882950</v>
+        <v>6882973</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8800,7 +8805,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8810,12 +8815,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackmärken.</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8842,10 +8842,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127172542</v>
+        <v>127171838</v>
       </c>
       <c r="B64" t="n">
-        <v>91356</v>
+        <v>79023</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8853,26 +8853,30 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8880,13 +8884,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>363093</v>
+        <v>363302</v>
       </c>
       <c r="R64" t="n">
-        <v>6882868</v>
+        <v>6882938</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8915,7 +8919,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8925,7 +8929,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8952,10 +8956,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127171838</v>
+        <v>127172542</v>
       </c>
       <c r="B65" t="n">
-        <v>79020</v>
+        <v>91359</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8963,30 +8967,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8994,13 +8994,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>363302</v>
+        <v>363093</v>
       </c>
       <c r="R65" t="n">
-        <v>6882938</v>
+        <v>6882868</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9069,7 +9069,7 @@
         <v>127172219</v>
       </c>
       <c r="B66" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>127170708</v>
       </c>
       <c r="B67" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>127172322</v>
       </c>
       <c r="B68" t="n">
-        <v>79099</v>
+        <v>79102</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>127170420</v>
       </c>
       <c r="B69" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>127170947</v>
       </c>
       <c r="B70" t="n">
-        <v>79099</v>
+        <v>79102</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>127172203</v>
       </c>
       <c r="B71" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>127171879</v>
       </c>
       <c r="B72" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>127170500</v>
       </c>
       <c r="B73" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>127170971</v>
       </c>
       <c r="B74" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>127171558</v>
       </c>
       <c r="B75" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>127170911</v>
       </c>
       <c r="B76" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>127172403</v>
       </c>
       <c r="B77" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>127315773</v>
       </c>
       <c r="B78" t="n">
-        <v>57767</v>
+        <v>57770</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>127315676</v>
       </c>
       <c r="B79" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -8496,7 +8496,7 @@
         <v>127171152</v>
       </c>
       <c r="B61" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>127172142</v>
       </c>
       <c r="B62" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>127172331</v>
       </c>
       <c r="B63" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8842,10 +8842,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127171838</v>
+        <v>127172542</v>
       </c>
       <c r="B64" t="n">
-        <v>79023</v>
+        <v>91367</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8853,30 +8853,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8884,13 +8880,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>363302</v>
+        <v>363093</v>
       </c>
       <c r="R64" t="n">
-        <v>6882938</v>
+        <v>6882868</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8919,7 +8915,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8929,7 +8925,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8956,10 +8952,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127172542</v>
+        <v>127171838</v>
       </c>
       <c r="B65" t="n">
-        <v>91359</v>
+        <v>79029</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8967,26 +8963,30 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8994,13 +8994,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>363093</v>
+        <v>363302</v>
       </c>
       <c r="R65" t="n">
-        <v>6882868</v>
+        <v>6882938</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9069,7 +9069,7 @@
         <v>127172219</v>
       </c>
       <c r="B66" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>127170708</v>
       </c>
       <c r="B67" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>127172322</v>
       </c>
       <c r="B68" t="n">
-        <v>79102</v>
+        <v>79108</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>127170420</v>
       </c>
       <c r="B69" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>127170947</v>
       </c>
       <c r="B70" t="n">
-        <v>79102</v>
+        <v>79108</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>127172203</v>
       </c>
       <c r="B71" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>127171879</v>
       </c>
       <c r="B72" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>127170500</v>
       </c>
       <c r="B73" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>127170971</v>
       </c>
       <c r="B74" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>127171558</v>
       </c>
       <c r="B75" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>127170911</v>
       </c>
       <c r="B76" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>127172403</v>
       </c>
       <c r="B77" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>127315773</v>
       </c>
       <c r="B78" t="n">
-        <v>57770</v>
+        <v>57776</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>127315676</v>
       </c>
       <c r="B79" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -8734,7 +8734,7 @@
         <v>127172331</v>
       </c>
       <c r="B63" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8842,10 +8842,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127172542</v>
+        <v>127171838</v>
       </c>
       <c r="B64" t="n">
-        <v>91367</v>
+        <v>79029</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8853,26 +8853,30 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8880,13 +8884,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>363093</v>
+        <v>363302</v>
       </c>
       <c r="R64" t="n">
-        <v>6882868</v>
+        <v>6882938</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8915,7 +8919,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8925,7 +8929,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8952,10 +8956,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127171838</v>
+        <v>127172542</v>
       </c>
       <c r="B65" t="n">
-        <v>79029</v>
+        <v>91368</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8963,30 +8967,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8994,13 +8994,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>363302</v>
+        <v>363093</v>
       </c>
       <c r="R65" t="n">
-        <v>6882938</v>
+        <v>6882868</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9628,7 +9628,7 @@
         <v>127172203</v>
       </c>
       <c r="B71" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9961,46 +9961,38 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127170971</v>
+        <v>127171558</v>
       </c>
       <c r="B74" t="n">
-        <v>57672</v>
+        <v>97345</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -10008,10 +10000,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>363315</v>
+        <v>363325</v>
       </c>
       <c r="R74" t="n">
-        <v>6882898</v>
+        <v>6882909</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -10043,7 +10035,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10053,7 +10045,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10080,38 +10072,46 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127171558</v>
+        <v>127170971</v>
       </c>
       <c r="B75" t="n">
-        <v>97344</v>
+        <v>57672</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10119,10 +10119,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>363325</v>
+        <v>363315</v>
       </c>
       <c r="R75" t="n">
-        <v>6882909</v>
+        <v>6882898</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -10154,7 +10154,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10309,7 +10309,7 @@
         <v>127172403</v>
       </c>
       <c r="B77" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY79"/>
+  <dimension ref="A1:AY86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10675,6 +10675,829 @@
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128820534</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57820</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Kokällmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>362267</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6882595</v>
+      </c>
+      <c r="S80" t="n">
+        <v>4</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128820515</v>
+      </c>
+      <c r="B81" t="n">
+        <v>97490</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Kokällmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>362287</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6882523</v>
+      </c>
+      <c r="S81" t="n">
+        <v>4</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128820649</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79116</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Kokällmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>362222</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6882658</v>
+      </c>
+      <c r="S82" t="n">
+        <v>4</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128822185</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57716</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Kokällmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>362326</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6882768</v>
+      </c>
+      <c r="S83" t="n">
+        <v>4</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128820694</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79195</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>864</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Kokällmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>362220</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6882659</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>128822490</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57716</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Kokällmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>362260</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6882421</v>
+      </c>
+      <c r="S85" t="n">
+        <v>4</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>128822499</v>
+      </c>
+      <c r="B86" t="n">
+        <v>57716</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Kokällmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>362273</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6882421</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -10911,10 +10911,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128820649</v>
+        <v>128822185</v>
       </c>
       <c r="B82" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10922,41 +10922,50 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>362222</v>
+        <v>362326</v>
       </c>
       <c r="R82" t="n">
-        <v>6882658</v>
+        <v>6882768</v>
       </c>
       <c r="S82" t="n">
         <v>4</v>
@@ -10988,7 +10997,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10998,7 +11007,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11025,10 +11034,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128822185</v>
+        <v>128820649</v>
       </c>
       <c r="B83" t="n">
-        <v>57716</v>
+        <v>79116</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11036,50 +11045,41 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>362326</v>
+        <v>362222</v>
       </c>
       <c r="R83" t="n">
-        <v>6882768</v>
+        <v>6882658</v>
       </c>
       <c r="S83" t="n">
         <v>4</v>
@@ -11111,7 +11111,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD83" t="b">

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -10799,7 +10799,7 @@
         <v>128820515</v>
       </c>
       <c r="B81" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10911,10 +10911,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128822185</v>
+        <v>128820649</v>
       </c>
       <c r="B82" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10922,50 +10922,41 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>362326</v>
+        <v>362222</v>
       </c>
       <c r="R82" t="n">
-        <v>6882768</v>
+        <v>6882658</v>
       </c>
       <c r="S82" t="n">
         <v>4</v>
@@ -10997,7 +10988,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -11007,7 +10998,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11034,10 +11025,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128820649</v>
+        <v>128822185</v>
       </c>
       <c r="B83" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11045,41 +11036,50 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>362222</v>
+        <v>362326</v>
       </c>
       <c r="R83" t="n">
-        <v>6882658</v>
+        <v>6882768</v>
       </c>
       <c r="S83" t="n">
         <v>4</v>
@@ -11111,7 +11111,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11151,7 +11151,7 @@
         <v>128820694</v>
       </c>
       <c r="B84" t="n">
-        <v>79195</v>
+        <v>79199</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -10799,7 +10799,7 @@
         <v>128820515</v>
       </c>
       <c r="B81" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -11148,10 +11148,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128820694</v>
+        <v>128822490</v>
       </c>
       <c r="B84" t="n">
-        <v>79199</v>
+        <v>57716</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11159,40 +11159,53 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>362220</v>
+        <v>362260</v>
       </c>
       <c r="R84" t="n">
-        <v>6882659</v>
+        <v>6882421</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11221,7 +11234,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11231,7 +11244,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11258,10 +11271,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128822490</v>
+        <v>128820694</v>
       </c>
       <c r="B85" t="n">
-        <v>57716</v>
+        <v>79199</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11269,53 +11282,40 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>362260</v>
+        <v>362220</v>
       </c>
       <c r="R85" t="n">
-        <v>6882421</v>
+        <v>6882659</v>
       </c>
       <c r="S85" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -11148,10 +11148,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128822490</v>
+        <v>128820694</v>
       </c>
       <c r="B84" t="n">
-        <v>57716</v>
+        <v>79199</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11159,53 +11159,40 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>362260</v>
+        <v>362220</v>
       </c>
       <c r="R84" t="n">
-        <v>6882421</v>
+        <v>6882659</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11234,7 +11221,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11244,7 +11231,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11271,10 +11258,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128820694</v>
+        <v>128822490</v>
       </c>
       <c r="B85" t="n">
-        <v>79199</v>
+        <v>57716</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11282,40 +11269,53 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>362220</v>
+        <v>362260</v>
       </c>
       <c r="R85" t="n">
-        <v>6882659</v>
+        <v>6882421</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -10680,7 +10680,7 @@
         <v>128820534</v>
       </c>
       <c r="B80" t="n">
-        <v>57820</v>
+        <v>57824</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>128820515</v>
       </c>
       <c r="B81" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10911,10 +10911,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128820649</v>
+        <v>128822185</v>
       </c>
       <c r="B82" t="n">
-        <v>79120</v>
+        <v>57720</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10922,41 +10922,50 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>362222</v>
+        <v>362326</v>
       </c>
       <c r="R82" t="n">
-        <v>6882658</v>
+        <v>6882768</v>
       </c>
       <c r="S82" t="n">
         <v>4</v>
@@ -10988,7 +10997,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10998,7 +11007,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11025,10 +11034,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128822185</v>
+        <v>128820649</v>
       </c>
       <c r="B83" t="n">
-        <v>57716</v>
+        <v>79124</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11036,50 +11045,41 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>362326</v>
+        <v>362222</v>
       </c>
       <c r="R83" t="n">
-        <v>6882768</v>
+        <v>6882658</v>
       </c>
       <c r="S83" t="n">
         <v>4</v>
@@ -11111,7 +11111,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11151,7 +11151,7 @@
         <v>128820694</v>
       </c>
       <c r="B84" t="n">
-        <v>79199</v>
+        <v>79203</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>128822490</v>
       </c>
       <c r="B85" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>128822499</v>
       </c>
       <c r="B86" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -11148,10 +11148,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128820694</v>
+        <v>128822490</v>
       </c>
       <c r="B84" t="n">
-        <v>79203</v>
+        <v>57720</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11159,40 +11159,53 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>362220</v>
+        <v>362260</v>
       </c>
       <c r="R84" t="n">
-        <v>6882659</v>
+        <v>6882421</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11221,7 +11234,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11231,7 +11244,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11258,10 +11271,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128822490</v>
+        <v>128820694</v>
       </c>
       <c r="B85" t="n">
-        <v>57720</v>
+        <v>79203</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11269,53 +11282,40 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>362260</v>
+        <v>362220</v>
       </c>
       <c r="R85" t="n">
-        <v>6882421</v>
+        <v>6882659</v>
       </c>
       <c r="S85" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -10911,10 +10911,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128822185</v>
+        <v>128820649</v>
       </c>
       <c r="B82" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10922,50 +10922,41 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>362326</v>
+        <v>362222</v>
       </c>
       <c r="R82" t="n">
-        <v>6882768</v>
+        <v>6882658</v>
       </c>
       <c r="S82" t="n">
         <v>4</v>
@@ -10997,7 +10988,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -11007,7 +10998,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11034,10 +11025,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128820649</v>
+        <v>128822185</v>
       </c>
       <c r="B83" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11045,41 +11036,50 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>362222</v>
+        <v>362326</v>
       </c>
       <c r="R83" t="n">
-        <v>6882658</v>
+        <v>6882768</v>
       </c>
       <c r="S83" t="n">
         <v>4</v>
@@ -11111,7 +11111,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD83" t="b">

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -10680,7 +10680,7 @@
         <v>128820534</v>
       </c>
       <c r="B80" t="n">
-        <v>57824</v>
+        <v>57827</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>128820515</v>
       </c>
       <c r="B81" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
         <v>128820649</v>
       </c>
       <c r="B82" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>128822185</v>
       </c>
       <c r="B83" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11148,10 +11148,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128822490</v>
+        <v>128820694</v>
       </c>
       <c r="B84" t="n">
-        <v>57720</v>
+        <v>79108</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11159,53 +11159,40 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>362260</v>
+        <v>362220</v>
       </c>
       <c r="R84" t="n">
-        <v>6882421</v>
+        <v>6882659</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11234,7 +11221,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11244,7 +11231,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11271,10 +11258,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128820694</v>
+        <v>128822490</v>
       </c>
       <c r="B85" t="n">
-        <v>79203</v>
+        <v>57723</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11282,40 +11269,53 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>362220</v>
+        <v>362260</v>
       </c>
       <c r="R85" t="n">
-        <v>6882659</v>
+        <v>6882421</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11384,7 +11384,7 @@
         <v>128822499</v>
       </c>
       <c r="B86" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -10799,7 +10799,7 @@
         <v>128820515</v>
       </c>
       <c r="B81" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -10799,7 +10799,7 @@
         <v>128820515</v>
       </c>
       <c r="B81" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
         <v>128820649</v>
       </c>
       <c r="B82" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11148,10 +11148,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128822490</v>
+        <v>128820694</v>
       </c>
       <c r="B84" t="n">
-        <v>57723</v>
+        <v>79114</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11159,53 +11159,40 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>362260</v>
+        <v>362220</v>
       </c>
       <c r="R84" t="n">
-        <v>6882421</v>
+        <v>6882659</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11234,7 +11221,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11244,7 +11231,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11271,10 +11258,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128820694</v>
+        <v>128822490</v>
       </c>
       <c r="B85" t="n">
-        <v>79113</v>
+        <v>57723</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11282,40 +11269,53 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>362220</v>
+        <v>362260</v>
       </c>
       <c r="R85" t="n">
-        <v>6882659</v>
+        <v>6882421</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -10680,7 +10680,7 @@
         <v>128820534</v>
       </c>
       <c r="B80" t="n">
-        <v>57827</v>
+        <v>57829</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>128820515</v>
       </c>
       <c r="B81" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
         <v>128820649</v>
       </c>
       <c r="B82" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>128822185</v>
       </c>
       <c r="B83" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11148,10 +11148,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128820694</v>
+        <v>128822490</v>
       </c>
       <c r="B84" t="n">
-        <v>79114</v>
+        <v>57725</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11159,40 +11159,53 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>362220</v>
+        <v>362260</v>
       </c>
       <c r="R84" t="n">
-        <v>6882659</v>
+        <v>6882421</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11221,7 +11234,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11231,7 +11244,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11258,10 +11271,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128822490</v>
+        <v>128820694</v>
       </c>
       <c r="B85" t="n">
-        <v>57723</v>
+        <v>79118</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11269,53 +11282,40 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>362260</v>
+        <v>362220</v>
       </c>
       <c r="R85" t="n">
-        <v>6882421</v>
+        <v>6882659</v>
       </c>
       <c r="S85" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11384,7 +11384,7 @@
         <v>128822499</v>
       </c>
       <c r="B86" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -11148,10 +11148,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128822490</v>
+        <v>128820694</v>
       </c>
       <c r="B84" t="n">
-        <v>57725</v>
+        <v>79118</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11159,53 +11159,40 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>362260</v>
+        <v>362220</v>
       </c>
       <c r="R84" t="n">
-        <v>6882421</v>
+        <v>6882659</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11234,7 +11221,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11244,7 +11231,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11271,10 +11258,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128820694</v>
+        <v>128822490</v>
       </c>
       <c r="B85" t="n">
-        <v>79118</v>
+        <v>57725</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11282,40 +11269,53 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>362220</v>
+        <v>362260</v>
       </c>
       <c r="R85" t="n">
-        <v>6882659</v>
+        <v>6882421</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -10799,7 +10799,7 @@
         <v>128820515</v>
       </c>
       <c r="B81" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -10680,7 +10680,7 @@
         <v>128820534</v>
       </c>
       <c r="B80" t="n">
-        <v>57829</v>
+        <v>57831</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>128820515</v>
       </c>
       <c r="B81" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
         <v>128820649</v>
       </c>
       <c r="B82" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>128822185</v>
       </c>
       <c r="B83" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11148,10 +11148,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128820694</v>
+        <v>128822490</v>
       </c>
       <c r="B84" t="n">
-        <v>79118</v>
+        <v>57727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11159,40 +11159,53 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>362220</v>
+        <v>362260</v>
       </c>
       <c r="R84" t="n">
-        <v>6882659</v>
+        <v>6882421</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11221,7 +11234,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11231,7 +11244,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11258,10 +11271,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128822490</v>
+        <v>128820694</v>
       </c>
       <c r="B85" t="n">
-        <v>57725</v>
+        <v>79120</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11269,53 +11282,40 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>362260</v>
+        <v>362220</v>
       </c>
       <c r="R85" t="n">
-        <v>6882421</v>
+        <v>6882659</v>
       </c>
       <c r="S85" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11384,7 +11384,7 @@
         <v>128822499</v>
       </c>
       <c r="B86" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -11148,10 +11148,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128822490</v>
+        <v>128820694</v>
       </c>
       <c r="B84" t="n">
-        <v>57727</v>
+        <v>79120</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11159,53 +11159,40 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>362260</v>
+        <v>362220</v>
       </c>
       <c r="R84" t="n">
-        <v>6882421</v>
+        <v>6882659</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11234,7 +11221,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11244,7 +11231,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11271,10 +11258,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128820694</v>
+        <v>128822490</v>
       </c>
       <c r="B85" t="n">
-        <v>79120</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11282,40 +11269,53 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>362220</v>
+        <v>362260</v>
       </c>
       <c r="R85" t="n">
-        <v>6882659</v>
+        <v>6882421</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -10911,10 +10911,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128820649</v>
+        <v>128822185</v>
       </c>
       <c r="B82" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10922,41 +10922,50 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>362222</v>
+        <v>362326</v>
       </c>
       <c r="R82" t="n">
-        <v>6882658</v>
+        <v>6882768</v>
       </c>
       <c r="S82" t="n">
         <v>4</v>
@@ -10988,7 +10997,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10998,7 +11007,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11025,10 +11034,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128822185</v>
+        <v>128820649</v>
       </c>
       <c r="B83" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11036,50 +11045,41 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>362326</v>
+        <v>362222</v>
       </c>
       <c r="R83" t="n">
-        <v>6882768</v>
+        <v>6882658</v>
       </c>
       <c r="S83" t="n">
         <v>4</v>
@@ -11111,7 +11111,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD83" t="b">

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -10799,7 +10799,7 @@
         <v>128820515</v>
       </c>
       <c r="B81" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10911,10 +10911,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128822185</v>
+        <v>128820649</v>
       </c>
       <c r="B82" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10922,50 +10922,41 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>362326</v>
+        <v>362222</v>
       </c>
       <c r="R82" t="n">
-        <v>6882768</v>
+        <v>6882658</v>
       </c>
       <c r="S82" t="n">
         <v>4</v>
@@ -10997,7 +10988,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -11007,7 +10998,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11034,10 +11025,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128820649</v>
+        <v>128822185</v>
       </c>
       <c r="B83" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11045,41 +11036,50 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>362222</v>
+        <v>362326</v>
       </c>
       <c r="R83" t="n">
-        <v>6882658</v>
+        <v>6882768</v>
       </c>
       <c r="S83" t="n">
         <v>4</v>
@@ -11111,7 +11111,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11148,10 +11148,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128820694</v>
+        <v>128822490</v>
       </c>
       <c r="B84" t="n">
-        <v>79120</v>
+        <v>57727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11159,40 +11159,53 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>362220</v>
+        <v>362260</v>
       </c>
       <c r="R84" t="n">
-        <v>6882659</v>
+        <v>6882421</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11221,7 +11234,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11231,7 +11244,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11258,10 +11271,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128822490</v>
+        <v>128820694</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>79120</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11269,53 +11282,40 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>362260</v>
+        <v>362220</v>
       </c>
       <c r="R85" t="n">
-        <v>6882421</v>
+        <v>6882659</v>
       </c>
       <c r="S85" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -10799,7 +10799,7 @@
         <v>128820515</v>
       </c>
       <c r="B81" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11148,10 +11148,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128822490</v>
+        <v>128820694</v>
       </c>
       <c r="B84" t="n">
-        <v>57727</v>
+        <v>79120</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11159,53 +11159,40 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>362260</v>
+        <v>362220</v>
       </c>
       <c r="R84" t="n">
-        <v>6882421</v>
+        <v>6882659</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11234,7 +11221,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11244,7 +11231,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11271,10 +11258,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128820694</v>
+        <v>128822490</v>
       </c>
       <c r="B85" t="n">
-        <v>79120</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11282,40 +11269,53 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>362220</v>
+        <v>362260</v>
       </c>
       <c r="R85" t="n">
-        <v>6882659</v>
+        <v>6882421</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -10799,7 +10799,7 @@
         <v>128820515</v>
       </c>
       <c r="B81" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11148,10 +11148,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128820694</v>
+        <v>128822490</v>
       </c>
       <c r="B84" t="n">
-        <v>79120</v>
+        <v>57727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11159,40 +11159,53 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>362220</v>
+        <v>362260</v>
       </c>
       <c r="R84" t="n">
-        <v>6882659</v>
+        <v>6882421</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11221,7 +11234,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11231,7 +11244,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11258,10 +11271,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128822490</v>
+        <v>128820694</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>79120</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11269,53 +11282,40 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>362260</v>
+        <v>362220</v>
       </c>
       <c r="R85" t="n">
-        <v>6882421</v>
+        <v>6882659</v>
       </c>
       <c r="S85" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY86"/>
+  <dimension ref="A1:AY84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8493,10 +8493,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127171152</v>
+        <v>127172142</v>
       </c>
       <c r="B61" t="n">
-        <v>79029</v>
+        <v>57657</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8504,28 +8504,33 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -8535,10 +8540,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>363314</v>
+        <v>363196</v>
       </c>
       <c r="R61" t="n">
-        <v>6882905</v>
+        <v>6882950</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -8570,7 +8575,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8580,7 +8585,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8607,46 +8617,38 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127172142</v>
+        <v>127172331</v>
       </c>
       <c r="B62" t="n">
-        <v>57672</v>
+        <v>97314</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8654,10 +8656,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>363196</v>
+        <v>363170</v>
       </c>
       <c r="R62" t="n">
-        <v>6882950</v>
+        <v>6882973</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8689,7 +8691,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8699,12 +8701,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackmärken.</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8731,38 +8728,41 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127172331</v>
+        <v>127171152</v>
       </c>
       <c r="B63" t="n">
-        <v>97345</v>
+        <v>79011</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8770,10 +8770,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>363170</v>
+        <v>363314</v>
       </c>
       <c r="R63" t="n">
-        <v>6882973</v>
+        <v>6882905</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8845,7 +8845,7 @@
         <v>127171838</v>
       </c>
       <c r="B64" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>127172542</v>
       </c>
       <c r="B65" t="n">
-        <v>91368</v>
+        <v>91337</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>127172219</v>
       </c>
       <c r="B66" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>127170708</v>
       </c>
       <c r="B67" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>127172322</v>
       </c>
       <c r="B68" t="n">
-        <v>79108</v>
+        <v>79090</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>127170420</v>
       </c>
       <c r="B69" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>127170947</v>
       </c>
       <c r="B70" t="n">
-        <v>79108</v>
+        <v>79090</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>127172203</v>
       </c>
       <c r="B71" t="n">
-        <v>97345</v>
+        <v>97314</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>127171879</v>
       </c>
       <c r="B72" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>127170500</v>
       </c>
       <c r="B73" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9961,38 +9961,46 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127171558</v>
+        <v>127170971</v>
       </c>
       <c r="B74" t="n">
-        <v>97345</v>
+        <v>57657</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -10000,10 +10008,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>363325</v>
+        <v>363315</v>
       </c>
       <c r="R74" t="n">
-        <v>6882909</v>
+        <v>6882898</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -10035,7 +10043,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10045,7 +10053,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10072,46 +10080,38 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127170971</v>
+        <v>127171558</v>
       </c>
       <c r="B75" t="n">
-        <v>57672</v>
+        <v>97314</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10119,10 +10119,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>363315</v>
+        <v>363325</v>
       </c>
       <c r="R75" t="n">
-        <v>6882898</v>
+        <v>6882909</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -10154,7 +10154,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10194,7 +10194,7 @@
         <v>127170911</v>
       </c>
       <c r="B76" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>127172403</v>
       </c>
       <c r="B77" t="n">
-        <v>91368</v>
+        <v>91337</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10420,10 +10420,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127315773</v>
+        <v>128820534</v>
       </c>
       <c r="B78" t="n">
-        <v>57776</v>
+        <v>57831</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10450,37 +10450,30 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>363120</v>
+        <v>362267</v>
       </c>
       <c r="R78" t="n">
-        <v>6882934</v>
+        <v>6882595</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10504,22 +10497,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10534,66 +10527,50 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127315676</v>
+        <v>128820515</v>
       </c>
       <c r="B79" t="n">
-        <v>57672</v>
+        <v>97577</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -10601,17 +10578,17 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>363122</v>
+        <v>362287</v>
       </c>
       <c r="R79" t="n">
-        <v>6882946</v>
+        <v>6882523</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10635,22 +10612,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10665,58 +10642,53 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128820534</v>
+        <v>128820649</v>
       </c>
       <c r="B80" t="n">
-        <v>57831</v>
+        <v>79041</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -10724,10 +10696,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>362267</v>
+        <v>362222</v>
       </c>
       <c r="R80" t="n">
-        <v>6882595</v>
+        <v>6882658</v>
       </c>
       <c r="S80" t="n">
         <v>4</v>
@@ -10759,7 +10731,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10769,7 +10741,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10796,38 +10768,46 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128820515</v>
+        <v>128822185</v>
       </c>
       <c r="B81" t="n">
-        <v>97577</v>
+        <v>57727</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -10839,10 +10819,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>362287</v>
+        <v>362326</v>
       </c>
       <c r="R81" t="n">
-        <v>6882523</v>
+        <v>6882768</v>
       </c>
       <c r="S81" t="n">
         <v>4</v>
@@ -10874,7 +10854,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10884,7 +10864,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10911,10 +10891,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128820649</v>
+        <v>128822490</v>
       </c>
       <c r="B82" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10922,41 +10902,50 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>362222</v>
+        <v>362260</v>
       </c>
       <c r="R82" t="n">
-        <v>6882658</v>
+        <v>6882421</v>
       </c>
       <c r="S82" t="n">
         <v>4</v>
@@ -10988,7 +10977,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10998,7 +10987,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11025,10 +11014,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128822185</v>
+        <v>128820694</v>
       </c>
       <c r="B83" t="n">
-        <v>57727</v>
+        <v>79120</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11036,53 +11025,40 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>362326</v>
+        <v>362220</v>
       </c>
       <c r="R83" t="n">
-        <v>6882768</v>
+        <v>6882659</v>
       </c>
       <c r="S83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -11111,7 +11087,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11121,7 +11097,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11148,7 +11124,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128822490</v>
+        <v>128822499</v>
       </c>
       <c r="B84" t="n">
         <v>57727</v>
@@ -11188,24 +11164,20 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>362260</v>
+        <v>362273</v>
       </c>
       <c r="R84" t="n">
         <v>6882421</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11234,7 +11206,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11244,7 +11216,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11268,235 +11240,6 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>128820694</v>
-      </c>
-      <c r="B85" t="n">
-        <v>79120</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>864</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Knottrig blåslav</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Hypogymnia bitteri</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Kokällmyren, Dlr</t>
-        </is>
-      </c>
-      <c r="Q85" t="n">
-        <v>362220</v>
-      </c>
-      <c r="R85" t="n">
-        <v>6882659</v>
-      </c>
-      <c r="S85" t="n">
-        <v>5</v>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Älvdalen</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>Idre</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AD85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT85" t="inlineStr"/>
-      <c r="AW85" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>128822499</v>
-      </c>
-      <c r="B86" t="n">
-        <v>57727</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Kokällmyren, Dlr</t>
-        </is>
-      </c>
-      <c r="Q86" t="n">
-        <v>362273</v>
-      </c>
-      <c r="R86" t="n">
-        <v>6882421</v>
-      </c>
-      <c r="S86" t="n">
-        <v>5</v>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Älvdalen</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>Idre</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AD86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT86" t="inlineStr"/>
-      <c r="AW86" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -11503,7 +11503,7 @@
         <v>130470733</v>
       </c>
       <c r="B87" t="n">
-        <v>91742</v>
+        <v>91745</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -11503,7 +11503,7 @@
         <v>130470733</v>
       </c>
       <c r="B87" t="n">
-        <v>91745</v>
+        <v>91771</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -11503,7 +11503,7 @@
         <v>130470733</v>
       </c>
       <c r="B87" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -11503,7 +11503,7 @@
         <v>130470733</v>
       </c>
       <c r="B87" t="n">
-        <v>91772</v>
+        <v>91773</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -11503,7 +11503,7 @@
         <v>130470733</v>
       </c>
       <c r="B87" t="n">
-        <v>91773</v>
+        <v>91775</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -11503,7 +11503,7 @@
         <v>130470733</v>
       </c>
       <c r="B87" t="n">
-        <v>91775</v>
+        <v>91788</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -11503,7 +11503,7 @@
         <v>130470733</v>
       </c>
       <c r="B87" t="n">
-        <v>91788</v>
+        <v>91789</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -11503,7 +11503,7 @@
         <v>130470733</v>
       </c>
       <c r="B87" t="n">
-        <v>91789</v>
+        <v>91790</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -11503,7 +11503,7 @@
         <v>130470733</v>
       </c>
       <c r="B87" t="n">
-        <v>91790</v>
+        <v>91798</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY98"/>
+  <dimension ref="A1:AZ98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121899167</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -920,6 +930,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118103854</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,6 +1050,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118113514</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1145,6 +1165,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127170947</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1255,6 +1280,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172322</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1365,6 +1395,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172714</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1475,6 +1510,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128820694</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1582,6 +1622,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130470732</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1689,6 +1734,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130470733</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1796,6 +1846,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121206216</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1903,6 +1958,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121206277</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2023,6 +2083,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118112482</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2168,6 +2233,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118340526</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2295,6 +2365,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121206393</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2422,6 +2497,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121206160</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2567,6 +2647,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110444488</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2681,6 +2766,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110513997</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2795,6 +2885,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110514177</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2909,6 +3004,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110514236</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3050,6 +3150,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118103637</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3195,6 +3300,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118103682</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3316,6 +3426,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118103868</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3441,6 +3556,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118108025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3571,6 +3691,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118108207</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3690,6 +3815,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118112682</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3835,6 +3965,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118118581</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3965,6 +4100,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118119303</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4114,6 +4254,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118341001</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4228,6 +4373,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127170375</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4343,6 +4493,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127170420</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4458,6 +4613,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127170500</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4577,6 +4737,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127170642</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4692,6 +4857,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127170911</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4806,6 +4976,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171152</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4920,6 +5095,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171838</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5030,6 +5210,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171879</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5140,6 +5325,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172219</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5255,6 +5445,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172815</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5370,6 +5565,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172852</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5484,6 +5684,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128820649</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5610,6 +5815,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118118723</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5717,6 +5927,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121898927</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5847,6 +6062,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118103394</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5977,6 +6197,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118103560</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6107,6 +6332,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118107736</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6231,6 +6461,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118113015</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6355,6 +6590,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118113051</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6485,6 +6725,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118118450</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6615,6 +6860,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118118466</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6745,6 +6995,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118118547</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6875,6 +7130,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118118562</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7005,6 +7265,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118118603</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7135,6 +7400,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118118863</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7265,6 +7535,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118118905</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7395,6 +7670,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118119133</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7525,6 +7805,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118119170</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7655,6 +7940,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118119483</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7785,6 +8075,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118119653</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7915,6 +8210,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118119701</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8045,6 +8345,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118119770</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8170,6 +8475,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118119872</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8300,6 +8610,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118120074</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8430,6 +8745,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118120164</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8560,6 +8880,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118120248</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8685,6 +9010,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118120388</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8815,6 +9145,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118120447</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8945,6 +9280,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118120506</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -9075,6 +9415,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118122341</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9205,6 +9550,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118122435</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9335,6 +9685,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118122458</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9465,6 +9820,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118122497</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9595,6 +9955,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118340481</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9725,6 +10090,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118340595</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9855,6 +10225,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118340691</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9985,6 +10360,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118340748</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -10115,6 +10495,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118340920</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -10222,6 +10607,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121206319</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -10341,6 +10731,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127170971</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -10465,6 +10860,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172142</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10584,6 +10984,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172737</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10708,6 +11113,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172795</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10827,6 +11237,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172899</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10958,6 +11373,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127315676</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -11081,6 +11501,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128822185</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -11204,6 +11629,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128822490</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -11323,6 +11753,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128822499</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -11455,6 +11890,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118122325</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11581,6 +12021,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127315773</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11700,6 +12145,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128820534</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11822,6 +12272,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118122289</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11949,6 +12404,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118118517</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -12076,6 +12536,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118118821</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -12198,6 +12663,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118119084</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -12309,6 +12779,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171558</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -12420,6 +12895,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172203</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -12531,6 +13011,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172331</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -12646,8 +13131,112 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128820515</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ98"/>
+  <dimension ref="A1:AZ102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118103854</v>
+        <v>135621906</v>
       </c>
       <c r="B3" t="n">
-        <v>79406</v>
+        <v>92287</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,40 +803,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>362321</v>
+        <v>362658</v>
       </c>
       <c r="R3" t="n">
-        <v>6882091</v>
+        <v>6882750</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,27 +866,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Växer på gran i naturskog.</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,59 +890,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118103854</t>
+          <t>https://artportalen.se/Sighting/135621906</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118113514</v>
+        <v>135622151</v>
       </c>
       <c r="B4" t="n">
-        <v>79406</v>
+        <v>92287</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,40 +924,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>362466</v>
+        <v>362625</v>
       </c>
       <c r="R4" t="n">
-        <v>6882217</v>
+        <v>6882754</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,27 +978,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På björk vid myrholme. Naturskog</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,24 +1008,24 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118113514</t>
+          <t>https://artportalen.se/Sighting/135622151</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127170947</v>
+        <v>118103854</v>
       </c>
       <c r="B5" t="n">
         <v>79406</v>
@@ -1092,17 +1059,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363316</v>
+        <v>362321</v>
       </c>
       <c r="R5" t="n">
-        <v>6882898</v>
+        <v>6882091</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1126,22 +1093,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Växer på gran i naturskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,8 +1122,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1167,13 +1165,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170947</t>
+          <t>https://artportalen.se/Sighting/118103854</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127172322</v>
+        <v>118113514</v>
       </c>
       <c r="B6" t="n">
         <v>79406</v>
@@ -1207,17 +1205,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>363173</v>
+        <v>362466</v>
       </c>
       <c r="R6" t="n">
-        <v>6882970</v>
+        <v>6882217</v>
       </c>
       <c r="S6" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1241,22 +1239,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På björk vid myrholme. Naturskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,13 +1285,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172322</t>
+          <t>https://artportalen.se/Sighting/118113514</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127172714</v>
+        <v>127170947</v>
       </c>
       <c r="B7" t="n">
         <v>79406</v>
@@ -1326,10 +1329,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>363141</v>
+        <v>363316</v>
       </c>
       <c r="R7" t="n">
-        <v>6882796</v>
+        <v>6882898</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1361,7 +1364,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1371,7 +1374,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1397,13 +1400,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172714</t>
+          <t>https://artportalen.se/Sighting/127170947</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128820694</v>
+        <v>127172322</v>
       </c>
       <c r="B8" t="n">
         <v>79406</v>
@@ -1437,17 +1440,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>362220</v>
+        <v>363173</v>
       </c>
       <c r="R8" t="n">
-        <v>6882659</v>
+        <v>6882970</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1471,22 +1474,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,13 +1515,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128820694</t>
+          <t>https://artportalen.se/Sighting/127172322</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130470732</v>
+        <v>127172714</v>
       </c>
       <c r="B9" t="n">
         <v>79406</v>
@@ -1547,19 +1550,22 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lövåsen, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>363300</v>
+        <v>363141</v>
       </c>
       <c r="R9" t="n">
-        <v>6882818</v>
+        <v>6882796</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1583,22 +1589,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,65 +1619,68 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Anders Björkén, Maria Hindemo</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130470732</t>
+          <t>https://artportalen.se/Sighting/127172714</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130470733</v>
+        <v>128820694</v>
       </c>
       <c r="B10" t="n">
-        <v>91923</v>
+        <v>79406</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lövåsen, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>363275</v>
+        <v>362220</v>
       </c>
       <c r="R10" t="n">
-        <v>6882937</v>
+        <v>6882659</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1695,22 +1704,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,27 +1734,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Anders Björkén, Maria Hindemo</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130470733</t>
+          <t>https://artportalen.se/Sighting/128820694</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121206216</v>
+        <v>130470732</v>
       </c>
       <c r="B11" t="n">
-        <v>92369</v>
+        <v>79406</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,37 +1762,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Lövåsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>363227</v>
+        <v>363300</v>
       </c>
       <c r="R11" t="n">
-        <v>6882956</v>
+        <v>6882818</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1807,22 +1816,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,27 +1846,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Cajsa Björkén, Anders Björkén, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121206216</t>
+          <t>https://artportalen.se/Sighting/130470732</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121206277</v>
+        <v>135621791</v>
       </c>
       <c r="B12" t="n">
-        <v>83173</v>
+        <v>92016</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,21 +1874,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1889,13 +1898,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>363227</v>
+        <v>362646</v>
       </c>
       <c r="R12" t="n">
-        <v>6882956</v>
+        <v>6882779</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1919,22 +1928,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1949,27 +1958,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121206277</t>
+          <t>https://artportalen.se/Sighting/135621791</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118112482</v>
+        <v>130470733</v>
       </c>
       <c r="B13" t="n">
-        <v>92083</v>
+        <v>91923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,44 +1986,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1503</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Dlr</t>
+          <t>Lövåsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>362476</v>
+        <v>363275</v>
       </c>
       <c r="R13" t="n">
-        <v>6882192</v>
+        <v>6882937</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2038,27 +2040,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Växer under gammal gren från jättetall på myrholme. Skogen är avverkningsanmäld</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,34 +2064,33 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Cajsa Björkén, Anders Björkén, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118112482</t>
+          <t>https://artportalen.se/Sighting/130470733</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118340526</v>
+        <v>121206216</v>
       </c>
       <c r="B14" t="n">
-        <v>91831</v>
+        <v>92369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2102,44 +2098,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3242</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>362269</v>
+        <v>363227</v>
       </c>
       <c r="R14" t="n">
-        <v>6882132</v>
+        <v>6882956</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2163,27 +2152,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Växer på undersida av tallgren från gammal tall. Fjällnära skog.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,59 +2176,33 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Barrnaturskog. Fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340526</t>
+          <t>https://artportalen.se/Sighting/121206216</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121206393</v>
+        <v>135621801</v>
       </c>
       <c r="B15" t="n">
-        <v>91831</v>
+        <v>92448</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,21 +2210,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3242</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2276,13 +2234,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>363237</v>
+        <v>362649</v>
       </c>
       <c r="R15" t="n">
-        <v>6883017</v>
+        <v>6882777</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2306,22 +2264,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2332,73 +2290,53 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Dead branch  # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121206393</t>
+          <t>https://artportalen.se/Sighting/135621801</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121206160</v>
+        <v>121206277</v>
       </c>
       <c r="B16" t="n">
-        <v>92632</v>
+        <v>83173</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2408,10 +2346,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>363153</v>
+        <v>363227</v>
       </c>
       <c r="R16" t="n">
-        <v>6882853</v>
+        <v>6882956</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2443,7 +2381,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2453,7 +2391,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2464,26 +2402,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2499,16 +2417,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121206160</t>
+          <t>https://artportalen.se/Sighting/121206277</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110444488</v>
+        <v>118112482</v>
       </c>
       <c r="B17" t="n">
-        <v>79327</v>
+        <v>92083</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2516,44 +2434,44 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lövåsen, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>363277</v>
+        <v>362476</v>
       </c>
       <c r="R17" t="n">
-        <v>6882948</v>
+        <v>6882192</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2577,27 +2495,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ymnig förekomst av garnlav i fin grannaturskog. Granar draperade av laven. På grov gran garnlav med soral.</t>
+          <t>Växer under gammal gren från jättetall på myrholme. Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2610,31 +2528,6 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
@@ -2649,61 +2542,61 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110444488</t>
+          <t>https://artportalen.se/Sighting/118112482</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>110513997</v>
+        <v>118340526</v>
       </c>
       <c r="B18" t="n">
-        <v>79327</v>
+        <v>91831</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lövåsen , Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>363288</v>
+        <v>362269</v>
       </c>
       <c r="R18" t="n">
-        <v>6882833</v>
+        <v>6882132</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2727,22 +2620,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Växer på undersida av tallgren från gammal tall. Fjällnära skog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2751,8 +2649,34 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2768,61 +2692,54 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110513997</t>
+          <t>https://artportalen.se/Sighting/118340526</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>110514177</v>
+        <v>121206393</v>
       </c>
       <c r="B19" t="n">
-        <v>79327</v>
+        <v>91831</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lövåsen , Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>363305</v>
+        <v>363237</v>
       </c>
       <c r="R19" t="n">
-        <v>6882833</v>
+        <v>6883017</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2846,22 +2763,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2872,76 +2789,89 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Dead branch  # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110514177</t>
+          <t>https://artportalen.se/Sighting/121206393</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>110514236</v>
+        <v>121206160</v>
       </c>
       <c r="B20" t="n">
-        <v>79327</v>
+        <v>92632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lövåsen , Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>363313</v>
+        <v>363153</v>
       </c>
       <c r="R20" t="n">
-        <v>6882881</v>
+        <v>6882853</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2965,22 +2895,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2991,28 +2921,48 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110514236</t>
+          <t>https://artportalen.se/Sighting/121206160</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118103637</v>
+        <v>110444488</v>
       </c>
       <c r="B21" t="n">
         <v>79327</v>
@@ -3042,21 +2992,25 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Lövåsen, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>362276</v>
+        <v>363277</v>
       </c>
       <c r="R21" t="n">
-        <v>6882072</v>
+        <v>6882948</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3080,27 +3034,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Växer på gran i naturskog.</t>
+          <t>Ymnig förekomst av garnlav i fin grannaturskog. Granar draperade av laven. På grov gran garnlav med soral.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3152,13 +3106,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118103637</t>
+          <t>https://artportalen.se/Sighting/110444488</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118103682</v>
+        <v>110513997</v>
       </c>
       <c r="B22" t="n">
         <v>79327</v>
@@ -3187,26 +3141,26 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Lövåsen , Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>362257</v>
+        <v>363288</v>
       </c>
       <c r="R22" t="n">
-        <v>6882084</v>
+        <v>6882833</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3230,27 +3184,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Växer på gammal gran i avverkningsanmäld skog.</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3259,34 +3208,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3302,13 +3225,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118103682</t>
+          <t>https://artportalen.se/Sighting/110513997</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118103868</v>
+        <v>110514177</v>
       </c>
       <c r="B23" t="n">
         <v>79327</v>
@@ -3338,18 +3261,22 @@
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Lövåsen , Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>362279</v>
+        <v>363305</v>
       </c>
       <c r="R23" t="n">
-        <v>6882106</v>
+        <v>6882833</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3376,22 +3303,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3400,19 +3327,8 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3428,13 +3344,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118103868</t>
+          <t>https://artportalen.se/Sighting/110514177</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118108025</v>
+        <v>110514236</v>
       </c>
       <c r="B24" t="n">
         <v>79327</v>
@@ -3463,23 +3379,23 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Lövåsen , Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>362343</v>
+        <v>363313</v>
       </c>
       <c r="R24" t="n">
-        <v>6882273</v>
+        <v>6882881</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3506,22 +3422,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3530,19 +3446,8 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3558,13 +3463,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118108025</t>
+          <t>https://artportalen.se/Sighting/110514236</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118108207</v>
+        <v>118103637</v>
       </c>
       <c r="B25" t="n">
         <v>79327</v>
@@ -3593,11 +3498,7 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3606,10 +3507,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>362326</v>
+        <v>362276</v>
       </c>
       <c r="R25" t="n">
-        <v>6882154</v>
+        <v>6882072</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3641,7 +3542,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3651,12 +3552,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Naturskog med riklig förekomst av garnlav</t>
+          <t>Växer på gran i naturskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3676,7 +3577,22 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Gammelgranskog</t>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3693,13 +3609,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118108207</t>
+          <t>https://artportalen.se/Sighting/118103637</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118112682</v>
+        <v>118103682</v>
       </c>
       <c r="B26" t="n">
         <v>79327</v>
@@ -3737,14 +3653,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>362476</v>
+        <v>362257</v>
       </c>
       <c r="R26" t="n">
-        <v>6882192</v>
+        <v>6882084</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3771,27 +3687,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Växer i granbestånd på myrholme</t>
+          <t>Växer på gammal gran i avverkningsanmäld skog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3800,8 +3716,34 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3817,13 +3759,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118112682</t>
+          <t>https://artportalen.se/Sighting/118103682</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118118581</v>
+        <v>118103868</v>
       </c>
       <c r="B27" t="n">
         <v>79327</v>
@@ -3852,23 +3794,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>362380</v>
+        <v>362279</v>
       </c>
       <c r="R27" t="n">
-        <v>6882318</v>
+        <v>6882106</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3895,27 +3833,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav i grannaturskog.</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3935,22 +3868,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Grannaturskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3967,13 +3885,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118581</t>
+          <t>https://artportalen.se/Sighting/118103868</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118119303</v>
+        <v>118108025</v>
       </c>
       <c r="B28" t="n">
         <v>79327</v>
@@ -4011,14 +3929,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>362310</v>
+        <v>362343</v>
       </c>
       <c r="R28" t="n">
-        <v>6882298</v>
+        <v>6882273</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4045,27 +3963,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Väldigt långa bålar och i granbeståndet flera draperade av garnlav.</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4085,7 +3998,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4102,13 +4015,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119303</t>
+          <t>https://artportalen.se/Sighting/118108025</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118341001</v>
+        <v>118108207</v>
       </c>
       <c r="B29" t="n">
         <v>79327</v>
@@ -4142,22 +4055,18 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>362320</v>
+        <v>362326</v>
       </c>
       <c r="R29" t="n">
-        <v>6882282</v>
+        <v>6882154</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4184,27 +4093,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Granar draperade med garnlav.</t>
+          <t>Naturskog med riklig förekomst av garnlav</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4224,22 +4133,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Gammelgranskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4256,13 +4150,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118341001</t>
+          <t>https://artportalen.se/Sighting/118108207</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127170375</v>
+        <v>118112682</v>
       </c>
       <c r="B30" t="n">
         <v>79327</v>
@@ -4291,26 +4185,26 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lövåsen, Dlr</t>
+          <t>Sälderbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>363314</v>
+        <v>362476</v>
       </c>
       <c r="R30" t="n">
-        <v>6882815</v>
+        <v>6882192</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4334,22 +4228,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Växer i granbestånd på myrholme</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4375,13 +4274,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170375</t>
+          <t>https://artportalen.se/Sighting/118112682</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127170420</v>
+        <v>118118581</v>
       </c>
       <c r="B31" t="n">
         <v>79327</v>
@@ -4410,19 +4309,23 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>363307</v>
+        <v>362380</v>
       </c>
       <c r="R31" t="n">
-        <v>6882847</v>
+        <v>6882318</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4449,27 +4352,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Granar draperade med garnlav</t>
+          <t>Riklig förekomst av garnlav i grannaturskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4478,8 +4381,34 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4495,13 +4424,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170420</t>
+          <t>https://artportalen.se/Sighting/118118581</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127170500</v>
+        <v>118119303</v>
       </c>
       <c r="B32" t="n">
         <v>79327</v>
@@ -4530,22 +4459,26 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>363303</v>
+        <v>362310</v>
       </c>
       <c r="R32" t="n">
-        <v>6882872</v>
+        <v>6882298</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4569,27 +4502,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Granar draperade med garnlav.</t>
+          <t>Väldigt långa bålar och i granbeståndet flera draperade av garnlav.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4598,8 +4531,19 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4615,13 +4559,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170500</t>
+          <t>https://artportalen.se/Sighting/118119303</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127170642</v>
+        <v>118341001</v>
       </c>
       <c r="B33" t="n">
         <v>79327</v>
@@ -4650,7 +4594,11 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>med apothecier</t>
@@ -4659,17 +4607,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>363306</v>
+        <v>362320</v>
       </c>
       <c r="R33" t="n">
-        <v>6882880</v>
+        <v>6882282</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4693,27 +4641,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Garnlavsdraperade granar.</t>
+          <t>Granar draperade med garnlav.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4722,8 +4670,34 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4739,13 +4713,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170642</t>
+          <t>https://artportalen.se/Sighting/118341001</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127170911</v>
+        <v>127170375</v>
       </c>
       <c r="B34" t="n">
         <v>79327</v>
@@ -4775,18 +4749,22 @@
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Lövåsen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>363318</v>
+        <v>363314</v>
       </c>
       <c r="R34" t="n">
-        <v>6882898</v>
+        <v>6882815</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4818,7 +4796,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4828,12 +4806,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Draperade granar. Hotad fjällnära skog.</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4859,13 +4832,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170911</t>
+          <t>https://artportalen.se/Sighting/127170375</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127171152</v>
+        <v>127170420</v>
       </c>
       <c r="B35" t="n">
         <v>79327</v>
@@ -4895,11 +4868,7 @@
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4907,13 +4876,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>363314</v>
+        <v>363307</v>
       </c>
       <c r="R35" t="n">
-        <v>6882905</v>
+        <v>6882847</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4942,7 +4911,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4952,7 +4921,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Granar draperade med garnlav</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4978,13 +4952,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127171152</t>
+          <t>https://artportalen.se/Sighting/127170420</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127171838</v>
+        <v>127170500</v>
       </c>
       <c r="B36" t="n">
         <v>79327</v>
@@ -5014,11 +4988,7 @@
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5026,13 +4996,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>363302</v>
+        <v>363303</v>
       </c>
       <c r="R36" t="n">
-        <v>6882938</v>
+        <v>6882872</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5061,7 +5031,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5071,7 +5041,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Granar draperade med garnlav.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5097,13 +5072,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127171838</t>
+          <t>https://artportalen.se/Sighting/127170500</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127171879</v>
+        <v>127170642</v>
       </c>
       <c r="B37" t="n">
         <v>79327</v>
@@ -5133,7 +5108,11 @@
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5141,13 +5120,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>363287</v>
+        <v>363306</v>
       </c>
       <c r="R37" t="n">
-        <v>6882939</v>
+        <v>6882880</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5176,7 +5155,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5186,7 +5165,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Garnlavsdraperade granar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5212,13 +5196,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127171879</t>
+          <t>https://artportalen.se/Sighting/127170642</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127172219</v>
+        <v>127170911</v>
       </c>
       <c r="B38" t="n">
         <v>79327</v>
@@ -5256,10 +5240,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>363195</v>
+        <v>363318</v>
       </c>
       <c r="R38" t="n">
-        <v>6882944</v>
+        <v>6882898</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -5291,7 +5275,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5301,7 +5285,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Draperade granar. Hotad fjällnära skog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5327,13 +5316,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172219</t>
+          <t>https://artportalen.se/Sighting/127170911</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127172815</v>
+        <v>127171152</v>
       </c>
       <c r="B39" t="n">
         <v>79327</v>
@@ -5363,7 +5352,11 @@
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5371,10 +5364,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>363204</v>
+        <v>363314</v>
       </c>
       <c r="R39" t="n">
-        <v>6882810</v>
+        <v>6882905</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5406,7 +5399,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5416,12 +5409,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:33</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Draperade granar</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5447,13 +5435,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172815</t>
+          <t>https://artportalen.se/Sighting/127171152</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127172852</v>
+        <v>127171838</v>
       </c>
       <c r="B40" t="n">
         <v>79327</v>
@@ -5483,7 +5471,11 @@
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5491,13 +5483,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>363214</v>
+        <v>363302</v>
       </c>
       <c r="R40" t="n">
-        <v>6882814</v>
+        <v>6882938</v>
       </c>
       <c r="S40" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5526,7 +5518,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5536,12 +5528,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Garnlavsdraperade granar</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5567,13 +5554,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172852</t>
+          <t>https://artportalen.se/Sighting/127171838</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128820649</v>
+        <v>127171879</v>
       </c>
       <c r="B41" t="n">
         <v>79327</v>
@@ -5602,26 +5589,22 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>362222</v>
+        <v>363287</v>
       </c>
       <c r="R41" t="n">
-        <v>6882658</v>
+        <v>6882939</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5645,22 +5628,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5686,38 +5669,38 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128820649</t>
+          <t>https://artportalen.se/Sighting/127171879</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118118723</v>
+        <v>127172219</v>
       </c>
       <c r="B42" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5726,17 +5709,17 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>362344</v>
+        <v>363195</v>
       </c>
       <c r="R42" t="n">
-        <v>6882253</v>
+        <v>6882944</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5760,27 +5743,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Växer på stubbe av jättetall</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5789,19 +5767,8 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Barrnaturskog. Fjällnära</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5817,16 +5784,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118723</t>
+          <t>https://artportalen.se/Sighting/127172219</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121898927</v>
+        <v>127172815</v>
       </c>
       <c r="B43" t="n">
-        <v>83305</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5834,37 +5801,40 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>363129</v>
+        <v>363204</v>
       </c>
       <c r="R43" t="n">
-        <v>6882975</v>
+        <v>6882810</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5888,22 +5858,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Draperade granar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5918,73 +5893,68 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo, Cecilia Öster</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121898927</t>
+          <t>https://artportalen.se/Sighting/127172815</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118103394</v>
+        <v>127172852</v>
       </c>
       <c r="B44" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>362272</v>
+        <v>363214</v>
       </c>
       <c r="R44" t="n">
-        <v>6882099</v>
+        <v>6882814</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6008,27 +5978,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färska hacksmärken på gran Grannaturskog</t>
+          <t>Garnlavsdraperade granar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6039,16 +6009,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6064,62 +6024,61 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118103394</t>
+          <t>https://artportalen.se/Sighting/127172852</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118103560</v>
+        <v>128820649</v>
       </c>
       <c r="B45" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>362276</v>
+        <v>362222</v>
       </c>
       <c r="R45" t="n">
-        <v>6882083</v>
+        <v>6882658</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6143,27 +6102,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Färska hackmärken på gran i grannaturskog som är avverkningsanmäld.</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6174,16 +6128,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6199,16 +6143,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118103560</t>
+          <t>https://artportalen.se/Sighting/128820649</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118107736</v>
+        <v>118118723</v>
       </c>
       <c r="B46" t="n">
-        <v>57953</v>
+        <v>79946</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6216,31 +6160,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6248,10 +6187,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>362349</v>
+        <v>362344</v>
       </c>
       <c r="R46" t="n">
-        <v>6882279</v>
+        <v>6882253</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6278,27 +6217,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i naturskog.</t>
+          <t>Växer på stubbe av jättetall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6307,6 +6246,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6317,7 +6257,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Mycket gamla granar och tallar</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6334,66 +6274,54 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118107736</t>
+          <t>https://artportalen.se/Sighting/118118723</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118113015</v>
+        <v>121898927</v>
       </c>
       <c r="B47" t="n">
-        <v>57953</v>
+        <v>83305</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>362487</v>
+        <v>363129</v>
       </c>
       <c r="R47" t="n">
-        <v>6882179</v>
+        <v>6882975</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6417,27 +6345,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Hackmärken på gran i myrholme.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6452,24 +6375,24 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Andreas Öster, Maria Hindemo, Cecilia Öster</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118113015</t>
+          <t>https://artportalen.se/Sighting/121898927</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118113051</v>
+        <v>118103394</v>
       </c>
       <c r="B48" t="n">
         <v>57953</v>
@@ -6497,32 +6420,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>362482</v>
+        <v>362272</v>
       </c>
       <c r="R48" t="n">
-        <v>6882180</v>
+        <v>6882099</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6546,27 +6465,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Hackmärken gran på myrholme. Naturskog</t>
+          <t>Färska hacksmärken på gran Grannaturskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6577,6 +6496,16 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6592,13 +6521,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118113051</t>
+          <t>https://artportalen.se/Sighting/118103394</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118118450</v>
+        <v>118103560</v>
       </c>
       <c r="B49" t="n">
         <v>57953</v>
@@ -6641,10 +6570,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>362489</v>
+        <v>362276</v>
       </c>
       <c r="R49" t="n">
-        <v>6882203</v>
+        <v>6882083</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6671,27 +6600,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Hackmärken på gran. Myrholme som är avverkningsanmäld</t>
+          <t>Färska hackmärken på gran i grannaturskog som är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6710,7 +6639,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Lokalt fuktig miljö</t>
+          <t>Grannaturskog</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6727,13 +6656,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118450</t>
+          <t>https://artportalen.se/Sighting/118103560</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118118466</v>
+        <v>118107736</v>
       </c>
       <c r="B50" t="n">
         <v>57953</v>
@@ -6772,14 +6701,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>362421</v>
+        <v>362349</v>
       </c>
       <c r="R50" t="n">
-        <v>6882227</v>
+        <v>6882279</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6806,27 +6735,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Färska hackmärken på fertalet grannar på denna myrholme.</t>
+          <t>Färska hackmärken på gran i naturskog.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6845,7 +6774,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Barrnaturskog på myrholme</t>
+          <t>Barrnaturskog. Mycket gamla granar och tallar</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6862,13 +6791,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118466</t>
+          <t>https://artportalen.se/Sighting/118107736</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118118547</v>
+        <v>118113015</v>
       </c>
       <c r="B51" t="n">
         <v>57953</v>
@@ -6896,7 +6825,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
@@ -6907,14 +6840,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>362378</v>
+        <v>362487</v>
       </c>
       <c r="R51" t="n">
-        <v>6882297</v>
+        <v>6882179</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6946,7 +6879,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6956,12 +6889,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Äldre hackmärken på gammal gran i barrnaturskog.</t>
+          <t>Hackmärken på gran i myrholme.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6972,16 +6905,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6997,13 +6920,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118547</t>
+          <t>https://artportalen.se/Sighting/118113015</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118118562</v>
+        <v>118113051</v>
       </c>
       <c r="B52" t="n">
         <v>57953</v>
@@ -7031,28 +6954,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>362373</v>
+        <v>362482</v>
       </c>
       <c r="R52" t="n">
-        <v>6882312</v>
+        <v>6882180</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7081,7 +7008,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7091,12 +7018,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Hackmärken på gammal gran i barrnaturskog. Skogen är avverkningsanmäld</t>
+          <t>Hackmärken gran på myrholme. Naturskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7107,16 +7034,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Barrnaturskog. Fjällnära</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -7132,13 +7049,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118562</t>
+          <t>https://artportalen.se/Sighting/118113051</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118118603</v>
+        <v>118118450</v>
       </c>
       <c r="B53" t="n">
         <v>57953</v>
@@ -7181,10 +7098,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>362381</v>
+        <v>362489</v>
       </c>
       <c r="R53" t="n">
-        <v>6882250</v>
+        <v>6882203</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -7216,7 +7133,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7226,12 +7143,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gammal gran i barrnaturskog som avverkningsanmäld.</t>
+          <t>Hackmärken på gran. Myrholme som är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7250,7 +7167,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog. Lokalt fuktig miljö</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7267,13 +7184,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118603</t>
+          <t>https://artportalen.se/Sighting/118118450</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118118863</v>
+        <v>118118466</v>
       </c>
       <c r="B54" t="n">
         <v>57953</v>
@@ -7312,14 +7229,14 @@
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>362327</v>
+        <v>362421</v>
       </c>
       <c r="R54" t="n">
-        <v>6882265</v>
+        <v>6882227</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -7351,7 +7268,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7361,12 +7278,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i barrnaturskog som är avverkningsanmäld</t>
+          <t>Färska hackmärken på fertalet grannar på denna myrholme.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7385,7 +7302,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog på myrholme</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7402,13 +7319,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118863</t>
+          <t>https://artportalen.se/Sighting/118118466</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118118905</v>
+        <v>118118547</v>
       </c>
       <c r="B55" t="n">
         <v>57953</v>
@@ -7451,10 +7368,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>362338</v>
+        <v>362378</v>
       </c>
       <c r="R55" t="n">
-        <v>6882298</v>
+        <v>6882297</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7486,7 +7403,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7496,12 +7413,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Hackmärken på gran i barrnaturskog</t>
+          <t>Äldre hackmärken på gammal gran i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7520,7 +7437,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7537,13 +7454,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118905</t>
+          <t>https://artportalen.se/Sighting/118118547</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118119133</v>
+        <v>118118562</v>
       </c>
       <c r="B56" t="n">
         <v>57953</v>
@@ -7586,10 +7503,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>362371</v>
+        <v>362373</v>
       </c>
       <c r="R56" t="n">
-        <v>6882362</v>
+        <v>6882312</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7621,7 +7538,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7631,12 +7548,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Färska hackmärken på grov gammal gran. i barrnaturskog som är hotad av avverkning.</t>
+          <t>Hackmärken på gammal gran i barrnaturskog. Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7672,13 +7589,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119133</t>
+          <t>https://artportalen.se/Sighting/118118562</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118119170</v>
+        <v>118118603</v>
       </c>
       <c r="B57" t="n">
         <v>57953</v>
@@ -7717,14 +7634,14 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>362327</v>
+        <v>362381</v>
       </c>
       <c r="R57" t="n">
-        <v>6882360</v>
+        <v>6882250</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7756,7 +7673,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7766,12 +7683,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Färska hackmärken på grov gammal gran i barrnaturskog. Avverkningsanmäld skog.</t>
+          <t>Färska hackmärken på gammal gran i barrnaturskog som avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7790,7 +7707,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Barrnatursk. Fjällnära</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7807,13 +7724,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119170</t>
+          <t>https://artportalen.se/Sighting/118118603</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118119483</v>
+        <v>118118863</v>
       </c>
       <c r="B58" t="n">
         <v>57953</v>
@@ -7856,10 +7773,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>362284</v>
+        <v>362327</v>
       </c>
       <c r="R58" t="n">
-        <v>6882318</v>
+        <v>6882265</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7891,7 +7808,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7901,12 +7818,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i barrnaturskog.</t>
+          <t>Färska hackmärken på gran i barrnaturskog som är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7942,13 +7859,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119483</t>
+          <t>https://artportalen.se/Sighting/118118863</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118119653</v>
+        <v>118118905</v>
       </c>
       <c r="B59" t="n">
         <v>57953</v>
@@ -7991,10 +7908,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>362269</v>
+        <v>362338</v>
       </c>
       <c r="R59" t="n">
-        <v>6882324</v>
+        <v>6882298</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -8026,7 +7943,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8036,12 +7953,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Hackmärken på grov gran intill skidspår som går genom barrnaturskogen. Avverkningsanmäld skog.</t>
+          <t>Hackmärken på gran i barrnaturskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8077,13 +7994,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119653</t>
+          <t>https://artportalen.se/Sighting/118118905</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118119701</v>
+        <v>118119133</v>
       </c>
       <c r="B60" t="n">
         <v>57953</v>
@@ -8126,10 +8043,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>362279</v>
+        <v>362371</v>
       </c>
       <c r="R60" t="n">
-        <v>6882363</v>
+        <v>6882362</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -8161,7 +8078,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8171,12 +8088,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i barrnaturskog som hotas av avverkning</t>
+          <t>Färska hackmärken på grov gammal gran. i barrnaturskog som är hotad av avverkning.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8212,13 +8129,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119701</t>
+          <t>https://artportalen.se/Sighting/118119133</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118119770</v>
+        <v>118119170</v>
       </c>
       <c r="B61" t="n">
         <v>57953</v>
@@ -8261,10 +8178,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>362240</v>
+        <v>362327</v>
       </c>
       <c r="R61" t="n">
-        <v>6882345</v>
+        <v>6882360</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -8296,7 +8213,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8306,12 +8223,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gammal gran i barrnaturskog.</t>
+          <t>Färska hackmärken på grov gammal gran i barrnaturskog. Avverkningsanmäld skog.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8330,7 +8247,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnatursk. Fjällnära</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8347,13 +8264,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119770</t>
+          <t>https://artportalen.se/Sighting/118119170</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118119872</v>
+        <v>118119483</v>
       </c>
       <c r="B62" t="n">
         <v>57953</v>
@@ -8386,7 +8303,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8396,10 +8313,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>362230</v>
+        <v>362284</v>
       </c>
       <c r="R62" t="n">
-        <v>6882332</v>
+        <v>6882318</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -8431,7 +8348,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8441,7 +8358,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på gran i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8477,13 +8399,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119872</t>
+          <t>https://artportalen.se/Sighting/118119483</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118120074</v>
+        <v>118119653</v>
       </c>
       <c r="B63" t="n">
         <v>57953</v>
@@ -8516,7 +8438,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -8526,10 +8448,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>362243</v>
+        <v>362269</v>
       </c>
       <c r="R63" t="n">
-        <v>6882254</v>
+        <v>6882324</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -8561,7 +8483,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8571,12 +8493,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Färska och äldre hackmärken på gammal gran i barrnatuskog.</t>
+          <t>Hackmärken på grov gran intill skidspår som går genom barrnaturskogen. Avverkningsanmäld skog.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8612,13 +8534,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120074</t>
+          <t>https://artportalen.se/Sighting/118119653</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118120164</v>
+        <v>118119701</v>
       </c>
       <c r="B64" t="n">
         <v>57953</v>
@@ -8661,10 +8583,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>362252</v>
+        <v>362279</v>
       </c>
       <c r="R64" t="n">
-        <v>6882248</v>
+        <v>6882363</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8696,7 +8618,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8706,12 +8628,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran in barrnaturskog.</t>
+          <t>Färska hackmärken på gran i barrnaturskog som hotas av avverkning</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8747,13 +8669,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120164</t>
+          <t>https://artportalen.se/Sighting/118119701</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118120248</v>
+        <v>118119770</v>
       </c>
       <c r="B65" t="n">
         <v>57953</v>
@@ -8796,10 +8718,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>362267</v>
+        <v>362240</v>
       </c>
       <c r="R65" t="n">
-        <v>6882224</v>
+        <v>6882345</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8831,7 +8753,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8841,12 +8763,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Färska hackmärken i ett granbestånd. I avverkningsanmält skogsområe</t>
+          <t>Färska hackmärken på gammal gran i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8882,13 +8804,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120248</t>
+          <t>https://artportalen.se/Sighting/118119770</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118120388</v>
+        <v>118119872</v>
       </c>
       <c r="B66" t="n">
         <v>57953</v>
@@ -8931,10 +8853,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>362196</v>
+        <v>362230</v>
       </c>
       <c r="R66" t="n">
-        <v>6882301</v>
+        <v>6882332</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8966,7 +8888,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8976,7 +8898,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8995,7 +8917,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9012,13 +8934,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120388</t>
+          <t>https://artportalen.se/Sighting/118119872</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118120447</v>
+        <v>118120074</v>
       </c>
       <c r="B67" t="n">
         <v>57953</v>
@@ -9061,10 +8983,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>362200</v>
+        <v>362243</v>
       </c>
       <c r="R67" t="n">
-        <v>6882350</v>
+        <v>6882254</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -9096,7 +9018,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9106,12 +9028,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Färska och äldre hackmärken på grov gran i barrnaturskog.</t>
+          <t>Färska och äldre hackmärken på gammal gran i barrnatuskog.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9147,13 +9069,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120447</t>
+          <t>https://artportalen.se/Sighting/118120074</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118120506</v>
+        <v>118120164</v>
       </c>
       <c r="B68" t="n">
         <v>57953</v>
@@ -9186,7 +9108,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -9196,10 +9118,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>362168</v>
+        <v>362252</v>
       </c>
       <c r="R68" t="n">
-        <v>6882359</v>
+        <v>6882248</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -9231,7 +9153,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9241,12 +9163,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Äldre hackmärken på gammal gran med garnlav. I avverkningsanmäld barrnaturskog</t>
+          <t>Färska hackmärken på gran in barrnaturskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9265,7 +9187,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Barrnaturskog.</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9282,13 +9204,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120506</t>
+          <t>https://artportalen.se/Sighting/118120164</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118122341</v>
+        <v>118120248</v>
       </c>
       <c r="B69" t="n">
         <v>57953</v>
@@ -9327,14 +9249,14 @@
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>362247</v>
+        <v>362267</v>
       </c>
       <c r="R69" t="n">
-        <v>6882178</v>
+        <v>6882224</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -9361,27 +9283,27 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Hackmärken på tall i barrnaturskog.</t>
+          <t>Färska hackmärken i ett granbestånd. I avverkningsanmält skogsområe</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9400,7 +9322,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9417,13 +9339,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122341</t>
+          <t>https://artportalen.se/Sighting/118120248</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118122435</v>
+        <v>118120388</v>
       </c>
       <c r="B70" t="n">
         <v>57953</v>
@@ -9456,20 +9378,20 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>362276</v>
+        <v>362196</v>
       </c>
       <c r="R70" t="n">
-        <v>6882136</v>
+        <v>6882301</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9496,27 +9418,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska hackmärken på gran i barrnaturskog</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9552,13 +9469,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122435</t>
+          <t>https://artportalen.se/Sighting/118120388</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118122458</v>
+        <v>118120447</v>
       </c>
       <c r="B71" t="n">
         <v>57953</v>
@@ -9597,14 +9514,14 @@
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>362281</v>
+        <v>362200</v>
       </c>
       <c r="R71" t="n">
-        <v>6882135</v>
+        <v>6882350</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9631,27 +9548,27 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i fin barrnaturskog som är avverkningsanmäld</t>
+          <t>Färska och äldre hackmärken på grov gran i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9670,7 +9587,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9687,13 +9604,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122458</t>
+          <t>https://artportalen.se/Sighting/118120447</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118122497</v>
+        <v>118120506</v>
       </c>
       <c r="B72" t="n">
         <v>57953</v>
@@ -9726,20 +9643,20 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>362283</v>
+        <v>362168</v>
       </c>
       <c r="R72" t="n">
-        <v>6882105</v>
+        <v>6882359</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9766,27 +9683,27 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i avverkningsanmäld barrnaturskog</t>
+          <t>Äldre hackmärken på gammal gran med garnlav. I avverkningsanmäld barrnaturskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9805,7 +9722,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Barrnaturskog.</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9822,13 +9739,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122497</t>
+          <t>https://artportalen.se/Sighting/118120506</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118340481</v>
+        <v>118122341</v>
       </c>
       <c r="B73" t="n">
         <v>57953</v>
@@ -9871,10 +9788,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>362275</v>
+        <v>362247</v>
       </c>
       <c r="R73" t="n">
-        <v>6882133</v>
+        <v>6882178</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9901,27 +9818,27 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i fjällnära skog.</t>
+          <t>Hackmärken på tall i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9940,7 +9857,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9957,13 +9874,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340481</t>
+          <t>https://artportalen.se/Sighting/118122341</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118340595</v>
+        <v>118122435</v>
       </c>
       <c r="B74" t="n">
         <v>57953</v>
@@ -10006,10 +9923,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>362281</v>
+        <v>362276</v>
       </c>
       <c r="R74" t="n">
-        <v>6882106</v>
+        <v>6882136</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -10036,27 +9953,27 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>färska hackmärken på gatan. Fjällnära skog</t>
+          <t>Färska hackmärken på gran i barrnaturskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10075,7 +9992,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10092,13 +10009,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340595</t>
+          <t>https://artportalen.se/Sighting/118122435</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118340691</v>
+        <v>118122458</v>
       </c>
       <c r="B75" t="n">
         <v>57953</v>
@@ -10141,13 +10058,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>362270</v>
+        <v>362281</v>
       </c>
       <c r="R75" t="n">
-        <v>6882100</v>
+        <v>6882135</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10171,27 +10088,27 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i fjällnära skog</t>
+          <t>Färska hackmärken på gran i fin barrnaturskog som är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10210,7 +10127,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10227,13 +10144,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340691</t>
+          <t>https://artportalen.se/Sighting/118122458</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118340748</v>
+        <v>118122497</v>
       </c>
       <c r="B76" t="n">
         <v>57953</v>
@@ -10276,10 +10193,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>362272</v>
+        <v>362283</v>
       </c>
       <c r="R76" t="n">
-        <v>6882086</v>
+        <v>6882105</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -10306,27 +10223,27 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>färska hackmnärken på gran i naturskog. Fjällnära</t>
+          <t>Färska hackmärken på gran i avverkningsanmäld barrnaturskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10345,7 +10262,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10362,13 +10279,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340748</t>
+          <t>https://artportalen.se/Sighting/118122497</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118340920</v>
+        <v>118340481</v>
       </c>
       <c r="B77" t="n">
         <v>57953</v>
@@ -10407,14 +10324,14 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>362284</v>
+        <v>362275</v>
       </c>
       <c r="R77" t="n">
-        <v>6882361</v>
+        <v>6882133</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -10461,7 +10378,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Färska och äldre hackmärken. Skogen är avverkningsanmäld. Gran med hackmärken inom anmälan. Se bild</t>
+          <t>Färska hackmärken på gran i fjällnära skog.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10480,7 +10397,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10497,13 +10414,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340920</t>
+          <t>https://artportalen.se/Sighting/118340481</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121206319</v>
+        <v>118340595</v>
       </c>
       <c r="B78" t="n">
         <v>57953</v>
@@ -10532,19 +10449,27 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>363246</v>
+        <v>362281</v>
       </c>
       <c r="R78" t="n">
-        <v>6883004</v>
+        <v>6882106</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10568,22 +10493,27 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>färska hackmärken på gatan. Fjällnära skog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10594,28 +10524,38 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121206319</t>
+          <t>https://artportalen.se/Sighting/118340595</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127170971</v>
+        <v>118340691</v>
       </c>
       <c r="B79" t="n">
         <v>57953</v>
@@ -10643,32 +10583,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>363315</v>
+        <v>362270</v>
       </c>
       <c r="R79" t="n">
-        <v>6882898</v>
+        <v>6882100</v>
       </c>
       <c r="S79" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10692,22 +10628,27 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på gran i fjällnära skog</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10718,6 +10659,16 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -10733,13 +10684,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170971</t>
+          <t>https://artportalen.se/Sighting/118340691</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127172142</v>
+        <v>118340748</v>
       </c>
       <c r="B80" t="n">
         <v>57953</v>
@@ -10767,11 +10718,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
@@ -10782,17 +10729,17 @@
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>363196</v>
+        <v>362272</v>
       </c>
       <c r="R80" t="n">
-        <v>6882950</v>
+        <v>6882086</v>
       </c>
       <c r="S80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10816,27 +10763,27 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Färska och äldre hackmärken.</t>
+          <t>färska hackmnärken på gran i naturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10847,6 +10794,16 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -10862,13 +10819,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172142</t>
+          <t>https://artportalen.se/Sighting/118340748</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127172737</v>
+        <v>118340920</v>
       </c>
       <c r="B81" t="n">
         <v>57953</v>
@@ -10896,32 +10853,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>363143</v>
+        <v>362284</v>
       </c>
       <c r="R81" t="n">
-        <v>6882797</v>
+        <v>6882361</v>
       </c>
       <c r="S81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10945,22 +10898,27 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken. Skogen är avverkningsanmäld. Gran med hackmärken inom anmälan. Se bild</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10971,6 +10929,16 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>barrnaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -10986,13 +10954,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172737</t>
+          <t>https://artportalen.se/Sighting/118340920</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127172795</v>
+        <v>121206319</v>
       </c>
       <c r="B82" t="n">
         <v>57953</v>
@@ -11020,32 +10988,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>363188</v>
+        <v>363246</v>
       </c>
       <c r="R82" t="n">
-        <v>6882809</v>
+        <v>6883004</v>
       </c>
       <c r="S82" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -11069,27 +11025,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackmärken</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11104,24 +11055,24 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172795</t>
+          <t>https://artportalen.se/Sighting/121206319</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127172899</v>
+        <v>127170971</v>
       </c>
       <c r="B83" t="n">
         <v>57953</v>
@@ -11168,13 +11119,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>363234</v>
+        <v>363315</v>
       </c>
       <c r="R83" t="n">
-        <v>6882800</v>
+        <v>6882898</v>
       </c>
       <c r="S83" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -11203,7 +11154,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11213,7 +11164,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11239,13 +11190,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172899</t>
+          <t>https://artportalen.se/Sighting/127170971</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127315676</v>
+        <v>127172142</v>
       </c>
       <c r="B84" t="n">
         <v>57953</v>
@@ -11275,42 +11226,30 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>363122</v>
+        <v>363196</v>
       </c>
       <c r="R84" t="n">
-        <v>6882946</v>
+        <v>6882950</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11334,22 +11273,27 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11364,24 +11308,24 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127315676</t>
+          <t>https://artportalen.se/Sighting/127172142</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128822185</v>
+        <v>127172737</v>
       </c>
       <c r="B85" t="n">
         <v>57953</v>
@@ -11421,21 +11365,17 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>362326</v>
+        <v>363143</v>
       </c>
       <c r="R85" t="n">
-        <v>6882768</v>
+        <v>6882797</v>
       </c>
       <c r="S85" t="n">
         <v>4</v>
@@ -11462,22 +11402,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11503,13 +11443,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128822185</t>
+          <t>https://artportalen.se/Sighting/127172737</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128822490</v>
+        <v>127172795</v>
       </c>
       <c r="B86" t="n">
         <v>57953</v>
@@ -11546,27 +11486,23 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>362260</v>
+        <v>363188</v>
       </c>
       <c r="R86" t="n">
-        <v>6882421</v>
+        <v>6882809</v>
       </c>
       <c r="S86" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -11590,22 +11526,27 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11631,13 +11572,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128822490</t>
+          <t>https://artportalen.se/Sighting/127172795</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128822499</v>
+        <v>127172899</v>
       </c>
       <c r="B87" t="n">
         <v>57953</v>
@@ -11680,17 +11621,17 @@
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>362273</v>
+        <v>363234</v>
       </c>
       <c r="R87" t="n">
-        <v>6882421</v>
+        <v>6882800</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11714,22 +11655,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11755,63 +11696,78 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128822499</t>
+          <t>https://artportalen.se/Sighting/127172899</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118122325</v>
+        <v>127315676</v>
       </c>
       <c r="B88" t="n">
-        <v>5179</v>
+        <v>57953</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>362234</v>
+        <v>363122</v>
       </c>
       <c r="R88" t="n">
-        <v>6882185</v>
+        <v>6882946</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11835,27 +11791,22 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>På torrgran vid myrknat intill barrnaturskog</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11864,44 +11815,33 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>Myrmark intill barrnaturskog</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Marcus Hansson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Marcus Hansson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122325</t>
+          <t>https://artportalen.se/Sighting/127315676</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127315773</v>
+        <v>128822185</v>
       </c>
       <c r="B89" t="n">
-        <v>58057</v>
+        <v>57953</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11909,16 +11849,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -11928,17 +11868,14 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -11948,17 +11885,17 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>363120</v>
+        <v>362326</v>
       </c>
       <c r="R89" t="n">
-        <v>6882934</v>
+        <v>6882768</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11982,22 +11919,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -12012,27 +11949,27 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127315773</t>
+          <t>https://artportalen.se/Sighting/128822185</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128820534</v>
+        <v>128822490</v>
       </c>
       <c r="B90" t="n">
-        <v>58057</v>
+        <v>57953</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12040,16 +11977,16 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -12066,20 +12003,24 @@
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>362267</v>
+        <v>362260</v>
       </c>
       <c r="R90" t="n">
-        <v>6882595</v>
+        <v>6882421</v>
       </c>
       <c r="S90" t="n">
         <v>4</v>
@@ -12111,7 +12052,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -12121,7 +12062,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -12147,55 +12088,63 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128820534</t>
+          <t>https://artportalen.se/Sighting/128822490</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118122289</v>
+        <v>128822499</v>
       </c>
       <c r="B91" t="n">
-        <v>99035</v>
+        <v>57953</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>362232</v>
+        <v>362273</v>
       </c>
       <c r="R91" t="n">
-        <v>6882193</v>
+        <v>6882421</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -12222,22 +12171,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12246,19 +12195,8 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AH91" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>Barrnaturskog vid myrkant</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -12274,16 +12212,16 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122289</t>
+          <t>https://artportalen.se/Sighting/128822499</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118118517</v>
+        <v>118122325</v>
       </c>
       <c r="B92" t="n">
-        <v>97983</v>
+        <v>5179</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12291,27 +12229,32 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -12319,10 +12262,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>362380</v>
+        <v>362234</v>
       </c>
       <c r="R92" t="n">
-        <v>6882294</v>
+        <v>6882185</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -12349,27 +12292,27 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Växer under gamla granar i barrnaturskog. Fuktig miljö.</t>
+          <t>På torrgran vid myrknat intill barrnaturskog</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12389,7 +12332,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Myrmark intill barrnaturskog</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12406,58 +12349,73 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118517</t>
+          <t>https://artportalen.se/Sighting/118122325</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118118821</v>
+        <v>127315773</v>
       </c>
       <c r="B93" t="n">
-        <v>97983</v>
+        <v>58057</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221945</v>
+        <v>103031</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>362339</v>
+        <v>363120</v>
       </c>
       <c r="R93" t="n">
-        <v>6882268</v>
+        <v>6882934</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -12481,27 +12439,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Växer på en stor yta under gamla granar i barrnaturskog</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12510,86 +12463,83 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>Barrnaturskog. Fjällnära</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Marcus Hansson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Marcus Hansson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118821</t>
+          <t>https://artportalen.se/Sighting/127315773</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118119084</v>
+        <v>128820534</v>
       </c>
       <c r="B94" t="n">
-        <v>97983</v>
+        <v>58057</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221945</v>
+        <v>103031</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>362369</v>
+        <v>362267</v>
       </c>
       <c r="R94" t="n">
-        <v>6882345</v>
+        <v>6882595</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12613,22 +12563,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12637,19 +12587,8 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>Grannaturskog. Fjällnära</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -12665,16 +12604,16 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119084</t>
+          <t>https://artportalen.se/Sighting/128820534</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127171558</v>
+        <v>118122289</v>
       </c>
       <c r="B95" t="n">
-        <v>97983</v>
+        <v>99035</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12682,21 +12621,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12706,17 +12645,17 @@
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>363325</v>
+        <v>362232</v>
       </c>
       <c r="R95" t="n">
-        <v>6882909</v>
+        <v>6882193</v>
       </c>
       <c r="S95" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12740,22 +12679,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12764,8 +12703,19 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>Barrnaturskog vid myrkant</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -12781,13 +12731,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127171558</t>
+          <t>https://artportalen.se/Sighting/118122289</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127172203</v>
+        <v>118118517</v>
       </c>
       <c r="B96" t="n">
         <v>97983</v>
@@ -12822,17 +12772,17 @@
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>363195</v>
+        <v>362380</v>
       </c>
       <c r="R96" t="n">
-        <v>6882944</v>
+        <v>6882294</v>
       </c>
       <c r="S96" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12856,22 +12806,27 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Växer under gamla granar i barrnaturskog. Fuktig miljö.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12880,8 +12835,19 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -12897,13 +12863,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172203</t>
+          <t>https://artportalen.se/Sighting/118118517</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127172331</v>
+        <v>118118821</v>
       </c>
       <c r="B97" t="n">
         <v>97983</v>
@@ -12938,17 +12904,17 @@
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>363170</v>
+        <v>362339</v>
       </c>
       <c r="R97" t="n">
-        <v>6882973</v>
+        <v>6882268</v>
       </c>
       <c r="S97" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12972,22 +12938,27 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Växer på en stor yta under gamla granar i barrnaturskog</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12996,8 +12967,19 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -13013,13 +12995,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172331</t>
+          <t>https://artportalen.se/Sighting/118118821</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128820515</v>
+        <v>118119084</v>
       </c>
       <c r="B98" t="n">
         <v>97983</v>
@@ -13051,24 +13033,20 @@
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>362287</v>
+        <v>362369</v>
       </c>
       <c r="R98" t="n">
-        <v>6882523</v>
+        <v>6882345</v>
       </c>
       <c r="S98" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -13092,22 +13070,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13116,8 +13094,19 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>Grannaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -13132,6 +13121,474 @@
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118119084</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>127171558</v>
+      </c>
+      <c r="B99" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Kerstibygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>363325</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6882909</v>
+      </c>
+      <c r="S99" t="n">
+        <v>4</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171558</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>127172203</v>
+      </c>
+      <c r="B100" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Kerstibygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>363195</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6882944</v>
+      </c>
+      <c r="S100" t="n">
+        <v>4</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172203</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>127172331</v>
+      </c>
+      <c r="B101" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Kerstibygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>363170</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6882973</v>
+      </c>
+      <c r="S101" t="n">
+        <v>4</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172331</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>128820515</v>
+      </c>
+      <c r="B102" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Kokällmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>362287</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6882523</v>
+      </c>
+      <c r="S102" t="n">
+        <v>4</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128820515</t>
         </is>
@@ -13236,6 +13693,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135621906</v>
       </c>
       <c r="B3" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>135622151</v>
       </c>
       <c r="B4" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>135621791</v>
       </c>
       <c r="B12" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>135621801</v>
       </c>
       <c r="B15" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ98"/>
+  <dimension ref="A1:AZ102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118103854</v>
+        <v>135621906</v>
       </c>
       <c r="B3" t="n">
-        <v>79406</v>
+        <v>92319</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,40 +803,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>362321</v>
+        <v>362658</v>
       </c>
       <c r="R3" t="n">
-        <v>6882091</v>
+        <v>6882750</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,27 +866,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Växer på gran i naturskog.</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,59 +890,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118103854</t>
+          <t>https://artportalen.se/Sighting/135621906</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118113514</v>
+        <v>135622151</v>
       </c>
       <c r="B4" t="n">
-        <v>79406</v>
+        <v>92319</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,40 +924,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>362466</v>
+        <v>362625</v>
       </c>
       <c r="R4" t="n">
-        <v>6882217</v>
+        <v>6882754</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,27 +978,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:56</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På björk vid myrholme. Naturskog</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,24 +1008,24 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118113514</t>
+          <t>https://artportalen.se/Sighting/135622151</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127170947</v>
+        <v>118103854</v>
       </c>
       <c r="B5" t="n">
         <v>79406</v>
@@ -1092,17 +1059,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363316</v>
+        <v>362321</v>
       </c>
       <c r="R5" t="n">
-        <v>6882898</v>
+        <v>6882091</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1126,22 +1093,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Växer på gran i naturskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,8 +1122,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1167,13 +1165,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170947</t>
+          <t>https://artportalen.se/Sighting/118103854</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127172322</v>
+        <v>118113514</v>
       </c>
       <c r="B6" t="n">
         <v>79406</v>
@@ -1207,17 +1205,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>363173</v>
+        <v>362466</v>
       </c>
       <c r="R6" t="n">
-        <v>6882970</v>
+        <v>6882217</v>
       </c>
       <c r="S6" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1241,22 +1239,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På björk vid myrholme. Naturskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,13 +1285,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172322</t>
+          <t>https://artportalen.se/Sighting/118113514</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127172714</v>
+        <v>127170947</v>
       </c>
       <c r="B7" t="n">
         <v>79406</v>
@@ -1326,10 +1329,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>363141</v>
+        <v>363316</v>
       </c>
       <c r="R7" t="n">
-        <v>6882796</v>
+        <v>6882898</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1361,7 +1364,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1371,7 +1374,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1397,13 +1400,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172714</t>
+          <t>https://artportalen.se/Sighting/127170947</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128820694</v>
+        <v>127172322</v>
       </c>
       <c r="B8" t="n">
         <v>79406</v>
@@ -1437,17 +1440,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>362220</v>
+        <v>363173</v>
       </c>
       <c r="R8" t="n">
-        <v>6882659</v>
+        <v>6882970</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1471,22 +1474,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,13 +1515,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128820694</t>
+          <t>https://artportalen.se/Sighting/127172322</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130470732</v>
+        <v>127172714</v>
       </c>
       <c r="B9" t="n">
         <v>79406</v>
@@ -1547,19 +1550,22 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lövåsen, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>363300</v>
+        <v>363141</v>
       </c>
       <c r="R9" t="n">
-        <v>6882818</v>
+        <v>6882796</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1583,22 +1589,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,65 +1619,68 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Anders Björkén, Maria Hindemo</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130470732</t>
+          <t>https://artportalen.se/Sighting/127172714</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130470733</v>
+        <v>128820694</v>
       </c>
       <c r="B10" t="n">
-        <v>91923</v>
+        <v>79406</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lövåsen, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>363275</v>
+        <v>362220</v>
       </c>
       <c r="R10" t="n">
-        <v>6882937</v>
+        <v>6882659</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1695,22 +1704,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,27 +1734,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Anders Björkén, Maria Hindemo</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130470733</t>
+          <t>https://artportalen.se/Sighting/128820694</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121206216</v>
+        <v>130470732</v>
       </c>
       <c r="B11" t="n">
-        <v>92369</v>
+        <v>79406</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,37 +1762,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Lövåsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>363227</v>
+        <v>363300</v>
       </c>
       <c r="R11" t="n">
-        <v>6882956</v>
+        <v>6882818</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1807,22 +1816,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,27 +1846,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Cajsa Björkén, Anders Björkén, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121206216</t>
+          <t>https://artportalen.se/Sighting/130470732</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121206277</v>
+        <v>135621791</v>
       </c>
       <c r="B12" t="n">
-        <v>83173</v>
+        <v>92048</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,21 +1874,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1889,13 +1898,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>363227</v>
+        <v>362646</v>
       </c>
       <c r="R12" t="n">
-        <v>6882956</v>
+        <v>6882779</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1919,22 +1928,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1949,27 +1958,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121206277</t>
+          <t>https://artportalen.se/Sighting/135621791</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118112482</v>
+        <v>130470733</v>
       </c>
       <c r="B13" t="n">
-        <v>92083</v>
+        <v>91923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,44 +1986,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1503</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Dlr</t>
+          <t>Lövåsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>362476</v>
+        <v>363275</v>
       </c>
       <c r="R13" t="n">
-        <v>6882192</v>
+        <v>6882937</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2038,27 +2040,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Växer under gammal gren från jättetall på myrholme. Skogen är avverkningsanmäld</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,34 +2064,33 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Cajsa Björkén, Anders Björkén, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118112482</t>
+          <t>https://artportalen.se/Sighting/130470733</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118340526</v>
+        <v>121206216</v>
       </c>
       <c r="B14" t="n">
-        <v>91831</v>
+        <v>92369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2102,44 +2098,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3242</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>362269</v>
+        <v>363227</v>
       </c>
       <c r="R14" t="n">
-        <v>6882132</v>
+        <v>6882956</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2163,27 +2152,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Växer på undersida av tallgren från gammal tall. Fjällnära skog.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,59 +2176,33 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Barrnaturskog. Fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340526</t>
+          <t>https://artportalen.se/Sighting/121206216</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121206393</v>
+        <v>135621801</v>
       </c>
       <c r="B15" t="n">
-        <v>91831</v>
+        <v>92480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,21 +2210,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3242</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2276,13 +2234,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>363237</v>
+        <v>362649</v>
       </c>
       <c r="R15" t="n">
-        <v>6883017</v>
+        <v>6882777</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2306,22 +2264,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2332,73 +2290,53 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Dead branch  # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121206393</t>
+          <t>https://artportalen.se/Sighting/135621801</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121206160</v>
+        <v>121206277</v>
       </c>
       <c r="B16" t="n">
-        <v>92632</v>
+        <v>83173</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2408,10 +2346,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>363153</v>
+        <v>363227</v>
       </c>
       <c r="R16" t="n">
-        <v>6882853</v>
+        <v>6882956</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2443,7 +2381,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2453,7 +2391,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2464,26 +2402,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2499,16 +2417,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121206160</t>
+          <t>https://artportalen.se/Sighting/121206277</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110444488</v>
+        <v>118112482</v>
       </c>
       <c r="B17" t="n">
-        <v>79327</v>
+        <v>92083</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2516,44 +2434,44 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lövåsen, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>363277</v>
+        <v>362476</v>
       </c>
       <c r="R17" t="n">
-        <v>6882948</v>
+        <v>6882192</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2577,27 +2495,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ymnig förekomst av garnlav i fin grannaturskog. Granar draperade av laven. På grov gran garnlav med soral.</t>
+          <t>Växer under gammal gren från jättetall på myrholme. Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2610,31 +2528,6 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
@@ -2649,61 +2542,61 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110444488</t>
+          <t>https://artportalen.se/Sighting/118112482</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>110513997</v>
+        <v>118340526</v>
       </c>
       <c r="B18" t="n">
-        <v>79327</v>
+        <v>91831</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lövåsen , Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>363288</v>
+        <v>362269</v>
       </c>
       <c r="R18" t="n">
-        <v>6882833</v>
+        <v>6882132</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2727,22 +2620,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Växer på undersida av tallgren från gammal tall. Fjällnära skog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2751,8 +2649,34 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2768,61 +2692,54 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110513997</t>
+          <t>https://artportalen.se/Sighting/118340526</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>110514177</v>
+        <v>121206393</v>
       </c>
       <c r="B19" t="n">
-        <v>79327</v>
+        <v>91831</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lövåsen , Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>363305</v>
+        <v>363237</v>
       </c>
       <c r="R19" t="n">
-        <v>6882833</v>
+        <v>6883017</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2846,22 +2763,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2872,76 +2789,89 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Dead branch  # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110514177</t>
+          <t>https://artportalen.se/Sighting/121206393</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>110514236</v>
+        <v>121206160</v>
       </c>
       <c r="B20" t="n">
-        <v>79327</v>
+        <v>92632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lövåsen , Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>363313</v>
+        <v>363153</v>
       </c>
       <c r="R20" t="n">
-        <v>6882881</v>
+        <v>6882853</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2965,22 +2895,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2991,28 +2921,48 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110514236</t>
+          <t>https://artportalen.se/Sighting/121206160</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118103637</v>
+        <v>110444488</v>
       </c>
       <c r="B21" t="n">
         <v>79327</v>
@@ -3042,21 +2992,25 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Lövåsen, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>362276</v>
+        <v>363277</v>
       </c>
       <c r="R21" t="n">
-        <v>6882072</v>
+        <v>6882948</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3080,27 +3034,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Växer på gran i naturskog.</t>
+          <t>Ymnig förekomst av garnlav i fin grannaturskog. Granar draperade av laven. På grov gran garnlav med soral.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3152,13 +3106,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118103637</t>
+          <t>https://artportalen.se/Sighting/110444488</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118103682</v>
+        <v>110513997</v>
       </c>
       <c r="B22" t="n">
         <v>79327</v>
@@ -3187,26 +3141,26 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Lövåsen , Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>362257</v>
+        <v>363288</v>
       </c>
       <c r="R22" t="n">
-        <v>6882084</v>
+        <v>6882833</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3230,27 +3184,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Växer på gammal gran i avverkningsanmäld skog.</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3259,34 +3208,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3302,13 +3225,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118103682</t>
+          <t>https://artportalen.se/Sighting/110513997</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118103868</v>
+        <v>110514177</v>
       </c>
       <c r="B23" t="n">
         <v>79327</v>
@@ -3338,18 +3261,22 @@
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Lövåsen , Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>362279</v>
+        <v>363305</v>
       </c>
       <c r="R23" t="n">
-        <v>6882106</v>
+        <v>6882833</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3376,22 +3303,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3400,19 +3327,8 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3428,13 +3344,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118103868</t>
+          <t>https://artportalen.se/Sighting/110514177</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118108025</v>
+        <v>110514236</v>
       </c>
       <c r="B24" t="n">
         <v>79327</v>
@@ -3463,23 +3379,23 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Lövåsen , Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>362343</v>
+        <v>363313</v>
       </c>
       <c r="R24" t="n">
-        <v>6882273</v>
+        <v>6882881</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3506,22 +3422,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3530,19 +3446,8 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3558,13 +3463,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118108025</t>
+          <t>https://artportalen.se/Sighting/110514236</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118108207</v>
+        <v>118103637</v>
       </c>
       <c r="B25" t="n">
         <v>79327</v>
@@ -3593,11 +3498,7 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3606,10 +3507,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>362326</v>
+        <v>362276</v>
       </c>
       <c r="R25" t="n">
-        <v>6882154</v>
+        <v>6882072</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3641,7 +3542,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3651,12 +3552,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Naturskog med riklig förekomst av garnlav</t>
+          <t>Växer på gran i naturskog.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3676,7 +3577,22 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Gammelgranskog</t>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3693,13 +3609,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118108207</t>
+          <t>https://artportalen.se/Sighting/118103637</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118112682</v>
+        <v>118103682</v>
       </c>
       <c r="B26" t="n">
         <v>79327</v>
@@ -3737,14 +3653,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>362476</v>
+        <v>362257</v>
       </c>
       <c r="R26" t="n">
-        <v>6882192</v>
+        <v>6882084</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3771,27 +3687,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Växer i granbestånd på myrholme</t>
+          <t>Växer på gammal gran i avverkningsanmäld skog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3800,8 +3716,34 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3817,13 +3759,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118112682</t>
+          <t>https://artportalen.se/Sighting/118103682</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118118581</v>
+        <v>118103868</v>
       </c>
       <c r="B27" t="n">
         <v>79327</v>
@@ -3852,23 +3794,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>362380</v>
+        <v>362279</v>
       </c>
       <c r="R27" t="n">
-        <v>6882318</v>
+        <v>6882106</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3895,27 +3833,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av garnlav i grannaturskog.</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3935,22 +3868,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Grannaturskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3967,13 +3885,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118581</t>
+          <t>https://artportalen.se/Sighting/118103868</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118119303</v>
+        <v>118108025</v>
       </c>
       <c r="B28" t="n">
         <v>79327</v>
@@ -4011,14 +3929,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>362310</v>
+        <v>362343</v>
       </c>
       <c r="R28" t="n">
-        <v>6882298</v>
+        <v>6882273</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4045,27 +3963,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Väldigt långa bålar och i granbeståndet flera draperade av garnlav.</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4085,7 +3998,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4102,13 +4015,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119303</t>
+          <t>https://artportalen.se/Sighting/118108025</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118341001</v>
+        <v>118108207</v>
       </c>
       <c r="B29" t="n">
         <v>79327</v>
@@ -4142,22 +4055,18 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>362320</v>
+        <v>362326</v>
       </c>
       <c r="R29" t="n">
-        <v>6882282</v>
+        <v>6882154</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4184,27 +4093,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Granar draperade med garnlav.</t>
+          <t>Naturskog med riklig förekomst av garnlav</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4224,22 +4133,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Gammelgranskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4256,13 +4150,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118341001</t>
+          <t>https://artportalen.se/Sighting/118108207</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127170375</v>
+        <v>118112682</v>
       </c>
       <c r="B30" t="n">
         <v>79327</v>
@@ -4291,26 +4185,26 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lövåsen, Dlr</t>
+          <t>Sälderbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>363314</v>
+        <v>362476</v>
       </c>
       <c r="R30" t="n">
-        <v>6882815</v>
+        <v>6882192</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4334,22 +4228,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Växer i granbestånd på myrholme</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4375,13 +4274,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170375</t>
+          <t>https://artportalen.se/Sighting/118112682</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127170420</v>
+        <v>118118581</v>
       </c>
       <c r="B31" t="n">
         <v>79327</v>
@@ -4410,19 +4309,23 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>363307</v>
+        <v>362380</v>
       </c>
       <c r="R31" t="n">
-        <v>6882847</v>
+        <v>6882318</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4449,27 +4352,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Granar draperade med garnlav</t>
+          <t>Riklig förekomst av garnlav i grannaturskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4478,8 +4381,34 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4495,13 +4424,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170420</t>
+          <t>https://artportalen.se/Sighting/118118581</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127170500</v>
+        <v>118119303</v>
       </c>
       <c r="B32" t="n">
         <v>79327</v>
@@ -4530,22 +4459,26 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>363303</v>
+        <v>362310</v>
       </c>
       <c r="R32" t="n">
-        <v>6882872</v>
+        <v>6882298</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4569,27 +4502,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Granar draperade med garnlav.</t>
+          <t>Väldigt långa bålar och i granbeståndet flera draperade av garnlav.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4598,8 +4531,19 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4615,13 +4559,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170500</t>
+          <t>https://artportalen.se/Sighting/118119303</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127170642</v>
+        <v>118341001</v>
       </c>
       <c r="B33" t="n">
         <v>79327</v>
@@ -4650,7 +4594,11 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>med apothecier</t>
@@ -4659,17 +4607,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>363306</v>
+        <v>362320</v>
       </c>
       <c r="R33" t="n">
-        <v>6882880</v>
+        <v>6882282</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4693,27 +4641,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Garnlavsdraperade granar.</t>
+          <t>Granar draperade med garnlav.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4722,8 +4670,34 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4739,13 +4713,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170642</t>
+          <t>https://artportalen.se/Sighting/118341001</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127170911</v>
+        <v>127170375</v>
       </c>
       <c r="B34" t="n">
         <v>79327</v>
@@ -4775,18 +4749,22 @@
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Lövåsen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>363318</v>
+        <v>363314</v>
       </c>
       <c r="R34" t="n">
-        <v>6882898</v>
+        <v>6882815</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4818,7 +4796,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4828,12 +4806,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:58</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Draperade granar. Hotad fjällnära skog.</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4859,13 +4832,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170911</t>
+          <t>https://artportalen.se/Sighting/127170375</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127171152</v>
+        <v>127170420</v>
       </c>
       <c r="B35" t="n">
         <v>79327</v>
@@ -4895,11 +4868,7 @@
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4907,13 +4876,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>363314</v>
+        <v>363307</v>
       </c>
       <c r="R35" t="n">
-        <v>6882905</v>
+        <v>6882847</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4942,7 +4911,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4952,7 +4921,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Granar draperade med garnlav</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4978,13 +4952,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127171152</t>
+          <t>https://artportalen.se/Sighting/127170420</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127171838</v>
+        <v>127170500</v>
       </c>
       <c r="B36" t="n">
         <v>79327</v>
@@ -5014,11 +4988,7 @@
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5026,13 +4996,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>363302</v>
+        <v>363303</v>
       </c>
       <c r="R36" t="n">
-        <v>6882938</v>
+        <v>6882872</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5061,7 +5031,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5071,7 +5041,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Granar draperade med garnlav.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5097,13 +5072,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127171838</t>
+          <t>https://artportalen.se/Sighting/127170500</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127171879</v>
+        <v>127170642</v>
       </c>
       <c r="B37" t="n">
         <v>79327</v>
@@ -5133,7 +5108,11 @@
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5141,13 +5120,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>363287</v>
+        <v>363306</v>
       </c>
       <c r="R37" t="n">
-        <v>6882939</v>
+        <v>6882880</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5176,7 +5155,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5186,7 +5165,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Garnlavsdraperade granar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5212,13 +5196,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127171879</t>
+          <t>https://artportalen.se/Sighting/127170642</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127172219</v>
+        <v>127170911</v>
       </c>
       <c r="B38" t="n">
         <v>79327</v>
@@ -5256,10 +5240,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>363195</v>
+        <v>363318</v>
       </c>
       <c r="R38" t="n">
-        <v>6882944</v>
+        <v>6882898</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -5291,7 +5275,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5301,7 +5285,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Draperade granar. Hotad fjällnära skog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5327,13 +5316,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172219</t>
+          <t>https://artportalen.se/Sighting/127170911</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127172815</v>
+        <v>127171152</v>
       </c>
       <c r="B39" t="n">
         <v>79327</v>
@@ -5363,7 +5352,11 @@
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5371,10 +5364,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>363204</v>
+        <v>363314</v>
       </c>
       <c r="R39" t="n">
-        <v>6882810</v>
+        <v>6882905</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5406,7 +5399,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5416,12 +5409,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:33</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Draperade granar</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5447,13 +5435,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172815</t>
+          <t>https://artportalen.se/Sighting/127171152</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127172852</v>
+        <v>127171838</v>
       </c>
       <c r="B40" t="n">
         <v>79327</v>
@@ -5483,7 +5471,11 @@
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5491,13 +5483,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>363214</v>
+        <v>363302</v>
       </c>
       <c r="R40" t="n">
-        <v>6882814</v>
+        <v>6882938</v>
       </c>
       <c r="S40" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5526,7 +5518,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5536,12 +5528,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Garnlavsdraperade granar</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5567,13 +5554,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172852</t>
+          <t>https://artportalen.se/Sighting/127171838</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128820649</v>
+        <v>127171879</v>
       </c>
       <c r="B41" t="n">
         <v>79327</v>
@@ -5602,26 +5589,22 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>362222</v>
+        <v>363287</v>
       </c>
       <c r="R41" t="n">
-        <v>6882658</v>
+        <v>6882939</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5645,22 +5628,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5686,38 +5669,38 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128820649</t>
+          <t>https://artportalen.se/Sighting/127171879</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118118723</v>
+        <v>127172219</v>
       </c>
       <c r="B42" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5726,17 +5709,17 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>362344</v>
+        <v>363195</v>
       </c>
       <c r="R42" t="n">
-        <v>6882253</v>
+        <v>6882944</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5760,27 +5743,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Växer på stubbe av jättetall</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5789,19 +5767,8 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Barrnaturskog. Fjällnära</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5817,16 +5784,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118723</t>
+          <t>https://artportalen.se/Sighting/127172219</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121898927</v>
+        <v>127172815</v>
       </c>
       <c r="B43" t="n">
-        <v>83305</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5834,37 +5801,40 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>363129</v>
+        <v>363204</v>
       </c>
       <c r="R43" t="n">
-        <v>6882975</v>
+        <v>6882810</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5888,22 +5858,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Draperade granar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5918,73 +5893,68 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo, Cecilia Öster</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121898927</t>
+          <t>https://artportalen.se/Sighting/127172815</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118103394</v>
+        <v>127172852</v>
       </c>
       <c r="B44" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>362272</v>
+        <v>363214</v>
       </c>
       <c r="R44" t="n">
-        <v>6882099</v>
+        <v>6882814</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6008,27 +5978,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färska hacksmärken på gran Grannaturskog</t>
+          <t>Garnlavsdraperade granar</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6039,16 +6009,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6064,62 +6024,61 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118103394</t>
+          <t>https://artportalen.se/Sighting/127172852</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118103560</v>
+        <v>128820649</v>
       </c>
       <c r="B45" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>362276</v>
+        <v>362222</v>
       </c>
       <c r="R45" t="n">
-        <v>6882083</v>
+        <v>6882658</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6143,27 +6102,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Färska hackmärken på gran i grannaturskog som är avverkningsanmäld.</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6174,16 +6128,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6199,16 +6143,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118103560</t>
+          <t>https://artportalen.se/Sighting/128820649</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118107736</v>
+        <v>118118723</v>
       </c>
       <c r="B46" t="n">
-        <v>57953</v>
+        <v>79946</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6216,31 +6160,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6248,10 +6187,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>362349</v>
+        <v>362344</v>
       </c>
       <c r="R46" t="n">
-        <v>6882279</v>
+        <v>6882253</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6278,27 +6217,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i naturskog.</t>
+          <t>Växer på stubbe av jättetall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6307,6 +6246,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6317,7 +6257,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Mycket gamla granar och tallar</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6334,66 +6274,54 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118107736</t>
+          <t>https://artportalen.se/Sighting/118118723</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118113015</v>
+        <v>121898927</v>
       </c>
       <c r="B47" t="n">
-        <v>57953</v>
+        <v>83305</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>362487</v>
+        <v>363129</v>
       </c>
       <c r="R47" t="n">
-        <v>6882179</v>
+        <v>6882975</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6417,27 +6345,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Hackmärken på gran i myrholme.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6452,24 +6375,24 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Andreas Öster, Maria Hindemo, Cecilia Öster</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118113015</t>
+          <t>https://artportalen.se/Sighting/121898927</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118113051</v>
+        <v>118103394</v>
       </c>
       <c r="B48" t="n">
         <v>57953</v>
@@ -6497,32 +6420,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>362482</v>
+        <v>362272</v>
       </c>
       <c r="R48" t="n">
-        <v>6882180</v>
+        <v>6882099</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6546,27 +6465,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Hackmärken gran på myrholme. Naturskog</t>
+          <t>Färska hacksmärken på gran Grannaturskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6577,6 +6496,16 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6592,13 +6521,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118113051</t>
+          <t>https://artportalen.se/Sighting/118103394</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118118450</v>
+        <v>118103560</v>
       </c>
       <c r="B49" t="n">
         <v>57953</v>
@@ -6641,10 +6570,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>362489</v>
+        <v>362276</v>
       </c>
       <c r="R49" t="n">
-        <v>6882203</v>
+        <v>6882083</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6671,27 +6600,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Hackmärken på gran. Myrholme som är avverkningsanmäld</t>
+          <t>Färska hackmärken på gran i grannaturskog som är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6710,7 +6639,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Lokalt fuktig miljö</t>
+          <t>Grannaturskog</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6727,13 +6656,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118450</t>
+          <t>https://artportalen.se/Sighting/118103560</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118118466</v>
+        <v>118107736</v>
       </c>
       <c r="B50" t="n">
         <v>57953</v>
@@ -6772,14 +6701,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>362421</v>
+        <v>362349</v>
       </c>
       <c r="R50" t="n">
-        <v>6882227</v>
+        <v>6882279</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6806,27 +6735,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Färska hackmärken på fertalet grannar på denna myrholme.</t>
+          <t>Färska hackmärken på gran i naturskog.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6845,7 +6774,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Barrnaturskog på myrholme</t>
+          <t>Barrnaturskog. Mycket gamla granar och tallar</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6862,13 +6791,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118466</t>
+          <t>https://artportalen.se/Sighting/118107736</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118118547</v>
+        <v>118113015</v>
       </c>
       <c r="B51" t="n">
         <v>57953</v>
@@ -6896,7 +6825,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
@@ -6907,14 +6840,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>362378</v>
+        <v>362487</v>
       </c>
       <c r="R51" t="n">
-        <v>6882297</v>
+        <v>6882179</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6946,7 +6879,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6956,12 +6889,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Äldre hackmärken på gammal gran i barrnaturskog.</t>
+          <t>Hackmärken på gran i myrholme.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6972,16 +6905,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6997,13 +6920,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118547</t>
+          <t>https://artportalen.se/Sighting/118113015</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118118562</v>
+        <v>118113051</v>
       </c>
       <c r="B52" t="n">
         <v>57953</v>
@@ -7031,28 +6954,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>362373</v>
+        <v>362482</v>
       </c>
       <c r="R52" t="n">
-        <v>6882312</v>
+        <v>6882180</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7081,7 +7008,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7091,12 +7018,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Hackmärken på gammal gran i barrnaturskog. Skogen är avverkningsanmäld</t>
+          <t>Hackmärken gran på myrholme. Naturskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7107,16 +7034,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Barrnaturskog. Fjällnära</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -7132,13 +7049,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118562</t>
+          <t>https://artportalen.se/Sighting/118113051</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118118603</v>
+        <v>118118450</v>
       </c>
       <c r="B53" t="n">
         <v>57953</v>
@@ -7181,10 +7098,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>362381</v>
+        <v>362489</v>
       </c>
       <c r="R53" t="n">
-        <v>6882250</v>
+        <v>6882203</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -7216,7 +7133,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7226,12 +7143,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gammal gran i barrnaturskog som avverkningsanmäld.</t>
+          <t>Hackmärken på gran. Myrholme som är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7250,7 +7167,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog. Lokalt fuktig miljö</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7267,13 +7184,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118603</t>
+          <t>https://artportalen.se/Sighting/118118450</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118118863</v>
+        <v>118118466</v>
       </c>
       <c r="B54" t="n">
         <v>57953</v>
@@ -7312,14 +7229,14 @@
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>362327</v>
+        <v>362421</v>
       </c>
       <c r="R54" t="n">
-        <v>6882265</v>
+        <v>6882227</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -7351,7 +7268,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7361,12 +7278,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i barrnaturskog som är avverkningsanmäld</t>
+          <t>Färska hackmärken på fertalet grannar på denna myrholme.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7385,7 +7302,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog på myrholme</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7402,13 +7319,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118863</t>
+          <t>https://artportalen.se/Sighting/118118466</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118118905</v>
+        <v>118118547</v>
       </c>
       <c r="B55" t="n">
         <v>57953</v>
@@ -7451,10 +7368,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>362338</v>
+        <v>362378</v>
       </c>
       <c r="R55" t="n">
-        <v>6882298</v>
+        <v>6882297</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7486,7 +7403,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7496,12 +7413,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Hackmärken på gran i barrnaturskog</t>
+          <t>Äldre hackmärken på gammal gran i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7520,7 +7437,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7537,13 +7454,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118905</t>
+          <t>https://artportalen.se/Sighting/118118547</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118119133</v>
+        <v>118118562</v>
       </c>
       <c r="B56" t="n">
         <v>57953</v>
@@ -7586,10 +7503,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>362371</v>
+        <v>362373</v>
       </c>
       <c r="R56" t="n">
-        <v>6882362</v>
+        <v>6882312</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7621,7 +7538,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7631,12 +7548,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Färska hackmärken på grov gammal gran. i barrnaturskog som är hotad av avverkning.</t>
+          <t>Hackmärken på gammal gran i barrnaturskog. Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7672,13 +7589,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119133</t>
+          <t>https://artportalen.se/Sighting/118118562</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118119170</v>
+        <v>118118603</v>
       </c>
       <c r="B57" t="n">
         <v>57953</v>
@@ -7717,14 +7634,14 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>362327</v>
+        <v>362381</v>
       </c>
       <c r="R57" t="n">
-        <v>6882360</v>
+        <v>6882250</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7756,7 +7673,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7766,12 +7683,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Färska hackmärken på grov gammal gran i barrnaturskog. Avverkningsanmäld skog.</t>
+          <t>Färska hackmärken på gammal gran i barrnaturskog som avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7790,7 +7707,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Barrnatursk. Fjällnära</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7807,13 +7724,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119170</t>
+          <t>https://artportalen.se/Sighting/118118603</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118119483</v>
+        <v>118118863</v>
       </c>
       <c r="B58" t="n">
         <v>57953</v>
@@ -7856,10 +7773,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>362284</v>
+        <v>362327</v>
       </c>
       <c r="R58" t="n">
-        <v>6882318</v>
+        <v>6882265</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7891,7 +7808,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7901,12 +7818,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i barrnaturskog.</t>
+          <t>Färska hackmärken på gran i barrnaturskog som är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7942,13 +7859,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119483</t>
+          <t>https://artportalen.se/Sighting/118118863</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118119653</v>
+        <v>118118905</v>
       </c>
       <c r="B59" t="n">
         <v>57953</v>
@@ -7991,10 +7908,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>362269</v>
+        <v>362338</v>
       </c>
       <c r="R59" t="n">
-        <v>6882324</v>
+        <v>6882298</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -8026,7 +7943,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8036,12 +7953,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Hackmärken på grov gran intill skidspår som går genom barrnaturskogen. Avverkningsanmäld skog.</t>
+          <t>Hackmärken på gran i barrnaturskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8077,13 +7994,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119653</t>
+          <t>https://artportalen.se/Sighting/118118905</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118119701</v>
+        <v>118119133</v>
       </c>
       <c r="B60" t="n">
         <v>57953</v>
@@ -8126,10 +8043,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>362279</v>
+        <v>362371</v>
       </c>
       <c r="R60" t="n">
-        <v>6882363</v>
+        <v>6882362</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -8161,7 +8078,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8171,12 +8088,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i barrnaturskog som hotas av avverkning</t>
+          <t>Färska hackmärken på grov gammal gran. i barrnaturskog som är hotad av avverkning.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8212,13 +8129,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119701</t>
+          <t>https://artportalen.se/Sighting/118119133</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118119770</v>
+        <v>118119170</v>
       </c>
       <c r="B61" t="n">
         <v>57953</v>
@@ -8261,10 +8178,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>362240</v>
+        <v>362327</v>
       </c>
       <c r="R61" t="n">
-        <v>6882345</v>
+        <v>6882360</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -8296,7 +8213,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8306,12 +8223,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gammal gran i barrnaturskog.</t>
+          <t>Färska hackmärken på grov gammal gran i barrnaturskog. Avverkningsanmäld skog.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8330,7 +8247,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnatursk. Fjällnära</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8347,13 +8264,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119770</t>
+          <t>https://artportalen.se/Sighting/118119170</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118119872</v>
+        <v>118119483</v>
       </c>
       <c r="B62" t="n">
         <v>57953</v>
@@ -8386,7 +8303,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8396,10 +8313,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>362230</v>
+        <v>362284</v>
       </c>
       <c r="R62" t="n">
-        <v>6882332</v>
+        <v>6882318</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -8431,7 +8348,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8441,7 +8358,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på gran i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8477,13 +8399,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119872</t>
+          <t>https://artportalen.se/Sighting/118119483</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118120074</v>
+        <v>118119653</v>
       </c>
       <c r="B63" t="n">
         <v>57953</v>
@@ -8516,7 +8438,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -8526,10 +8448,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>362243</v>
+        <v>362269</v>
       </c>
       <c r="R63" t="n">
-        <v>6882254</v>
+        <v>6882324</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -8561,7 +8483,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8571,12 +8493,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Färska och äldre hackmärken på gammal gran i barrnatuskog.</t>
+          <t>Hackmärken på grov gran intill skidspår som går genom barrnaturskogen. Avverkningsanmäld skog.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8612,13 +8534,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120074</t>
+          <t>https://artportalen.se/Sighting/118119653</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118120164</v>
+        <v>118119701</v>
       </c>
       <c r="B64" t="n">
         <v>57953</v>
@@ -8661,10 +8583,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>362252</v>
+        <v>362279</v>
       </c>
       <c r="R64" t="n">
-        <v>6882248</v>
+        <v>6882363</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8696,7 +8618,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8706,12 +8628,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran in barrnaturskog.</t>
+          <t>Färska hackmärken på gran i barrnaturskog som hotas av avverkning</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8747,13 +8669,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120164</t>
+          <t>https://artportalen.se/Sighting/118119701</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118120248</v>
+        <v>118119770</v>
       </c>
       <c r="B65" t="n">
         <v>57953</v>
@@ -8796,10 +8718,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>362267</v>
+        <v>362240</v>
       </c>
       <c r="R65" t="n">
-        <v>6882224</v>
+        <v>6882345</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8831,7 +8753,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8841,12 +8763,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Färska hackmärken i ett granbestånd. I avverkningsanmält skogsområe</t>
+          <t>Färska hackmärken på gammal gran i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8882,13 +8804,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120248</t>
+          <t>https://artportalen.se/Sighting/118119770</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118120388</v>
+        <v>118119872</v>
       </c>
       <c r="B66" t="n">
         <v>57953</v>
@@ -8931,10 +8853,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>362196</v>
+        <v>362230</v>
       </c>
       <c r="R66" t="n">
-        <v>6882301</v>
+        <v>6882332</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8966,7 +8888,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8976,7 +8898,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8995,7 +8917,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9012,13 +8934,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120388</t>
+          <t>https://artportalen.se/Sighting/118119872</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118120447</v>
+        <v>118120074</v>
       </c>
       <c r="B67" t="n">
         <v>57953</v>
@@ -9061,10 +8983,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>362200</v>
+        <v>362243</v>
       </c>
       <c r="R67" t="n">
-        <v>6882350</v>
+        <v>6882254</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -9096,7 +9018,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9106,12 +9028,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Färska och äldre hackmärken på grov gran i barrnaturskog.</t>
+          <t>Färska och äldre hackmärken på gammal gran i barrnatuskog.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9147,13 +9069,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120447</t>
+          <t>https://artportalen.se/Sighting/118120074</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118120506</v>
+        <v>118120164</v>
       </c>
       <c r="B68" t="n">
         <v>57953</v>
@@ -9186,7 +9108,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -9196,10 +9118,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>362168</v>
+        <v>362252</v>
       </c>
       <c r="R68" t="n">
-        <v>6882359</v>
+        <v>6882248</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -9231,7 +9153,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9241,12 +9163,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Äldre hackmärken på gammal gran med garnlav. I avverkningsanmäld barrnaturskog</t>
+          <t>Färska hackmärken på gran in barrnaturskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9265,7 +9187,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Barrnaturskog.</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9282,13 +9204,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120506</t>
+          <t>https://artportalen.se/Sighting/118120164</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118122341</v>
+        <v>118120248</v>
       </c>
       <c r="B69" t="n">
         <v>57953</v>
@@ -9327,14 +9249,14 @@
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>362247</v>
+        <v>362267</v>
       </c>
       <c r="R69" t="n">
-        <v>6882178</v>
+        <v>6882224</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -9361,27 +9283,27 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Hackmärken på tall i barrnaturskog.</t>
+          <t>Färska hackmärken i ett granbestånd. I avverkningsanmält skogsområe</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9400,7 +9322,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9417,13 +9339,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122341</t>
+          <t>https://artportalen.se/Sighting/118120248</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118122435</v>
+        <v>118120388</v>
       </c>
       <c r="B70" t="n">
         <v>57953</v>
@@ -9456,20 +9378,20 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>362276</v>
+        <v>362196</v>
       </c>
       <c r="R70" t="n">
-        <v>6882136</v>
+        <v>6882301</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9496,27 +9418,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska hackmärken på gran i barrnaturskog</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9552,13 +9469,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122435</t>
+          <t>https://artportalen.se/Sighting/118120388</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118122458</v>
+        <v>118120447</v>
       </c>
       <c r="B71" t="n">
         <v>57953</v>
@@ -9597,14 +9514,14 @@
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>362281</v>
+        <v>362200</v>
       </c>
       <c r="R71" t="n">
-        <v>6882135</v>
+        <v>6882350</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9631,27 +9548,27 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i fin barrnaturskog som är avverkningsanmäld</t>
+          <t>Färska och äldre hackmärken på grov gran i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9670,7 +9587,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9687,13 +9604,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122458</t>
+          <t>https://artportalen.se/Sighting/118120447</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118122497</v>
+        <v>118120506</v>
       </c>
       <c r="B72" t="n">
         <v>57953</v>
@@ -9726,20 +9643,20 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>362283</v>
+        <v>362168</v>
       </c>
       <c r="R72" t="n">
-        <v>6882105</v>
+        <v>6882359</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9766,27 +9683,27 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i avverkningsanmäld barrnaturskog</t>
+          <t>Äldre hackmärken på gammal gran med garnlav. I avverkningsanmäld barrnaturskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9805,7 +9722,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Barrnaturskog.</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9822,13 +9739,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122497</t>
+          <t>https://artportalen.se/Sighting/118120506</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118340481</v>
+        <v>118122341</v>
       </c>
       <c r="B73" t="n">
         <v>57953</v>
@@ -9871,10 +9788,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>362275</v>
+        <v>362247</v>
       </c>
       <c r="R73" t="n">
-        <v>6882133</v>
+        <v>6882178</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9901,27 +9818,27 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i fjällnära skog.</t>
+          <t>Hackmärken på tall i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9940,7 +9857,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9957,13 +9874,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340481</t>
+          <t>https://artportalen.se/Sighting/118122341</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118340595</v>
+        <v>118122435</v>
       </c>
       <c r="B74" t="n">
         <v>57953</v>
@@ -10006,10 +9923,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>362281</v>
+        <v>362276</v>
       </c>
       <c r="R74" t="n">
-        <v>6882106</v>
+        <v>6882136</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -10036,27 +9953,27 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>färska hackmärken på gatan. Fjällnära skog</t>
+          <t>Färska hackmärken på gran i barrnaturskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10075,7 +9992,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10092,13 +10009,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340595</t>
+          <t>https://artportalen.se/Sighting/118122435</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118340691</v>
+        <v>118122458</v>
       </c>
       <c r="B75" t="n">
         <v>57953</v>
@@ -10141,13 +10058,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>362270</v>
+        <v>362281</v>
       </c>
       <c r="R75" t="n">
-        <v>6882100</v>
+        <v>6882135</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10171,27 +10088,27 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i fjällnära skog</t>
+          <t>Färska hackmärken på gran i fin barrnaturskog som är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10210,7 +10127,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10227,13 +10144,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340691</t>
+          <t>https://artportalen.se/Sighting/118122458</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118340748</v>
+        <v>118122497</v>
       </c>
       <c r="B76" t="n">
         <v>57953</v>
@@ -10276,10 +10193,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>362272</v>
+        <v>362283</v>
       </c>
       <c r="R76" t="n">
-        <v>6882086</v>
+        <v>6882105</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -10306,27 +10223,27 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>färska hackmnärken på gran i naturskog. Fjällnära</t>
+          <t>Färska hackmärken på gran i avverkningsanmäld barrnaturskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10345,7 +10262,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10362,13 +10279,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340748</t>
+          <t>https://artportalen.se/Sighting/118122497</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118340920</v>
+        <v>118340481</v>
       </c>
       <c r="B77" t="n">
         <v>57953</v>
@@ -10407,14 +10324,14 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>362284</v>
+        <v>362275</v>
       </c>
       <c r="R77" t="n">
-        <v>6882361</v>
+        <v>6882133</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -10461,7 +10378,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Färska och äldre hackmärken. Skogen är avverkningsanmäld. Gran med hackmärken inom anmälan. Se bild</t>
+          <t>Färska hackmärken på gran i fjällnära skog.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10480,7 +10397,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10497,13 +10414,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340920</t>
+          <t>https://artportalen.se/Sighting/118340481</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121206319</v>
+        <v>118340595</v>
       </c>
       <c r="B78" t="n">
         <v>57953</v>
@@ -10532,19 +10449,27 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>363246</v>
+        <v>362281</v>
       </c>
       <c r="R78" t="n">
-        <v>6883004</v>
+        <v>6882106</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10568,22 +10493,27 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>färska hackmärken på gatan. Fjällnära skog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10594,28 +10524,38 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121206319</t>
+          <t>https://artportalen.se/Sighting/118340595</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127170971</v>
+        <v>118340691</v>
       </c>
       <c r="B79" t="n">
         <v>57953</v>
@@ -10643,32 +10583,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>363315</v>
+        <v>362270</v>
       </c>
       <c r="R79" t="n">
-        <v>6882898</v>
+        <v>6882100</v>
       </c>
       <c r="S79" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10692,22 +10628,27 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på gran i fjällnära skog</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10718,6 +10659,16 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -10733,13 +10684,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170971</t>
+          <t>https://artportalen.se/Sighting/118340691</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127172142</v>
+        <v>118340748</v>
       </c>
       <c r="B80" t="n">
         <v>57953</v>
@@ -10767,11 +10718,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
@@ -10782,17 +10729,17 @@
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>363196</v>
+        <v>362272</v>
       </c>
       <c r="R80" t="n">
-        <v>6882950</v>
+        <v>6882086</v>
       </c>
       <c r="S80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10816,27 +10763,27 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Färska och äldre hackmärken.</t>
+          <t>färska hackmnärken på gran i naturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10847,6 +10794,16 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -10862,13 +10819,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172142</t>
+          <t>https://artportalen.se/Sighting/118340748</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127172737</v>
+        <v>118340920</v>
       </c>
       <c r="B81" t="n">
         <v>57953</v>
@@ -10896,32 +10853,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>363143</v>
+        <v>362284</v>
       </c>
       <c r="R81" t="n">
-        <v>6882797</v>
+        <v>6882361</v>
       </c>
       <c r="S81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10945,22 +10898,27 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken. Skogen är avverkningsanmäld. Gran med hackmärken inom anmälan. Se bild</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10971,6 +10929,16 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>barrnaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -10986,13 +10954,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172737</t>
+          <t>https://artportalen.se/Sighting/118340920</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127172795</v>
+        <v>121206319</v>
       </c>
       <c r="B82" t="n">
         <v>57953</v>
@@ -11020,32 +10988,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>363188</v>
+        <v>363246</v>
       </c>
       <c r="R82" t="n">
-        <v>6882809</v>
+        <v>6883004</v>
       </c>
       <c r="S82" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -11069,27 +11025,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackmärken</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11104,24 +11055,24 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172795</t>
+          <t>https://artportalen.se/Sighting/121206319</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127172899</v>
+        <v>127170971</v>
       </c>
       <c r="B83" t="n">
         <v>57953</v>
@@ -11168,13 +11119,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>363234</v>
+        <v>363315</v>
       </c>
       <c r="R83" t="n">
-        <v>6882800</v>
+        <v>6882898</v>
       </c>
       <c r="S83" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -11203,7 +11154,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11213,7 +11164,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11239,13 +11190,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172899</t>
+          <t>https://artportalen.se/Sighting/127170971</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127315676</v>
+        <v>127172142</v>
       </c>
       <c r="B84" t="n">
         <v>57953</v>
@@ -11275,42 +11226,30 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>363122</v>
+        <v>363196</v>
       </c>
       <c r="R84" t="n">
-        <v>6882946</v>
+        <v>6882950</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11334,22 +11273,27 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11364,24 +11308,24 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127315676</t>
+          <t>https://artportalen.se/Sighting/127172142</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128822185</v>
+        <v>127172737</v>
       </c>
       <c r="B85" t="n">
         <v>57953</v>
@@ -11421,21 +11365,17 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>362326</v>
+        <v>363143</v>
       </c>
       <c r="R85" t="n">
-        <v>6882768</v>
+        <v>6882797</v>
       </c>
       <c r="S85" t="n">
         <v>4</v>
@@ -11462,22 +11402,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11503,13 +11443,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128822185</t>
+          <t>https://artportalen.se/Sighting/127172737</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128822490</v>
+        <v>127172795</v>
       </c>
       <c r="B86" t="n">
         <v>57953</v>
@@ -11546,27 +11486,23 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>362260</v>
+        <v>363188</v>
       </c>
       <c r="R86" t="n">
-        <v>6882421</v>
+        <v>6882809</v>
       </c>
       <c r="S86" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -11590,22 +11526,27 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11631,13 +11572,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128822490</t>
+          <t>https://artportalen.se/Sighting/127172795</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128822499</v>
+        <v>127172899</v>
       </c>
       <c r="B87" t="n">
         <v>57953</v>
@@ -11680,17 +11621,17 @@
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>362273</v>
+        <v>363234</v>
       </c>
       <c r="R87" t="n">
-        <v>6882421</v>
+        <v>6882800</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11714,22 +11655,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11755,63 +11696,78 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128822499</t>
+          <t>https://artportalen.se/Sighting/127172899</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118122325</v>
+        <v>127315676</v>
       </c>
       <c r="B88" t="n">
-        <v>5179</v>
+        <v>57953</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>362234</v>
+        <v>363122</v>
       </c>
       <c r="R88" t="n">
-        <v>6882185</v>
+        <v>6882946</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11835,27 +11791,22 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>På torrgran vid myrknat intill barrnaturskog</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11864,44 +11815,33 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>Myrmark intill barrnaturskog</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Marcus Hansson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Marcus Hansson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122325</t>
+          <t>https://artportalen.se/Sighting/127315676</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127315773</v>
+        <v>128822185</v>
       </c>
       <c r="B89" t="n">
-        <v>58057</v>
+        <v>57953</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11909,16 +11849,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -11928,17 +11868,14 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -11948,17 +11885,17 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>363120</v>
+        <v>362326</v>
       </c>
       <c r="R89" t="n">
-        <v>6882934</v>
+        <v>6882768</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11982,22 +11919,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -12012,27 +11949,27 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127315773</t>
+          <t>https://artportalen.se/Sighting/128822185</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128820534</v>
+        <v>128822490</v>
       </c>
       <c r="B90" t="n">
-        <v>58057</v>
+        <v>57953</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12040,16 +11977,16 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -12066,20 +12003,24 @@
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>362267</v>
+        <v>362260</v>
       </c>
       <c r="R90" t="n">
-        <v>6882595</v>
+        <v>6882421</v>
       </c>
       <c r="S90" t="n">
         <v>4</v>
@@ -12111,7 +12052,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -12121,7 +12062,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -12147,55 +12088,63 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128820534</t>
+          <t>https://artportalen.se/Sighting/128822490</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118122289</v>
+        <v>128822499</v>
       </c>
       <c r="B91" t="n">
-        <v>99035</v>
+        <v>57953</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>362232</v>
+        <v>362273</v>
       </c>
       <c r="R91" t="n">
-        <v>6882193</v>
+        <v>6882421</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -12222,22 +12171,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12246,19 +12195,8 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AH91" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>Barrnaturskog vid myrkant</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -12274,16 +12212,16 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122289</t>
+          <t>https://artportalen.se/Sighting/128822499</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118118517</v>
+        <v>118122325</v>
       </c>
       <c r="B92" t="n">
-        <v>97983</v>
+        <v>5179</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12291,27 +12229,32 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -12319,10 +12262,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>362380</v>
+        <v>362234</v>
       </c>
       <c r="R92" t="n">
-        <v>6882294</v>
+        <v>6882185</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -12349,27 +12292,27 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Växer under gamla granar i barrnaturskog. Fuktig miljö.</t>
+          <t>På torrgran vid myrknat intill barrnaturskog</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12389,7 +12332,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Myrmark intill barrnaturskog</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -12406,58 +12349,73 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118517</t>
+          <t>https://artportalen.se/Sighting/118122325</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118118821</v>
+        <v>127315773</v>
       </c>
       <c r="B93" t="n">
-        <v>97983</v>
+        <v>58057</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221945</v>
+        <v>103031</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>362339</v>
+        <v>363120</v>
       </c>
       <c r="R93" t="n">
-        <v>6882268</v>
+        <v>6882934</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -12481,27 +12439,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Växer på en stor yta under gamla granar i barrnaturskog</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12510,86 +12463,83 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>Barrnaturskog. Fjällnära</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Marcus Hansson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Marcus Hansson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118821</t>
+          <t>https://artportalen.se/Sighting/127315773</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118119084</v>
+        <v>128820534</v>
       </c>
       <c r="B94" t="n">
-        <v>97983</v>
+        <v>58057</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221945</v>
+        <v>103031</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>362369</v>
+        <v>362267</v>
       </c>
       <c r="R94" t="n">
-        <v>6882345</v>
+        <v>6882595</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12613,22 +12563,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12637,19 +12587,8 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>Grannaturskog. Fjällnära</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -12665,16 +12604,16 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119084</t>
+          <t>https://artportalen.se/Sighting/128820534</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127171558</v>
+        <v>118122289</v>
       </c>
       <c r="B95" t="n">
-        <v>97983</v>
+        <v>99035</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12682,21 +12621,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -12706,17 +12645,17 @@
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>363325</v>
+        <v>362232</v>
       </c>
       <c r="R95" t="n">
-        <v>6882909</v>
+        <v>6882193</v>
       </c>
       <c r="S95" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12740,22 +12679,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12764,8 +12703,19 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>Barrnaturskog vid myrkant</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -12781,13 +12731,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127171558</t>
+          <t>https://artportalen.se/Sighting/118122289</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127172203</v>
+        <v>118118517</v>
       </c>
       <c r="B96" t="n">
         <v>97983</v>
@@ -12822,17 +12772,17 @@
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>363195</v>
+        <v>362380</v>
       </c>
       <c r="R96" t="n">
-        <v>6882944</v>
+        <v>6882294</v>
       </c>
       <c r="S96" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12856,22 +12806,27 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Växer under gamla granar i barrnaturskog. Fuktig miljö.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12880,8 +12835,19 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -12897,13 +12863,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172203</t>
+          <t>https://artportalen.se/Sighting/118118517</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127172331</v>
+        <v>118118821</v>
       </c>
       <c r="B97" t="n">
         <v>97983</v>
@@ -12938,17 +12904,17 @@
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>363170</v>
+        <v>362339</v>
       </c>
       <c r="R97" t="n">
-        <v>6882973</v>
+        <v>6882268</v>
       </c>
       <c r="S97" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12972,22 +12938,27 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Växer på en stor yta under gamla granar i barrnaturskog</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12996,8 +12967,19 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -13013,13 +12995,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172331</t>
+          <t>https://artportalen.se/Sighting/118118821</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128820515</v>
+        <v>118119084</v>
       </c>
       <c r="B98" t="n">
         <v>97983</v>
@@ -13051,24 +13033,20 @@
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>362287</v>
+        <v>362369</v>
       </c>
       <c r="R98" t="n">
-        <v>6882523</v>
+        <v>6882345</v>
       </c>
       <c r="S98" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -13092,22 +13070,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13116,8 +13094,19 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>Grannaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -13132,6 +13121,474 @@
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118119084</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>127171558</v>
+      </c>
+      <c r="B99" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Kerstibygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>363325</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6882909</v>
+      </c>
+      <c r="S99" t="n">
+        <v>4</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171558</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>127172203</v>
+      </c>
+      <c r="B100" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Kerstibygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>363195</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6882944</v>
+      </c>
+      <c r="S100" t="n">
+        <v>4</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172203</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>127172331</v>
+      </c>
+      <c r="B101" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Kerstibygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>363170</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6882973</v>
+      </c>
+      <c r="S101" t="n">
+        <v>4</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172331</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>128820515</v>
+      </c>
+      <c r="B102" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Kokällmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>362287</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6882523</v>
+      </c>
+      <c r="S102" t="n">
+        <v>4</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128820515</t>
         </is>
@@ -13236,6 +13693,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135621906</v>
       </c>
       <c r="B3" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>135622151</v>
       </c>
       <c r="B4" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>135621791</v>
       </c>
       <c r="B12" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>135621801</v>
       </c>
       <c r="B15" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ102"/>
+  <dimension ref="A1:AZ104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1863,10 +1863,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135621791</v>
+        <v>135621366</v>
       </c>
       <c r="B12" t="n">
-        <v>92050</v>
+        <v>79520</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,37 +1874,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>362646</v>
+        <v>362561</v>
       </c>
       <c r="R12" t="n">
-        <v>6882779</v>
+        <v>6882778</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1969,54 +1969,54 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135621791</t>
+          <t>https://artportalen.se/Sighting/135621366</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130470733</v>
+        <v>135621791</v>
       </c>
       <c r="B13" t="n">
-        <v>91923</v>
+        <v>92050</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lövåsen, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>363275</v>
+        <v>362646</v>
       </c>
       <c r="R13" t="n">
-        <v>6882937</v>
+        <v>6882779</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2040,22 +2040,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2070,62 +2070,62 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Anders Björkén, Maria Hindemo</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130470733</t>
+          <t>https://artportalen.se/Sighting/135621791</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121206216</v>
+        <v>130470733</v>
       </c>
       <c r="B14" t="n">
-        <v>92369</v>
+        <v>91923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Lövåsen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>363227</v>
+        <v>363275</v>
       </c>
       <c r="R14" t="n">
-        <v>6882956</v>
+        <v>6882937</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2152,22 +2152,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2182,27 +2182,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Cajsa Björkén, Anders Björkén, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121206216</t>
+          <t>https://artportalen.se/Sighting/130470733</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135621801</v>
+        <v>121206216</v>
       </c>
       <c r="B15" t="n">
-        <v>92482</v>
+        <v>92369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2234,13 +2234,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>362649</v>
+        <v>363227</v>
       </c>
       <c r="R15" t="n">
-        <v>6882777</v>
+        <v>6882956</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2264,22 +2264,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,27 +2294,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Carl Wiking</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Carl Wiking</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135621801</t>
+          <t>https://artportalen.se/Sighting/121206216</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121206277</v>
+        <v>135621801</v>
       </c>
       <c r="B16" t="n">
-        <v>83173</v>
+        <v>92482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2322,21 +2322,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>363227</v>
+        <v>362649</v>
       </c>
       <c r="R16" t="n">
-        <v>6882956</v>
+        <v>6882777</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2376,22 +2376,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,72 +2406,65 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121206277</t>
+          <t>https://artportalen.se/Sighting/135621801</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118112482</v>
+        <v>121206277</v>
       </c>
       <c r="B17" t="n">
-        <v>92083</v>
+        <v>83173</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1503</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>362476</v>
+        <v>363227</v>
       </c>
       <c r="R17" t="n">
-        <v>6882192</v>
+        <v>6882956</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2495,27 +2488,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Växer under gammal gren från jättetall på myrholme. Skogen är avverkningsanmäld</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2524,56 +2512,55 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118112482</t>
+          <t>https://artportalen.se/Sighting/121206277</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118340526</v>
+        <v>118112482</v>
       </c>
       <c r="B18" t="n">
-        <v>91831</v>
+        <v>92083</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3242</v>
+        <v>1503</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2586,14 +2573,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>362269</v>
+        <v>362476</v>
       </c>
       <c r="R18" t="n">
-        <v>6882132</v>
+        <v>6882192</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2620,27 +2607,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Växer på undersida av tallgren från gammal tall. Fjällnära skog.</t>
+          <t>Växer under gammal gren från jättetall på myrholme. Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2653,31 +2640,6 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Barrnaturskog. Fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
@@ -2692,54 +2654,54 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340526</t>
+          <t>https://artportalen.se/Sighting/118112482</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121206393</v>
+        <v>135621229</v>
       </c>
       <c r="B19" t="n">
-        <v>91831</v>
+        <v>92405</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3242</v>
+        <v>1506</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>363237</v>
+        <v>362586</v>
       </c>
       <c r="R19" t="n">
-        <v>6883017</v>
+        <v>6882774</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2763,115 +2725,107 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Doftar inte så mycket. Tror det beror på att årets fruktkroppar inte är så utvecklade. Bör kollas upp lite senare.</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Dead branch  # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121206393</t>
+          <t>https://artportalen.se/Sighting/135621229</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121206160</v>
+        <v>118340526</v>
       </c>
       <c r="B20" t="n">
-        <v>92632</v>
+        <v>91831</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3298</v>
+        <v>3242</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>363153</v>
+        <v>362269</v>
       </c>
       <c r="R20" t="n">
-        <v>6882853</v>
+        <v>6882132</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2895,22 +2849,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Växer på undersida av tallgren från gammal tall. Fjällnära skog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2919,98 +2878,97 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
+      </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121206160</t>
+          <t>https://artportalen.se/Sighting/118340526</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>110444488</v>
+        <v>121206393</v>
       </c>
       <c r="B21" t="n">
-        <v>79327</v>
+        <v>91831</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lövåsen, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>363277</v>
+        <v>363237</v>
       </c>
       <c r="R21" t="n">
-        <v>6882948</v>
+        <v>6883017</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3034,27 +2992,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ymnig förekomst av garnlav i fin grannaturskog. Granar draperade av laven. På grov gran garnlav med soral.</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3063,104 +3016,91 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
-      </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Dead branch  # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110444488</t>
+          <t>https://artportalen.se/Sighting/121206393</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>110513997</v>
+        <v>121206160</v>
       </c>
       <c r="B22" t="n">
-        <v>79327</v>
+        <v>92632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lövåsen , Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>363288</v>
+        <v>363153</v>
       </c>
       <c r="R22" t="n">
-        <v>6882833</v>
+        <v>6882853</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3184,22 +3124,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3210,28 +3150,48 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110513997</t>
+          <t>https://artportalen.se/Sighting/121206160</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>110514177</v>
+        <v>110444488</v>
       </c>
       <c r="B23" t="n">
         <v>79327</v>
@@ -3263,23 +3223,23 @@
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lövåsen , Dlr</t>
+          <t>Lövåsen, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>363305</v>
+        <v>363277</v>
       </c>
       <c r="R23" t="n">
-        <v>6882833</v>
+        <v>6882948</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3303,22 +3263,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ymnig förekomst av garnlav i fin grannaturskog. Granar draperade av laven. På grov gran garnlav med soral.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3327,8 +3292,34 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3344,13 +3335,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110514177</t>
+          <t>https://artportalen.se/Sighting/110444488</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>110514236</v>
+        <v>110513997</v>
       </c>
       <c r="B24" t="n">
         <v>79327</v>
@@ -3392,13 +3383,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>363313</v>
+        <v>363288</v>
       </c>
       <c r="R24" t="n">
-        <v>6882881</v>
+        <v>6882833</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3427,7 +3418,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3437,7 +3428,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3463,13 +3454,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110514236</t>
+          <t>https://artportalen.se/Sighting/110513997</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118103637</v>
+        <v>110514177</v>
       </c>
       <c r="B25" t="n">
         <v>79327</v>
@@ -3499,18 +3490,22 @@
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Lövåsen , Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>362276</v>
+        <v>363305</v>
       </c>
       <c r="R25" t="n">
-        <v>6882072</v>
+        <v>6882833</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3537,27 +3532,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Växer på gran i naturskog.</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3566,34 +3556,8 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3609,13 +3573,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118103637</t>
+          <t>https://artportalen.se/Sighting/110514177</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118103682</v>
+        <v>110514236</v>
       </c>
       <c r="B26" t="n">
         <v>79327</v>
@@ -3644,23 +3608,23 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Lövåsen , Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>362257</v>
+        <v>363313</v>
       </c>
       <c r="R26" t="n">
-        <v>6882084</v>
+        <v>6882881</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3687,27 +3651,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Växer på gammal gran i avverkningsanmäld skog.</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3716,34 +3675,8 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3759,13 +3692,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118103682</t>
+          <t>https://artportalen.se/Sighting/110514236</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118103868</v>
+        <v>118103637</v>
       </c>
       <c r="B27" t="n">
         <v>79327</v>
@@ -3803,10 +3736,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>362279</v>
+        <v>362276</v>
       </c>
       <c r="R27" t="n">
-        <v>6882106</v>
+        <v>6882072</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3838,7 +3771,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3848,7 +3781,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Växer på gran i naturskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3871,6 +3809,21 @@
           <t>Grannaturskog</t>
         </is>
       </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
@@ -3885,13 +3838,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118103868</t>
+          <t>https://artportalen.se/Sighting/118103637</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118108025</v>
+        <v>118103682</v>
       </c>
       <c r="B28" t="n">
         <v>79327</v>
@@ -3933,10 +3886,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>362343</v>
+        <v>362257</v>
       </c>
       <c r="R28" t="n">
-        <v>6882273</v>
+        <v>6882084</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3968,7 +3921,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3978,7 +3931,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Växer på gammal gran i avverkningsanmäld skog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3998,7 +3956,22 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4015,13 +3988,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118108025</t>
+          <t>https://artportalen.se/Sighting/118103682</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118108207</v>
+        <v>118103868</v>
       </c>
       <c r="B29" t="n">
         <v>79327</v>
@@ -4050,11 +4023,7 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -4063,10 +4032,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>362326</v>
+        <v>362279</v>
       </c>
       <c r="R29" t="n">
-        <v>6882154</v>
+        <v>6882106</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4098,7 +4067,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4108,12 +4077,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Naturskog med riklig förekomst av garnlav</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4133,7 +4097,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Gammelgranskog</t>
+          <t>Grannaturskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4150,13 +4114,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118108207</t>
+          <t>https://artportalen.se/Sighting/118103868</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118112682</v>
+        <v>118108025</v>
       </c>
       <c r="B30" t="n">
         <v>79327</v>
@@ -4194,14 +4158,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>362476</v>
+        <v>362343</v>
       </c>
       <c r="R30" t="n">
-        <v>6882192</v>
+        <v>6882273</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4228,27 +4192,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Växer i granbestånd på myrholme</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4257,8 +4216,19 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4274,13 +4244,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118112682</t>
+          <t>https://artportalen.se/Sighting/118108025</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118118581</v>
+        <v>118108207</v>
       </c>
       <c r="B31" t="n">
         <v>79327</v>
@@ -4318,14 +4288,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>362380</v>
+        <v>362326</v>
       </c>
       <c r="R31" t="n">
-        <v>6882318</v>
+        <v>6882154</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4352,27 +4322,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav i grannaturskog.</t>
+          <t>Naturskog med riklig förekomst av garnlav</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4392,22 +4362,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Gammelgranskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4424,13 +4379,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118581</t>
+          <t>https://artportalen.se/Sighting/118108207</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118119303</v>
+        <v>118112682</v>
       </c>
       <c r="B32" t="n">
         <v>79327</v>
@@ -4468,14 +4423,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>362310</v>
+        <v>362476</v>
       </c>
       <c r="R32" t="n">
-        <v>6882298</v>
+        <v>6882192</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4507,7 +4462,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4517,12 +4472,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Väldigt långa bålar och i granbeståndet flera draperade av garnlav.</t>
+          <t>Växer i granbestånd på myrholme</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4531,19 +4486,8 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Barrnaturskog. Fjällnära</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4559,13 +4503,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119303</t>
+          <t>https://artportalen.se/Sighting/118112682</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118341001</v>
+        <v>118118581</v>
       </c>
       <c r="B33" t="n">
         <v>79327</v>
@@ -4599,11 +4543,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4611,10 +4551,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>362320</v>
+        <v>362380</v>
       </c>
       <c r="R33" t="n">
-        <v>6882282</v>
+        <v>6882318</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4641,27 +4581,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Granar draperade med garnlav.</t>
+          <t>Riklig förekomst av garnlav i grannaturskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4713,13 +4653,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118341001</t>
+          <t>https://artportalen.se/Sighting/118118581</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127170375</v>
+        <v>118119303</v>
       </c>
       <c r="B34" t="n">
         <v>79327</v>
@@ -4748,26 +4688,26 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lövåsen, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>363314</v>
+        <v>362310</v>
       </c>
       <c r="R34" t="n">
-        <v>6882815</v>
+        <v>6882298</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4791,22 +4731,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Väldigt långa bålar och i granbeståndet flera draperade av garnlav.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4815,8 +4760,19 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4832,13 +4788,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170375</t>
+          <t>https://artportalen.se/Sighting/118119303</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127170420</v>
+        <v>118341001</v>
       </c>
       <c r="B35" t="n">
         <v>79327</v>
@@ -4867,19 +4823,27 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>363307</v>
+        <v>362320</v>
       </c>
       <c r="R35" t="n">
-        <v>6882847</v>
+        <v>6882282</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4906,27 +4870,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Granar draperade med garnlav</t>
+          <t>Granar draperade med garnlav.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4935,8 +4899,34 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4952,13 +4942,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170420</t>
+          <t>https://artportalen.se/Sighting/118341001</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127170500</v>
+        <v>127170375</v>
       </c>
       <c r="B36" t="n">
         <v>79327</v>
@@ -4988,18 +4978,22 @@
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Lövåsen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>363303</v>
+        <v>363314</v>
       </c>
       <c r="R36" t="n">
-        <v>6882872</v>
+        <v>6882815</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -5031,7 +5025,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5041,12 +5035,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Granar draperade med garnlav.</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5072,13 +5061,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170500</t>
+          <t>https://artportalen.se/Sighting/127170375</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127170642</v>
+        <v>127170420</v>
       </c>
       <c r="B37" t="n">
         <v>79327</v>
@@ -5108,11 +5097,7 @@
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5120,13 +5105,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>363306</v>
+        <v>363307</v>
       </c>
       <c r="R37" t="n">
-        <v>6882880</v>
+        <v>6882847</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5155,7 +5140,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5165,12 +5150,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Garnlavsdraperade granar.</t>
+          <t>Granar draperade med garnlav</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5196,13 +5181,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170642</t>
+          <t>https://artportalen.se/Sighting/127170420</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127170911</v>
+        <v>127170500</v>
       </c>
       <c r="B38" t="n">
         <v>79327</v>
@@ -5240,10 +5225,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>363318</v>
+        <v>363303</v>
       </c>
       <c r="R38" t="n">
-        <v>6882898</v>
+        <v>6882872</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -5275,7 +5260,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5285,12 +5270,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Draperade granar. Hotad fjällnära skog.</t>
+          <t>Granar draperade med garnlav.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5316,13 +5301,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170911</t>
+          <t>https://artportalen.se/Sighting/127170500</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127171152</v>
+        <v>127170642</v>
       </c>
       <c r="B39" t="n">
         <v>79327</v>
@@ -5364,10 +5349,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>363314</v>
+        <v>363306</v>
       </c>
       <c r="R39" t="n">
-        <v>6882905</v>
+        <v>6882880</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5399,7 +5384,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5409,7 +5394,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Garnlavsdraperade granar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5435,13 +5425,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127171152</t>
+          <t>https://artportalen.se/Sighting/127170642</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127171838</v>
+        <v>127170911</v>
       </c>
       <c r="B40" t="n">
         <v>79327</v>
@@ -5471,11 +5461,7 @@
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5483,13 +5469,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>363302</v>
+        <v>363318</v>
       </c>
       <c r="R40" t="n">
-        <v>6882938</v>
+        <v>6882898</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5518,7 +5504,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5528,7 +5514,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Draperade granar. Hotad fjällnära skog.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5554,13 +5545,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127171838</t>
+          <t>https://artportalen.se/Sighting/127170911</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127171879</v>
+        <v>127171152</v>
       </c>
       <c r="B41" t="n">
         <v>79327</v>
@@ -5590,7 +5581,11 @@
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5598,13 +5593,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>363287</v>
+        <v>363314</v>
       </c>
       <c r="R41" t="n">
-        <v>6882939</v>
+        <v>6882905</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5633,7 +5628,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5643,7 +5638,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5669,13 +5664,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127171879</t>
+          <t>https://artportalen.se/Sighting/127171152</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127172219</v>
+        <v>127171838</v>
       </c>
       <c r="B42" t="n">
         <v>79327</v>
@@ -5705,7 +5700,11 @@
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5713,13 +5712,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>363195</v>
+        <v>363302</v>
       </c>
       <c r="R42" t="n">
-        <v>6882944</v>
+        <v>6882938</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5748,7 +5747,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5758,7 +5757,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5784,13 +5783,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172219</t>
+          <t>https://artportalen.se/Sighting/127171838</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127172815</v>
+        <v>127171879</v>
       </c>
       <c r="B43" t="n">
         <v>79327</v>
@@ -5828,13 +5827,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>363204</v>
+        <v>363287</v>
       </c>
       <c r="R43" t="n">
-        <v>6882810</v>
+        <v>6882939</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5863,7 +5862,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5873,12 +5872,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:33</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Draperade granar</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5904,13 +5898,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172815</t>
+          <t>https://artportalen.se/Sighting/127171879</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127172852</v>
+        <v>127172219</v>
       </c>
       <c r="B44" t="n">
         <v>79327</v>
@@ -5948,13 +5942,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>363214</v>
+        <v>363195</v>
       </c>
       <c r="R44" t="n">
-        <v>6882814</v>
+        <v>6882944</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5983,7 +5977,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5993,12 +5987,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Garnlavsdraperade granar</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6024,13 +6013,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172852</t>
+          <t>https://artportalen.se/Sighting/127172219</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128820649</v>
+        <v>127172815</v>
       </c>
       <c r="B45" t="n">
         <v>79327</v>
@@ -6059,23 +6048,19 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>362222</v>
+        <v>363204</v>
       </c>
       <c r="R45" t="n">
-        <v>6882658</v>
+        <v>6882810</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -6102,22 +6087,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Draperade granar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6143,38 +6133,38 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128820649</t>
+          <t>https://artportalen.se/Sighting/127172815</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118118723</v>
+        <v>127172852</v>
       </c>
       <c r="B46" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6183,17 +6173,17 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>362344</v>
+        <v>363214</v>
       </c>
       <c r="R46" t="n">
-        <v>6882253</v>
+        <v>6882814</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6217,27 +6207,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Växer på stubbe av jättetall</t>
+          <t>Garnlavsdraperade granar</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6246,19 +6236,8 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Barrnaturskog. Fjällnära</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6274,16 +6253,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118723</t>
+          <t>https://artportalen.se/Sighting/127172852</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121898927</v>
+        <v>128820649</v>
       </c>
       <c r="B47" t="n">
-        <v>83305</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6291,37 +6270,44 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>363129</v>
+        <v>362222</v>
       </c>
       <c r="R47" t="n">
-        <v>6882975</v>
+        <v>6882658</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6345,22 +6331,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6375,27 +6361,27 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo, Cecilia Öster</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121898927</t>
+          <t>https://artportalen.se/Sighting/128820649</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118103394</v>
+        <v>118118723</v>
       </c>
       <c r="B48" t="n">
-        <v>57953</v>
+        <v>79946</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6403,42 +6389,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>362272</v>
+        <v>362344</v>
       </c>
       <c r="R48" t="n">
-        <v>6882099</v>
+        <v>6882253</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6465,27 +6446,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Färska hacksmärken på gran Grannaturskog</t>
+          <t>Växer på stubbe av jättetall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6494,6 +6475,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6504,7 +6486,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Grannaturskog</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6521,62 +6503,54 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118103394</t>
+          <t>https://artportalen.se/Sighting/118118723</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118103560</v>
+        <v>121898927</v>
       </c>
       <c r="B49" t="n">
-        <v>57953</v>
+        <v>83305</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>362276</v>
+        <v>363129</v>
       </c>
       <c r="R49" t="n">
-        <v>6882083</v>
+        <v>6882975</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6600,27 +6574,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färska hackmärken på gran i grannaturskog som är avverkningsanmäld.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6631,38 +6600,28 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Andreas Öster, Maria Hindemo, Cecilia Öster</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118103560</t>
+          <t>https://artportalen.se/Sighting/121898927</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118107736</v>
+        <v>118103394</v>
       </c>
       <c r="B50" t="n">
         <v>57953</v>
@@ -6701,14 +6660,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>362349</v>
+        <v>362272</v>
       </c>
       <c r="R50" t="n">
-        <v>6882279</v>
+        <v>6882099</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6740,7 +6699,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6750,12 +6709,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i naturskog.</t>
+          <t>Färska hacksmärken på gran Grannaturskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6774,7 +6733,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Mycket gamla granar och tallar</t>
+          <t>Grannaturskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6791,13 +6750,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118107736</t>
+          <t>https://artportalen.se/Sighting/118103394</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118113015</v>
+        <v>118103560</v>
       </c>
       <c r="B51" t="n">
         <v>57953</v>
@@ -6825,16 +6784,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -6844,10 +6799,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>362487</v>
+        <v>362276</v>
       </c>
       <c r="R51" t="n">
-        <v>6882179</v>
+        <v>6882083</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6874,27 +6829,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Hackmärken på gran i myrholme.</t>
+          <t>Färska hackmärken på gran i grannaturskog som är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6905,6 +6860,16 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6920,13 +6885,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118113015</t>
+          <t>https://artportalen.se/Sighting/118103560</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118113051</v>
+        <v>118107736</v>
       </c>
       <c r="B52" t="n">
         <v>57953</v>
@@ -6954,32 +6919,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>362482</v>
+        <v>362349</v>
       </c>
       <c r="R52" t="n">
-        <v>6882180</v>
+        <v>6882279</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7003,27 +6964,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Hackmärken gran på myrholme. Naturskog</t>
+          <t>Färska hackmärken på gran i naturskog.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7034,6 +6995,16 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Mycket gamla granar och tallar</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -7049,13 +7020,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118113051</t>
+          <t>https://artportalen.se/Sighting/118107736</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118118450</v>
+        <v>118113015</v>
       </c>
       <c r="B53" t="n">
         <v>57953</v>
@@ -7083,12 +7054,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -7098,10 +7073,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>362489</v>
+        <v>362487</v>
       </c>
       <c r="R53" t="n">
-        <v>6882203</v>
+        <v>6882179</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -7133,7 +7108,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7143,12 +7118,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Hackmärken på gran. Myrholme som är avverkningsanmäld</t>
+          <t>Hackmärken på gran i myrholme.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7159,16 +7134,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>Barrnaturskog. Lokalt fuktig miljö</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7184,13 +7149,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118450</t>
+          <t>https://artportalen.se/Sighting/118113015</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118118466</v>
+        <v>118113051</v>
       </c>
       <c r="B54" t="n">
         <v>57953</v>
@@ -7218,28 +7183,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>362421</v>
+        <v>362482</v>
       </c>
       <c r="R54" t="n">
-        <v>6882227</v>
+        <v>6882180</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7268,7 +7237,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7278,12 +7247,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska hackmärken på fertalet grannar på denna myrholme.</t>
+          <t>Hackmärken gran på myrholme. Naturskog</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7294,16 +7263,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>Barrnaturskog på myrholme</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7319,13 +7278,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118466</t>
+          <t>https://artportalen.se/Sighting/118113051</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118118547</v>
+        <v>118118450</v>
       </c>
       <c r="B55" t="n">
         <v>57953</v>
@@ -7358,20 +7317,20 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>362378</v>
+        <v>362489</v>
       </c>
       <c r="R55" t="n">
-        <v>6882297</v>
+        <v>6882203</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7403,7 +7362,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7413,12 +7372,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Äldre hackmärken på gammal gran i barrnaturskog.</t>
+          <t>Hackmärken på gran. Myrholme som är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7437,7 +7396,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Barrnaturskog. Lokalt fuktig miljö</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7454,13 +7413,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118547</t>
+          <t>https://artportalen.se/Sighting/118118450</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118118562</v>
+        <v>118118466</v>
       </c>
       <c r="B56" t="n">
         <v>57953</v>
@@ -7499,14 +7458,14 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>362373</v>
+        <v>362421</v>
       </c>
       <c r="R56" t="n">
-        <v>6882312</v>
+        <v>6882227</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7538,7 +7497,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7548,12 +7507,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Hackmärken på gammal gran i barrnaturskog. Skogen är avverkningsanmäld</t>
+          <t>Färska hackmärken på fertalet grannar på denna myrholme.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7572,7 +7531,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog på myrholme</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7589,13 +7548,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118562</t>
+          <t>https://artportalen.se/Sighting/118118466</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118118603</v>
+        <v>118118547</v>
       </c>
       <c r="B57" t="n">
         <v>57953</v>
@@ -7628,20 +7587,20 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>362381</v>
+        <v>362378</v>
       </c>
       <c r="R57" t="n">
-        <v>6882250</v>
+        <v>6882297</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7673,7 +7632,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7683,12 +7642,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gammal gran i barrnaturskog som avverkningsanmäld.</t>
+          <t>Äldre hackmärken på gammal gran i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7707,7 +7666,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7724,13 +7683,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118603</t>
+          <t>https://artportalen.se/Sighting/118118547</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118118863</v>
+        <v>118118562</v>
       </c>
       <c r="B58" t="n">
         <v>57953</v>
@@ -7773,10 +7732,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>362327</v>
+        <v>362373</v>
       </c>
       <c r="R58" t="n">
-        <v>6882265</v>
+        <v>6882312</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7808,7 +7767,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7818,12 +7777,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i barrnaturskog som är avverkningsanmäld</t>
+          <t>Hackmärken på gammal gran i barrnaturskog. Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7859,13 +7818,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118863</t>
+          <t>https://artportalen.se/Sighting/118118562</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118118905</v>
+        <v>118118603</v>
       </c>
       <c r="B59" t="n">
         <v>57953</v>
@@ -7898,20 +7857,20 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>362338</v>
+        <v>362381</v>
       </c>
       <c r="R59" t="n">
-        <v>6882298</v>
+        <v>6882250</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7958,7 +7917,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Hackmärken på gran i barrnaturskog</t>
+          <t>Färska hackmärken på gammal gran i barrnaturskog som avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7994,13 +7953,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118905</t>
+          <t>https://artportalen.se/Sighting/118118603</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118119133</v>
+        <v>118118863</v>
       </c>
       <c r="B60" t="n">
         <v>57953</v>
@@ -8043,10 +8002,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>362371</v>
+        <v>362327</v>
       </c>
       <c r="R60" t="n">
-        <v>6882362</v>
+        <v>6882265</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -8078,7 +8037,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8088,12 +8047,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Färska hackmärken på grov gammal gran. i barrnaturskog som är hotad av avverkning.</t>
+          <t>Färska hackmärken på gran i barrnaturskog som är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8129,13 +8088,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119133</t>
+          <t>https://artportalen.se/Sighting/118118863</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118119170</v>
+        <v>118118905</v>
       </c>
       <c r="B61" t="n">
         <v>57953</v>
@@ -8168,7 +8127,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -8178,10 +8137,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>362327</v>
+        <v>362338</v>
       </c>
       <c r="R61" t="n">
-        <v>6882360</v>
+        <v>6882298</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -8213,7 +8172,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8223,12 +8182,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Färska hackmärken på grov gammal gran i barrnaturskog. Avverkningsanmäld skog.</t>
+          <t>Hackmärken på gran i barrnaturskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8247,7 +8206,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Barrnatursk. Fjällnära</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8264,13 +8223,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119170</t>
+          <t>https://artportalen.se/Sighting/118118905</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118119483</v>
+        <v>118119133</v>
       </c>
       <c r="B62" t="n">
         <v>57953</v>
@@ -8313,10 +8272,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>362284</v>
+        <v>362371</v>
       </c>
       <c r="R62" t="n">
-        <v>6882318</v>
+        <v>6882362</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -8348,7 +8307,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8358,12 +8317,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i barrnaturskog.</t>
+          <t>Färska hackmärken på grov gammal gran. i barrnaturskog som är hotad av avverkning.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8399,13 +8358,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119483</t>
+          <t>https://artportalen.se/Sighting/118119133</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118119653</v>
+        <v>118119170</v>
       </c>
       <c r="B63" t="n">
         <v>57953</v>
@@ -8438,7 +8397,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -8448,10 +8407,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>362269</v>
+        <v>362327</v>
       </c>
       <c r="R63" t="n">
-        <v>6882324</v>
+        <v>6882360</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -8483,7 +8442,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8493,12 +8452,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Hackmärken på grov gran intill skidspår som går genom barrnaturskogen. Avverkningsanmäld skog.</t>
+          <t>Färska hackmärken på grov gammal gran i barrnaturskog. Avverkningsanmäld skog.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8517,7 +8476,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnatursk. Fjällnära</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8534,13 +8493,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119653</t>
+          <t>https://artportalen.se/Sighting/118119170</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118119701</v>
+        <v>118119483</v>
       </c>
       <c r="B64" t="n">
         <v>57953</v>
@@ -8583,10 +8542,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>362279</v>
+        <v>362284</v>
       </c>
       <c r="R64" t="n">
-        <v>6882363</v>
+        <v>6882318</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8618,7 +8577,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8628,12 +8587,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i barrnaturskog som hotas av avverkning</t>
+          <t>Färska hackmärken på gran i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8669,13 +8628,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119701</t>
+          <t>https://artportalen.se/Sighting/118119483</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118119770</v>
+        <v>118119653</v>
       </c>
       <c r="B65" t="n">
         <v>57953</v>
@@ -8708,7 +8667,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -8718,10 +8677,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>362240</v>
+        <v>362269</v>
       </c>
       <c r="R65" t="n">
-        <v>6882345</v>
+        <v>6882324</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8768,7 +8727,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gammal gran i barrnaturskog.</t>
+          <t>Hackmärken på grov gran intill skidspår som går genom barrnaturskogen. Avverkningsanmäld skog.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8804,13 +8763,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119770</t>
+          <t>https://artportalen.se/Sighting/118119653</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118119872</v>
+        <v>118119701</v>
       </c>
       <c r="B66" t="n">
         <v>57953</v>
@@ -8843,7 +8802,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -8853,10 +8812,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>362230</v>
+        <v>362279</v>
       </c>
       <c r="R66" t="n">
-        <v>6882332</v>
+        <v>6882363</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8888,7 +8847,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8898,7 +8857,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på gran i barrnaturskog som hotas av avverkning</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8934,13 +8898,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119872</t>
+          <t>https://artportalen.se/Sighting/118119701</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118120074</v>
+        <v>118119770</v>
       </c>
       <c r="B67" t="n">
         <v>57953</v>
@@ -8983,10 +8947,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>362243</v>
+        <v>362240</v>
       </c>
       <c r="R67" t="n">
-        <v>6882254</v>
+        <v>6882345</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -9018,7 +8982,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9028,12 +8992,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Färska och äldre hackmärken på gammal gran i barrnatuskog.</t>
+          <t>Färska hackmärken på gammal gran i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9069,13 +9033,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120074</t>
+          <t>https://artportalen.se/Sighting/118119770</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118120164</v>
+        <v>118119872</v>
       </c>
       <c r="B68" t="n">
         <v>57953</v>
@@ -9108,7 +9072,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -9118,10 +9082,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>362252</v>
+        <v>362230</v>
       </c>
       <c r="R68" t="n">
-        <v>6882248</v>
+        <v>6882332</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -9153,7 +9117,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9163,12 +9127,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Färska hackmärken på gran in barrnaturskog.</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9204,13 +9163,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120164</t>
+          <t>https://artportalen.se/Sighting/118119872</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118120248</v>
+        <v>118120074</v>
       </c>
       <c r="B69" t="n">
         <v>57953</v>
@@ -9253,10 +9212,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>362267</v>
+        <v>362243</v>
       </c>
       <c r="R69" t="n">
-        <v>6882224</v>
+        <v>6882254</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -9288,7 +9247,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9298,12 +9257,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Färska hackmärken i ett granbestånd. I avverkningsanmält skogsområe</t>
+          <t>Färska och äldre hackmärken på gammal gran i barrnatuskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9339,13 +9298,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120248</t>
+          <t>https://artportalen.se/Sighting/118120074</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118120388</v>
+        <v>118120164</v>
       </c>
       <c r="B70" t="n">
         <v>57953</v>
@@ -9378,7 +9337,7 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -9388,10 +9347,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>362196</v>
+        <v>362252</v>
       </c>
       <c r="R70" t="n">
-        <v>6882301</v>
+        <v>6882248</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9436,6 +9395,11 @@
           <t>15:30</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på gran in barrnaturskog.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -9452,7 +9416,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9469,13 +9433,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120388</t>
+          <t>https://artportalen.se/Sighting/118120164</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118120447</v>
+        <v>118120248</v>
       </c>
       <c r="B71" t="n">
         <v>57953</v>
@@ -9518,10 +9482,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>362200</v>
+        <v>362267</v>
       </c>
       <c r="R71" t="n">
-        <v>6882350</v>
+        <v>6882224</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9553,7 +9517,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9563,12 +9527,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Färska och äldre hackmärken på grov gran i barrnaturskog.</t>
+          <t>Färska hackmärken i ett granbestånd. I avverkningsanmält skogsområe</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9604,13 +9568,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120447</t>
+          <t>https://artportalen.se/Sighting/118120248</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118120506</v>
+        <v>118120388</v>
       </c>
       <c r="B72" t="n">
         <v>57953</v>
@@ -9653,10 +9617,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>362168</v>
+        <v>362196</v>
       </c>
       <c r="R72" t="n">
-        <v>6882359</v>
+        <v>6882301</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9688,7 +9652,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9698,12 +9662,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken på gammal gran med garnlav. I avverkningsanmäld barrnaturskog</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9722,7 +9681,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>Barrnaturskog.</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9739,13 +9698,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120506</t>
+          <t>https://artportalen.se/Sighting/118120388</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118122341</v>
+        <v>118120447</v>
       </c>
       <c r="B73" t="n">
         <v>57953</v>
@@ -9784,14 +9743,14 @@
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>362247</v>
+        <v>362200</v>
       </c>
       <c r="R73" t="n">
-        <v>6882178</v>
+        <v>6882350</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9818,27 +9777,27 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Hackmärken på tall i barrnaturskog.</t>
+          <t>Färska och äldre hackmärken på grov gran i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9857,7 +9816,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9874,13 +9833,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122341</t>
+          <t>https://artportalen.se/Sighting/118120447</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118122435</v>
+        <v>118120506</v>
       </c>
       <c r="B74" t="n">
         <v>57953</v>
@@ -9913,20 +9872,20 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>362276</v>
+        <v>362168</v>
       </c>
       <c r="R74" t="n">
-        <v>6882136</v>
+        <v>6882359</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9953,27 +9912,27 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i barrnaturskog</t>
+          <t>Äldre hackmärken på gammal gran med garnlav. I avverkningsanmäld barrnaturskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9992,7 +9951,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Barrnaturskog.</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10009,13 +9968,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122435</t>
+          <t>https://artportalen.se/Sighting/118120506</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118122458</v>
+        <v>118122341</v>
       </c>
       <c r="B75" t="n">
         <v>57953</v>
@@ -10058,10 +10017,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>362281</v>
+        <v>362247</v>
       </c>
       <c r="R75" t="n">
-        <v>6882135</v>
+        <v>6882178</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -10093,7 +10052,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10103,12 +10062,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i fin barrnaturskog som är avverkningsanmäld</t>
+          <t>Hackmärken på tall i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10144,13 +10103,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122458</t>
+          <t>https://artportalen.se/Sighting/118122341</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118122497</v>
+        <v>118122435</v>
       </c>
       <c r="B76" t="n">
         <v>57953</v>
@@ -10193,10 +10152,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>362283</v>
+        <v>362276</v>
       </c>
       <c r="R76" t="n">
-        <v>6882105</v>
+        <v>6882136</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -10228,7 +10187,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10238,12 +10197,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i avverkningsanmäld barrnaturskog</t>
+          <t>Färska hackmärken på gran i barrnaturskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10279,13 +10238,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122497</t>
+          <t>https://artportalen.se/Sighting/118122435</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118340481</v>
+        <v>118122458</v>
       </c>
       <c r="B77" t="n">
         <v>57953</v>
@@ -10328,10 +10287,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>362275</v>
+        <v>362281</v>
       </c>
       <c r="R77" t="n">
-        <v>6882133</v>
+        <v>6882135</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -10358,27 +10317,27 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i fjällnära skog.</t>
+          <t>Färska hackmärken på gran i fin barrnaturskog som är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10397,7 +10356,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10414,13 +10373,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340481</t>
+          <t>https://artportalen.se/Sighting/118122458</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118340595</v>
+        <v>118122497</v>
       </c>
       <c r="B78" t="n">
         <v>57953</v>
@@ -10463,10 +10422,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>362281</v>
+        <v>362283</v>
       </c>
       <c r="R78" t="n">
-        <v>6882106</v>
+        <v>6882105</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -10493,27 +10452,27 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>färska hackmärken på gatan. Fjällnära skog</t>
+          <t>Färska hackmärken på gran i avverkningsanmäld barrnaturskog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10532,7 +10491,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10549,13 +10508,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340595</t>
+          <t>https://artportalen.se/Sighting/118122497</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118340691</v>
+        <v>118340481</v>
       </c>
       <c r="B79" t="n">
         <v>57953</v>
@@ -10598,13 +10557,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>362270</v>
+        <v>362275</v>
       </c>
       <c r="R79" t="n">
-        <v>6882100</v>
+        <v>6882133</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10648,7 +10607,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i fjällnära skog</t>
+          <t>Färska hackmärken på gran i fjällnära skog.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10684,13 +10643,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340691</t>
+          <t>https://artportalen.se/Sighting/118340481</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118340748</v>
+        <v>118340595</v>
       </c>
       <c r="B80" t="n">
         <v>57953</v>
@@ -10733,10 +10692,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>362272</v>
+        <v>362281</v>
       </c>
       <c r="R80" t="n">
-        <v>6882086</v>
+        <v>6882106</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10783,7 +10742,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>färska hackmnärken på gran i naturskog. Fjällnära</t>
+          <t>färska hackmärken på gatan. Fjällnära skog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10819,13 +10778,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340748</t>
+          <t>https://artportalen.se/Sighting/118340595</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118340920</v>
+        <v>118340691</v>
       </c>
       <c r="B81" t="n">
         <v>57953</v>
@@ -10864,17 +10823,17 @@
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>362284</v>
+        <v>362270</v>
       </c>
       <c r="R81" t="n">
-        <v>6882361</v>
+        <v>6882100</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10918,7 +10877,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Färska och äldre hackmärken. Skogen är avverkningsanmäld. Gran med hackmärken inom anmälan. Se bild</t>
+          <t>Färska hackmärken på gran i fjällnära skog</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10937,7 +10896,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10954,13 +10913,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340920</t>
+          <t>https://artportalen.se/Sighting/118340691</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121206319</v>
+        <v>118340748</v>
       </c>
       <c r="B82" t="n">
         <v>57953</v>
@@ -10989,19 +10948,27 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>363246</v>
+        <v>362272</v>
       </c>
       <c r="R82" t="n">
-        <v>6883004</v>
+        <v>6882086</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -11025,22 +10992,27 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>färska hackmnärken på gran i naturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11051,28 +11023,38 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121206319</t>
+          <t>https://artportalen.se/Sighting/118340748</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127170971</v>
+        <v>118340920</v>
       </c>
       <c r="B83" t="n">
         <v>57953</v>
@@ -11100,32 +11082,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>363315</v>
+        <v>362284</v>
       </c>
       <c r="R83" t="n">
-        <v>6882898</v>
+        <v>6882361</v>
       </c>
       <c r="S83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -11149,22 +11127,27 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken. Skogen är avverkningsanmäld. Gran med hackmärken inom anmälan. Se bild</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11175,6 +11158,16 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>barrnaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -11190,13 +11183,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170971</t>
+          <t>https://artportalen.se/Sighting/118340920</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127172142</v>
+        <v>121206319</v>
       </c>
       <c r="B84" t="n">
         <v>57953</v>
@@ -11224,32 +11217,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>363196</v>
+        <v>363246</v>
       </c>
       <c r="R84" t="n">
-        <v>6882950</v>
+        <v>6883004</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11273,27 +11254,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackmärken.</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11308,24 +11284,24 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172142</t>
+          <t>https://artportalen.se/Sighting/121206319</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127172737</v>
+        <v>127170971</v>
       </c>
       <c r="B85" t="n">
         <v>57953</v>
@@ -11372,10 +11348,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>363143</v>
+        <v>363315</v>
       </c>
       <c r="R85" t="n">
-        <v>6882797</v>
+        <v>6882898</v>
       </c>
       <c r="S85" t="n">
         <v>4</v>
@@ -11407,7 +11383,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11417,7 +11393,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11443,13 +11419,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172737</t>
+          <t>https://artportalen.se/Sighting/127170971</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127172795</v>
+        <v>127172142</v>
       </c>
       <c r="B86" t="n">
         <v>57953</v>
@@ -11496,13 +11472,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>363188</v>
+        <v>363196</v>
       </c>
       <c r="R86" t="n">
-        <v>6882809</v>
+        <v>6882950</v>
       </c>
       <c r="S86" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -11531,7 +11507,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11541,12 +11517,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Färska och äldre hackmärken</t>
+          <t>Färska och äldre hackmärken.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11572,13 +11548,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172795</t>
+          <t>https://artportalen.se/Sighting/127172142</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127172899</v>
+        <v>127172737</v>
       </c>
       <c r="B87" t="n">
         <v>57953</v>
@@ -11625,13 +11601,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>363234</v>
+        <v>363143</v>
       </c>
       <c r="R87" t="n">
-        <v>6882800</v>
+        <v>6882797</v>
       </c>
       <c r="S87" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11660,7 +11636,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11670,7 +11646,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11696,13 +11672,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172899</t>
+          <t>https://artportalen.se/Sighting/127172737</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127315676</v>
+        <v>127172795</v>
       </c>
       <c r="B88" t="n">
         <v>57953</v>
@@ -11732,42 +11708,30 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>363122</v>
+        <v>363188</v>
       </c>
       <c r="R88" t="n">
-        <v>6882946</v>
+        <v>6882809</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11791,22 +11755,27 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11821,24 +11790,24 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127315676</t>
+          <t>https://artportalen.se/Sighting/127172795</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128822185</v>
+        <v>127172899</v>
       </c>
       <c r="B89" t="n">
         <v>57953</v>
@@ -11878,24 +11847,20 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>362326</v>
+        <v>363234</v>
       </c>
       <c r="R89" t="n">
-        <v>6882768</v>
+        <v>6882800</v>
       </c>
       <c r="S89" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11919,22 +11884,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11960,13 +11925,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128822185</t>
+          <t>https://artportalen.se/Sighting/127172899</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128822490</v>
+        <v>127315676</v>
       </c>
       <c r="B90" t="n">
         <v>57953</v>
@@ -11996,14 +11961,22 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -12013,17 +11986,17 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>362260</v>
+        <v>363122</v>
       </c>
       <c r="R90" t="n">
-        <v>6882421</v>
+        <v>6882946</v>
       </c>
       <c r="S90" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -12047,22 +12020,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -12077,24 +12050,24 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Marcus Hansson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Marcus Hansson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128822490</t>
+          <t>https://artportalen.se/Sighting/127315676</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128822499</v>
+        <v>128822185</v>
       </c>
       <c r="B91" t="n">
         <v>57953</v>
@@ -12134,20 +12107,24 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>362273</v>
+        <v>362326</v>
       </c>
       <c r="R91" t="n">
-        <v>6882421</v>
+        <v>6882768</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -12176,7 +12153,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -12186,7 +12163,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12212,63 +12189,70 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128822499</t>
+          <t>https://artportalen.se/Sighting/128822185</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118122325</v>
+        <v>128822490</v>
       </c>
       <c r="B92" t="n">
-        <v>5179</v>
+        <v>57953</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>362234</v>
+        <v>362260</v>
       </c>
       <c r="R92" t="n">
-        <v>6882185</v>
+        <v>6882421</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -12292,27 +12276,22 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>På torrgran vid myrknat intill barrnaturskog</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12321,19 +12300,8 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>Myrmark intill barrnaturskog</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -12349,16 +12317,16 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122325</t>
+          <t>https://artportalen.se/Sighting/128822490</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127315773</v>
+        <v>128822499</v>
       </c>
       <c r="B93" t="n">
-        <v>58057</v>
+        <v>57953</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12366,16 +12334,16 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -12385,37 +12353,30 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>363120</v>
+        <v>362273</v>
       </c>
       <c r="R93" t="n">
-        <v>6882934</v>
+        <v>6882421</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -12439,22 +12400,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12469,77 +12430,74 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127315773</t>
+          <t>https://artportalen.se/Sighting/128822499</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128820534</v>
+        <v>118122325</v>
       </c>
       <c r="B94" t="n">
-        <v>58057</v>
+        <v>5179</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103031</v>
+        <v>100526</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>362267</v>
+        <v>362234</v>
       </c>
       <c r="R94" t="n">
-        <v>6882595</v>
+        <v>6882185</v>
       </c>
       <c r="S94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12563,22 +12521,27 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>På torrgran vid myrknat intill barrnaturskog</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12587,8 +12550,19 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>Myrmark intill barrnaturskog</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -12604,58 +12578,73 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128820534</t>
+          <t>https://artportalen.se/Sighting/118122325</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118122289</v>
+        <v>127315773</v>
       </c>
       <c r="B95" t="n">
-        <v>99035</v>
+        <v>58057</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>219790</v>
+        <v>103031</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>362232</v>
+        <v>363120</v>
       </c>
       <c r="R95" t="n">
-        <v>6882193</v>
+        <v>6882934</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12679,22 +12668,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12703,86 +12692,83 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>Barrnaturskog vid myrkant</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Marcus Hansson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Marcus Hansson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122289</t>
+          <t>https://artportalen.se/Sighting/127315773</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118118517</v>
+        <v>128820534</v>
       </c>
       <c r="B96" t="n">
-        <v>97983</v>
+        <v>58057</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221945</v>
+        <v>103031</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>362380</v>
+        <v>362267</v>
       </c>
       <c r="R96" t="n">
-        <v>6882294</v>
+        <v>6882595</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12806,27 +12792,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Växer under gamla granar i barrnaturskog. Fuktig miljö.</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12835,19 +12816,8 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -12863,16 +12833,16 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118517</t>
+          <t>https://artportalen.se/Sighting/128820534</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118118821</v>
+        <v>118122289</v>
       </c>
       <c r="B97" t="n">
-        <v>97983</v>
+        <v>99035</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12880,21 +12850,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -12908,10 +12878,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>362339</v>
+        <v>362232</v>
       </c>
       <c r="R97" t="n">
-        <v>6882268</v>
+        <v>6882193</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -12938,27 +12908,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Växer på en stor yta under gamla granar i barrnaturskog</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12978,7 +12943,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog vid myrkant</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -12995,13 +12960,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118821</t>
+          <t>https://artportalen.se/Sighting/118122289</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118119084</v>
+        <v>118118517</v>
       </c>
       <c r="B98" t="n">
         <v>97983</v>
@@ -13040,10 +13005,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>362369</v>
+        <v>362380</v>
       </c>
       <c r="R98" t="n">
-        <v>6882345</v>
+        <v>6882294</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -13075,7 +13040,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -13085,7 +13050,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Växer under gamla granar i barrnaturskog. Fuktig miljö.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13105,7 +13075,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>Grannaturskog. Fjällnära</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -13122,13 +13092,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119084</t>
+          <t>https://artportalen.se/Sighting/118118517</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127171558</v>
+        <v>118118821</v>
       </c>
       <c r="B99" t="n">
         <v>97983</v>
@@ -13163,17 +13133,17 @@
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>363325</v>
+        <v>362339</v>
       </c>
       <c r="R99" t="n">
-        <v>6882909</v>
+        <v>6882268</v>
       </c>
       <c r="S99" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -13197,22 +13167,27 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Växer på en stor yta under gamla granar i barrnaturskog</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13221,8 +13196,19 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -13238,13 +13224,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127171558</t>
+          <t>https://artportalen.se/Sighting/118118821</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127172203</v>
+        <v>118119084</v>
       </c>
       <c r="B100" t="n">
         <v>97983</v>
@@ -13279,17 +13265,17 @@
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>363195</v>
+        <v>362369</v>
       </c>
       <c r="R100" t="n">
-        <v>6882944</v>
+        <v>6882345</v>
       </c>
       <c r="S100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -13313,22 +13299,22 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13337,8 +13323,19 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>Grannaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -13354,13 +13351,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172203</t>
+          <t>https://artportalen.se/Sighting/118119084</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127172331</v>
+        <v>127171558</v>
       </c>
       <c r="B101" t="n">
         <v>97983</v>
@@ -13399,10 +13396,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>363170</v>
+        <v>363325</v>
       </c>
       <c r="R101" t="n">
-        <v>6882973</v>
+        <v>6882909</v>
       </c>
       <c r="S101" t="n">
         <v>4</v>
@@ -13434,7 +13431,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -13444,7 +13441,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13470,13 +13467,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172331</t>
+          <t>https://artportalen.se/Sighting/127171558</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128820515</v>
+        <v>127172203</v>
       </c>
       <c r="B102" t="n">
         <v>97983</v>
@@ -13508,21 +13505,17 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>362287</v>
+        <v>363195</v>
       </c>
       <c r="R102" t="n">
-        <v>6882523</v>
+        <v>6882944</v>
       </c>
       <c r="S102" t="n">
         <v>4</v>
@@ -13549,22 +13542,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13589,6 +13582,242 @@
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172203</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>127172331</v>
+      </c>
+      <c r="B103" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Kerstibygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>363170</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6882973</v>
+      </c>
+      <c r="S103" t="n">
+        <v>4</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172331</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>128820515</v>
+      </c>
+      <c r="B104" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Kokällmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>362287</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6882523</v>
+      </c>
+      <c r="S104" t="n">
+        <v>4</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128820515</t>
         </is>
@@ -13697,6 +13926,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135621906</v>
       </c>
       <c r="B3" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>135622151</v>
       </c>
       <c r="B4" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>135621366</v>
       </c>
       <c r="B12" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>135621791</v>
       </c>
       <c r="B13" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>135621801</v>
       </c>
       <c r="B16" t="n">
-        <v>92482</v>
+        <v>92496</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>135621229</v>
       </c>
       <c r="B19" t="n">
-        <v>92405</v>
+        <v>92417</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135621906</v>
       </c>
       <c r="B3" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>135622151</v>
       </c>
       <c r="B4" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>135621366</v>
       </c>
       <c r="B12" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>135621791</v>
       </c>
       <c r="B13" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>135621801</v>
       </c>
       <c r="B16" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>135621229</v>
       </c>
       <c r="B19" t="n">
-        <v>92417</v>
+        <v>92418</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135621906</v>
       </c>
       <c r="B3" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>135622151</v>
       </c>
       <c r="B4" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>135621791</v>
       </c>
       <c r="B13" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>135621801</v>
       </c>
       <c r="B16" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>135621229</v>
       </c>
       <c r="B19" t="n">
-        <v>92418</v>
+        <v>92419</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135621906</v>
       </c>
       <c r="B3" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>135622151</v>
       </c>
       <c r="B4" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>135621366</v>
       </c>
       <c r="B12" t="n">
-        <v>79523</v>
+        <v>79524</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>135621791</v>
       </c>
       <c r="B13" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>135621801</v>
       </c>
       <c r="B16" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>135621229</v>
       </c>
       <c r="B19" t="n">
-        <v>92419</v>
+        <v>92420</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -1866,7 +1866,7 @@
         <v>135621366</v>
       </c>
       <c r="B12" t="n">
-        <v>79524</v>
+        <v>79528</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>135621229</v>
       </c>
       <c r="B19" t="n">
-        <v>92420</v>
+        <v>92426</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -1866,7 +1866,7 @@
         <v>135621366</v>
       </c>
       <c r="B12" t="n">
-        <v>79528</v>
+        <v>79529</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>135621229</v>
       </c>
       <c r="B19" t="n">
-        <v>92426</v>
+        <v>92427</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -1866,7 +1866,7 @@
         <v>135621366</v>
       </c>
       <c r="B12" t="n">
-        <v>79529</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>135621229</v>
       </c>
       <c r="B19" t="n">
-        <v>92427</v>
+        <v>92433</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -1866,7 +1866,7 @@
         <v>135621366</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>135621229</v>
       </c>
       <c r="B19" t="n">
-        <v>92433</v>
+        <v>92440</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ104"/>
+  <dimension ref="A1:AZ107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2199,32 +2199,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121206216</v>
+        <v>136420582</v>
       </c>
       <c r="B15" t="n">
-        <v>92369</v>
+        <v>92101</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2234,13 +2234,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>363227</v>
+        <v>363014</v>
       </c>
       <c r="R15" t="n">
-        <v>6882956</v>
+        <v>6882849</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2264,22 +2264,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:07</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:07</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På äldre låga, myrkant</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,27 +2289,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Erik Göthlin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Erik Göthlin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121206216</t>
+          <t>https://artportalen.se/Sighting/136420582</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135621801</v>
+        <v>121206216</v>
       </c>
       <c r="B16" t="n">
-        <v>92499</v>
+        <v>92369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2346,13 +2341,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>362649</v>
+        <v>363227</v>
       </c>
       <c r="R16" t="n">
-        <v>6882777</v>
+        <v>6882956</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2376,22 +2371,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,27 +2401,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Carl Wiking</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carl Wiking</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135621801</t>
+          <t>https://artportalen.se/Sighting/121206216</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121206277</v>
+        <v>135621801</v>
       </c>
       <c r="B17" t="n">
-        <v>83173</v>
+        <v>92499</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2434,21 +2429,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2458,13 +2453,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>363227</v>
+        <v>362649</v>
       </c>
       <c r="R17" t="n">
-        <v>6882956</v>
+        <v>6882777</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2488,22 +2483,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2518,72 +2513,65 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121206277</t>
+          <t>https://artportalen.se/Sighting/135621801</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118112482</v>
+        <v>121206277</v>
       </c>
       <c r="B18" t="n">
-        <v>92083</v>
+        <v>83173</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1503</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>362476</v>
+        <v>363227</v>
       </c>
       <c r="R18" t="n">
-        <v>6882192</v>
+        <v>6882956</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2607,27 +2595,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Växer under gammal gren från jättetall på myrholme. Skogen är avverkningsanmäld</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2636,34 +2619,33 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118112482</t>
+          <t>https://artportalen.se/Sighting/121206277</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135621229</v>
+        <v>118112482</v>
       </c>
       <c r="B19" t="n">
-        <v>92440</v>
+        <v>92083</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2671,37 +2653,44 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1506</v>
+        <v>1503</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Öretjärnbäcken, Dlr</t>
+          <t>Sälderbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>362586</v>
+        <v>362476</v>
       </c>
       <c r="R19" t="n">
-        <v>6882774</v>
+        <v>6882192</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2725,107 +2714,101 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Doftar inte så mycket. Tror det beror på att årets fruktkroppar inte är så utvecklade. Bör kollas upp lite senare.</t>
+          <t>Växer under gammal gren från jättetall på myrholme. Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Carl Wiking</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Carl Wiking</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135621229</t>
+          <t>https://artportalen.se/Sighting/118112482</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118340526</v>
+        <v>135621229</v>
       </c>
       <c r="B20" t="n">
-        <v>91831</v>
+        <v>92440</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3242</v>
+        <v>1506</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Öretjärnbäcken, Öretjärnbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>362269</v>
+        <v>362586</v>
       </c>
       <c r="R20" t="n">
-        <v>6882132</v>
+        <v>6882774</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2849,85 +2832,59 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Växer på undersida av tallgren från gammal tall. Fjällnära skog.</t>
+          <t>Doftar inte så mycket. Tror det beror på att årets fruktkroppar inte är så utvecklade. Bör kollas upp lite senare.</t>
         </is>
       </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Barrnaturskog. Fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340526</t>
+          <t>https://artportalen.se/Sighting/135621229</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121206393</v>
+        <v>118340526</v>
       </c>
       <c r="B21" t="n">
         <v>91831</v>
@@ -2956,19 +2913,26 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>363237</v>
+        <v>362269</v>
       </c>
       <c r="R21" t="n">
-        <v>6883017</v>
+        <v>6882132</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2992,22 +2956,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Växer på undersida av tallgren från gammal tall. Fjällnära skog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3016,9 +2985,20 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
+      </c>
       <c r="AJ21" t="inlineStr">
         <is>
           <t>tall</t>
@@ -3029,62 +3009,57 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Dead branch  # Pinus sylvestris</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121206393</t>
+          <t>https://artportalen.se/Sighting/118340526</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121206160</v>
+        <v>121206393</v>
       </c>
       <c r="B22" t="n">
-        <v>92632</v>
+        <v>91831</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3298</v>
+        <v>3242</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3094,10 +3069,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>363153</v>
+        <v>363237</v>
       </c>
       <c r="R22" t="n">
-        <v>6882853</v>
+        <v>6883017</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3129,7 +3104,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3139,7 +3114,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3153,22 +3128,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Dead branch  # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3185,61 +3160,54 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121206160</t>
+          <t>https://artportalen.se/Sighting/121206393</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>110444488</v>
+        <v>121206160</v>
       </c>
       <c r="B23" t="n">
-        <v>79327</v>
+        <v>92632</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lövåsen, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>363277</v>
+        <v>363153</v>
       </c>
       <c r="R23" t="n">
-        <v>6882948</v>
+        <v>6882853</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3263,27 +3231,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ymnig förekomst av garnlav i fin grannaturskog. Granar draperade av laven. På grov gran garnlav med soral.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3292,20 +3255,9 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
-      </c>
       <c r="AJ23" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3316,32 +3268,37 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110444488</t>
+          <t>https://artportalen.se/Sighting/121206160</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>110513997</v>
+        <v>110444488</v>
       </c>
       <c r="B24" t="n">
         <v>79327</v>
@@ -3373,23 +3330,23 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lövåsen , Dlr</t>
+          <t>Lövåsen, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>363288</v>
+        <v>363277</v>
       </c>
       <c r="R24" t="n">
-        <v>6882833</v>
+        <v>6882948</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3413,22 +3370,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ymnig förekomst av garnlav i fin grannaturskog. Granar draperade av laven. På grov gran garnlav med soral.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3437,8 +3399,34 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3454,13 +3442,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110513997</t>
+          <t>https://artportalen.se/Sighting/110444488</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>110514177</v>
+        <v>110513997</v>
       </c>
       <c r="B25" t="n">
         <v>79327</v>
@@ -3502,13 +3490,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>363305</v>
+        <v>363288</v>
       </c>
       <c r="R25" t="n">
         <v>6882833</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3537,7 +3525,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3547,7 +3535,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3573,13 +3561,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110514177</t>
+          <t>https://artportalen.se/Sighting/110513997</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>110514236</v>
+        <v>110514177</v>
       </c>
       <c r="B26" t="n">
         <v>79327</v>
@@ -3621,10 +3609,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>363313</v>
+        <v>363305</v>
       </c>
       <c r="R26" t="n">
-        <v>6882881</v>
+        <v>6882833</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3656,7 +3644,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3666,7 +3654,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3692,13 +3680,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110514236</t>
+          <t>https://artportalen.se/Sighting/110514177</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118103637</v>
+        <v>110514236</v>
       </c>
       <c r="B27" t="n">
         <v>79327</v>
@@ -3728,18 +3716,22 @@
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Lövåsen , Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>362276</v>
+        <v>363313</v>
       </c>
       <c r="R27" t="n">
-        <v>6882072</v>
+        <v>6882881</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3766,27 +3758,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Växer på gran i naturskog.</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3795,34 +3782,8 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3838,13 +3799,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118103637</t>
+          <t>https://artportalen.se/Sighting/110514236</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118103682</v>
+        <v>118103637</v>
       </c>
       <c r="B28" t="n">
         <v>79327</v>
@@ -3873,11 +3834,7 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3886,10 +3843,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>362257</v>
+        <v>362276</v>
       </c>
       <c r="R28" t="n">
-        <v>6882084</v>
+        <v>6882072</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3936,7 +3893,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Växer på gammal gran i avverkningsanmäld skog.</t>
+          <t>Växer på gran i naturskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3988,13 +3945,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118103682</t>
+          <t>https://artportalen.se/Sighting/118103637</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118103868</v>
+        <v>118103682</v>
       </c>
       <c r="B29" t="n">
         <v>79327</v>
@@ -4023,7 +3980,11 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
@@ -4032,10 +3993,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>362279</v>
+        <v>362257</v>
       </c>
       <c r="R29" t="n">
-        <v>6882106</v>
+        <v>6882084</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4067,7 +4028,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4077,7 +4038,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Växer på gammal gran i avverkningsanmäld skog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4100,6 +4066,21 @@
           <t>Grannaturskog</t>
         </is>
       </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
@@ -4114,13 +4095,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118103868</t>
+          <t>https://artportalen.se/Sighting/118103682</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118108025</v>
+        <v>118103868</v>
       </c>
       <c r="B30" t="n">
         <v>79327</v>
@@ -4149,11 +4130,7 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
@@ -4162,10 +4139,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>362343</v>
+        <v>362279</v>
       </c>
       <c r="R30" t="n">
-        <v>6882273</v>
+        <v>6882106</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4197,7 +4174,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4207,7 +4184,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4227,7 +4204,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Grannaturskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4244,13 +4221,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118108025</t>
+          <t>https://artportalen.se/Sighting/118103868</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118108207</v>
+        <v>118108025</v>
       </c>
       <c r="B31" t="n">
         <v>79327</v>
@@ -4292,10 +4269,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>362326</v>
+        <v>362343</v>
       </c>
       <c r="R31" t="n">
-        <v>6882154</v>
+        <v>6882273</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4327,7 +4304,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4337,12 +4314,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Naturskog med riklig förekomst av garnlav</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4362,7 +4334,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Gammelgranskog</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4379,13 +4351,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118108207</t>
+          <t>https://artportalen.se/Sighting/118108025</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118112682</v>
+        <v>118108207</v>
       </c>
       <c r="B32" t="n">
         <v>79327</v>
@@ -4423,14 +4395,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>362476</v>
+        <v>362326</v>
       </c>
       <c r="R32" t="n">
-        <v>6882192</v>
+        <v>6882154</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4457,27 +4429,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Växer i granbestånd på myrholme</t>
+          <t>Naturskog med riklig förekomst av garnlav</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4486,8 +4458,19 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Gammelgranskog</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4503,13 +4486,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118112682</t>
+          <t>https://artportalen.se/Sighting/118108207</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118118581</v>
+        <v>118112682</v>
       </c>
       <c r="B33" t="n">
         <v>79327</v>
@@ -4547,14 +4530,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>362380</v>
+        <v>362476</v>
       </c>
       <c r="R33" t="n">
-        <v>6882318</v>
+        <v>6882192</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4586,7 +4569,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4596,12 +4579,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Riklig förekomst av garnlav i grannaturskog.</t>
+          <t>Växer i granbestånd på myrholme</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4610,34 +4593,8 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Barrnaturskog. Fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4653,13 +4610,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118581</t>
+          <t>https://artportalen.se/Sighting/118112682</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118119303</v>
+        <v>118118581</v>
       </c>
       <c r="B34" t="n">
         <v>79327</v>
@@ -4701,10 +4658,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>362310</v>
+        <v>362380</v>
       </c>
       <c r="R34" t="n">
-        <v>6882298</v>
+        <v>6882318</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4736,7 +4693,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4746,12 +4703,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Väldigt långa bålar och i granbeståndet flera draperade av garnlav.</t>
+          <t>Riklig förekomst av garnlav i grannaturskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4774,6 +4731,21 @@
           <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
@@ -4788,13 +4760,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119303</t>
+          <t>https://artportalen.se/Sighting/118118581</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118341001</v>
+        <v>118119303</v>
       </c>
       <c r="B35" t="n">
         <v>79327</v>
@@ -4828,11 +4800,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4840,10 +4808,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>362320</v>
+        <v>362310</v>
       </c>
       <c r="R35" t="n">
-        <v>6882282</v>
+        <v>6882298</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4870,27 +4838,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Granar draperade med garnlav.</t>
+          <t>Väldigt långa bålar och i granbeståndet flera draperade av garnlav.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4913,21 +4881,6 @@
           <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
@@ -4942,13 +4895,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118341001</t>
+          <t>https://artportalen.se/Sighting/118119303</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127170375</v>
+        <v>118341001</v>
       </c>
       <c r="B36" t="n">
         <v>79327</v>
@@ -4977,7 +4930,11 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>med apothecier</t>
@@ -4986,17 +4943,17 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lövåsen, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>363314</v>
+        <v>362320</v>
       </c>
       <c r="R36" t="n">
-        <v>6882815</v>
+        <v>6882282</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5020,22 +4977,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Granar draperade med garnlav.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5044,8 +5006,34 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5061,13 +5049,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170375</t>
+          <t>https://artportalen.se/Sighting/118341001</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127170420</v>
+        <v>127170375</v>
       </c>
       <c r="B37" t="n">
         <v>79327</v>
@@ -5097,21 +5085,25 @@
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Lövåsen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>363307</v>
+        <v>363314</v>
       </c>
       <c r="R37" t="n">
-        <v>6882847</v>
+        <v>6882815</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5140,7 +5132,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5150,12 +5142,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:31</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Granar draperade med garnlav</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5181,13 +5168,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170420</t>
+          <t>https://artportalen.se/Sighting/127170375</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127170500</v>
+        <v>127170420</v>
       </c>
       <c r="B38" t="n">
         <v>79327</v>
@@ -5225,13 +5212,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>363303</v>
+        <v>363307</v>
       </c>
       <c r="R38" t="n">
-        <v>6882872</v>
+        <v>6882847</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5260,7 +5247,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5270,12 +5257,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Granar draperade med garnlav.</t>
+          <t>Granar draperade med garnlav</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5301,13 +5288,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170500</t>
+          <t>https://artportalen.se/Sighting/127170420</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127170642</v>
+        <v>127170500</v>
       </c>
       <c r="B39" t="n">
         <v>79327</v>
@@ -5337,11 +5324,7 @@
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5349,10 +5332,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>363306</v>
+        <v>363303</v>
       </c>
       <c r="R39" t="n">
-        <v>6882880</v>
+        <v>6882872</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5384,7 +5367,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5394,12 +5377,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Garnlavsdraperade granar.</t>
+          <t>Granar draperade med garnlav.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5425,13 +5408,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170642</t>
+          <t>https://artportalen.se/Sighting/127170500</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127170911</v>
+        <v>127170642</v>
       </c>
       <c r="B40" t="n">
         <v>79327</v>
@@ -5461,7 +5444,11 @@
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5469,10 +5456,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>363318</v>
+        <v>363306</v>
       </c>
       <c r="R40" t="n">
-        <v>6882898</v>
+        <v>6882880</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5504,7 +5491,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5514,12 +5501,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Draperade granar. Hotad fjällnära skog.</t>
+          <t>Garnlavsdraperade granar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5545,13 +5532,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170911</t>
+          <t>https://artportalen.se/Sighting/127170642</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127171152</v>
+        <v>127170911</v>
       </c>
       <c r="B41" t="n">
         <v>79327</v>
@@ -5581,11 +5568,7 @@
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5593,10 +5576,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>363314</v>
+        <v>363318</v>
       </c>
       <c r="R41" t="n">
-        <v>6882905</v>
+        <v>6882898</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5628,7 +5611,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5638,7 +5621,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Draperade granar. Hotad fjällnära skog.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5664,13 +5652,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127171152</t>
+          <t>https://artportalen.se/Sighting/127170911</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127171838</v>
+        <v>127171152</v>
       </c>
       <c r="B42" t="n">
         <v>79327</v>
@@ -5712,13 +5700,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>363302</v>
+        <v>363314</v>
       </c>
       <c r="R42" t="n">
-        <v>6882938</v>
+        <v>6882905</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5747,7 +5735,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5757,7 +5745,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5783,13 +5771,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127171838</t>
+          <t>https://artportalen.se/Sighting/127171152</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127171879</v>
+        <v>127171838</v>
       </c>
       <c r="B43" t="n">
         <v>79327</v>
@@ -5819,7 +5807,11 @@
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5827,10 +5819,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>363287</v>
+        <v>363302</v>
       </c>
       <c r="R43" t="n">
-        <v>6882939</v>
+        <v>6882938</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5862,7 +5854,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5872,7 +5864,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5898,13 +5890,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127171879</t>
+          <t>https://artportalen.se/Sighting/127171838</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127172219</v>
+        <v>127171879</v>
       </c>
       <c r="B44" t="n">
         <v>79327</v>
@@ -5942,13 +5934,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>363195</v>
+        <v>363287</v>
       </c>
       <c r="R44" t="n">
-        <v>6882944</v>
+        <v>6882939</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5977,7 +5969,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5987,7 +5979,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6013,13 +6005,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172219</t>
+          <t>https://artportalen.se/Sighting/127171879</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127172815</v>
+        <v>127172219</v>
       </c>
       <c r="B45" t="n">
         <v>79327</v>
@@ -6057,10 +6049,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>363204</v>
+        <v>363195</v>
       </c>
       <c r="R45" t="n">
-        <v>6882810</v>
+        <v>6882944</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -6092,7 +6084,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6102,12 +6094,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:33</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Draperade granar</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6133,13 +6120,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172815</t>
+          <t>https://artportalen.se/Sighting/127172219</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127172852</v>
+        <v>127172815</v>
       </c>
       <c r="B46" t="n">
         <v>79327</v>
@@ -6177,13 +6164,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>363214</v>
+        <v>363204</v>
       </c>
       <c r="R46" t="n">
-        <v>6882814</v>
+        <v>6882810</v>
       </c>
       <c r="S46" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6212,7 +6199,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6222,12 +6209,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Garnlavsdraperade granar</t>
+          <t>Draperade granar</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6253,13 +6240,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172852</t>
+          <t>https://artportalen.se/Sighting/127172815</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128820649</v>
+        <v>127172852</v>
       </c>
       <c r="B47" t="n">
         <v>79327</v>
@@ -6288,26 +6275,22 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>362222</v>
+        <v>363214</v>
       </c>
       <c r="R47" t="n">
-        <v>6882658</v>
+        <v>6882814</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6331,22 +6314,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Garnlavsdraperade granar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6372,57 +6360,61 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128820649</t>
+          <t>https://artportalen.se/Sighting/127172852</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118118723</v>
+        <v>128820649</v>
       </c>
       <c r="B48" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>362344</v>
+        <v>362222</v>
       </c>
       <c r="R48" t="n">
-        <v>6882253</v>
+        <v>6882658</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6446,27 +6438,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Växer på stubbe av jättetall</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6475,19 +6462,8 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Barrnaturskog. Fjällnära</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6503,16 +6479,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118723</t>
+          <t>https://artportalen.se/Sighting/128820649</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121898927</v>
+        <v>136420049</v>
       </c>
       <c r="B49" t="n">
-        <v>83305</v>
+        <v>79460</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6520,21 +6496,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6544,13 +6520,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>363129</v>
+        <v>362971</v>
       </c>
       <c r="R49" t="n">
-        <v>6882975</v>
+        <v>6882793</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6574,22 +6550,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:07</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:07</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6604,70 +6575,62 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Erik Göthlin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo, Cecilia Öster</t>
+          <t>Erik Göthlin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121898927</t>
+          <t>https://artportalen.se/Sighting/136420049</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118103394</v>
+        <v>136420324</v>
       </c>
       <c r="B50" t="n">
-        <v>57953</v>
+        <v>79460</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>362272</v>
+        <v>362957</v>
       </c>
       <c r="R50" t="n">
-        <v>6882099</v>
+        <v>6882838</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6694,27 +6657,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Färska hacksmärken på gran Grannaturskog</t>
+          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6725,41 +6678,31 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Erik Göthlin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Erik Göthlin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118103394</t>
+          <t>https://artportalen.se/Sighting/136420324</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118103560</v>
+        <v>118118723</v>
       </c>
       <c r="B51" t="n">
-        <v>57953</v>
+        <v>79946</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6767,42 +6710,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>362276</v>
+        <v>362344</v>
       </c>
       <c r="R51" t="n">
-        <v>6882083</v>
+        <v>6882253</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6829,27 +6767,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i grannaturskog som är avverkningsanmäld.</t>
+          <t>Växer på stubbe av jättetall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6858,6 +6796,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6868,7 +6807,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Grannaturskog</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6885,62 +6824,54 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118103560</t>
+          <t>https://artportalen.se/Sighting/118118723</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118107736</v>
+        <v>121898927</v>
       </c>
       <c r="B52" t="n">
-        <v>57953</v>
+        <v>83305</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>362349</v>
+        <v>363129</v>
       </c>
       <c r="R52" t="n">
-        <v>6882279</v>
+        <v>6882975</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6964,27 +6895,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Färska hackmärken på gran i naturskog.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6995,38 +6921,28 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Barrnaturskog. Mycket gamla granar och tallar</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Andreas Öster, Maria Hindemo, Cecilia Öster</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118107736</t>
+          <t>https://artportalen.se/Sighting/121898927</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118113015</v>
+        <v>118103394</v>
       </c>
       <c r="B53" t="n">
         <v>57953</v>
@@ -7054,16 +6970,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -7073,10 +6985,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>362487</v>
+        <v>362272</v>
       </c>
       <c r="R53" t="n">
-        <v>6882179</v>
+        <v>6882099</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -7103,27 +7015,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Hackmärken på gran i myrholme.</t>
+          <t>Färska hacksmärken på gran Grannaturskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7134,6 +7046,16 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7149,13 +7071,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118113015</t>
+          <t>https://artportalen.se/Sighting/118103394</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118113051</v>
+        <v>118103560</v>
       </c>
       <c r="B54" t="n">
         <v>57953</v>
@@ -7183,32 +7105,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>362482</v>
+        <v>362276</v>
       </c>
       <c r="R54" t="n">
-        <v>6882180</v>
+        <v>6882083</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7232,27 +7150,27 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Hackmärken gran på myrholme. Naturskog</t>
+          <t>Färska hackmärken på gran i grannaturskog som är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7263,6 +7181,16 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7278,13 +7206,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118113051</t>
+          <t>https://artportalen.se/Sighting/118103560</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118118450</v>
+        <v>118107736</v>
       </c>
       <c r="B55" t="n">
         <v>57953</v>
@@ -7323,14 +7251,14 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>362489</v>
+        <v>362349</v>
       </c>
       <c r="R55" t="n">
-        <v>6882203</v>
+        <v>6882279</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7357,27 +7285,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Hackmärken på gran. Myrholme som är avverkningsanmäld</t>
+          <t>Färska hackmärken på gran i naturskog.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7396,7 +7324,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Lokalt fuktig miljö</t>
+          <t>Barrnaturskog. Mycket gamla granar och tallar</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7413,13 +7341,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118450</t>
+          <t>https://artportalen.se/Sighting/118107736</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118118466</v>
+        <v>118113015</v>
       </c>
       <c r="B56" t="n">
         <v>57953</v>
@@ -7447,12 +7375,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7462,10 +7394,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>362421</v>
+        <v>362487</v>
       </c>
       <c r="R56" t="n">
-        <v>6882227</v>
+        <v>6882179</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7497,7 +7429,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7507,12 +7439,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Färska hackmärken på fertalet grannar på denna myrholme.</t>
+          <t>Hackmärken på gran i myrholme.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7523,16 +7455,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>Barrnaturskog på myrholme</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7548,13 +7470,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118466</t>
+          <t>https://artportalen.se/Sighting/118113015</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118118547</v>
+        <v>118113051</v>
       </c>
       <c r="B57" t="n">
         <v>57953</v>
@@ -7582,7 +7504,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
@@ -7593,17 +7519,17 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>362378</v>
+        <v>362482</v>
       </c>
       <c r="R57" t="n">
-        <v>6882297</v>
+        <v>6882180</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7632,7 +7558,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7642,12 +7568,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Äldre hackmärken på gammal gran i barrnaturskog.</t>
+          <t>Hackmärken gran på myrholme. Naturskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7658,16 +7584,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7683,13 +7599,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118547</t>
+          <t>https://artportalen.se/Sighting/118113051</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118118562</v>
+        <v>118118450</v>
       </c>
       <c r="B58" t="n">
         <v>57953</v>
@@ -7728,14 +7644,14 @@
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>362373</v>
+        <v>362489</v>
       </c>
       <c r="R58" t="n">
-        <v>6882312</v>
+        <v>6882203</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7767,7 +7683,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7777,12 +7693,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Hackmärken på gammal gran i barrnaturskog. Skogen är avverkningsanmäld</t>
+          <t>Hackmärken på gran. Myrholme som är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7801,7 +7717,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog. Lokalt fuktig miljö</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7818,13 +7734,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118562</t>
+          <t>https://artportalen.se/Sighting/118118450</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118118603</v>
+        <v>118118466</v>
       </c>
       <c r="B59" t="n">
         <v>57953</v>
@@ -7867,10 +7783,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>362381</v>
+        <v>362421</v>
       </c>
       <c r="R59" t="n">
-        <v>6882250</v>
+        <v>6882227</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7902,7 +7818,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7912,12 +7828,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gammal gran i barrnaturskog som avverkningsanmäld.</t>
+          <t>Färska hackmärken på fertalet grannar på denna myrholme.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7936,7 +7852,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog på myrholme</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7953,13 +7869,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118603</t>
+          <t>https://artportalen.se/Sighting/118118466</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118118863</v>
+        <v>118118547</v>
       </c>
       <c r="B60" t="n">
         <v>57953</v>
@@ -7992,7 +7908,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -8002,10 +7918,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>362327</v>
+        <v>362378</v>
       </c>
       <c r="R60" t="n">
-        <v>6882265</v>
+        <v>6882297</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -8037,7 +7953,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8047,12 +7963,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i barrnaturskog som är avverkningsanmäld</t>
+          <t>Äldre hackmärken på gammal gran i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8071,7 +7987,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8088,13 +8004,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118863</t>
+          <t>https://artportalen.se/Sighting/118118547</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118118905</v>
+        <v>118118562</v>
       </c>
       <c r="B61" t="n">
         <v>57953</v>
@@ -8127,7 +8043,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -8137,10 +8053,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>362338</v>
+        <v>362373</v>
       </c>
       <c r="R61" t="n">
-        <v>6882298</v>
+        <v>6882312</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -8172,7 +8088,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8182,12 +8098,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Hackmärken på gran i barrnaturskog</t>
+          <t>Hackmärken på gammal gran i barrnaturskog. Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8223,13 +8139,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118905</t>
+          <t>https://artportalen.se/Sighting/118118562</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118119133</v>
+        <v>118118603</v>
       </c>
       <c r="B62" t="n">
         <v>57953</v>
@@ -8268,14 +8184,14 @@
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>362371</v>
+        <v>362381</v>
       </c>
       <c r="R62" t="n">
-        <v>6882362</v>
+        <v>6882250</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -8307,7 +8223,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8317,12 +8233,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färska hackmärken på grov gammal gran. i barrnaturskog som är hotad av avverkning.</t>
+          <t>Färska hackmärken på gammal gran i barrnaturskog som avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8358,13 +8274,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119133</t>
+          <t>https://artportalen.se/Sighting/118118603</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118119170</v>
+        <v>118118863</v>
       </c>
       <c r="B63" t="n">
         <v>57953</v>
@@ -8410,7 +8326,7 @@
         <v>362327</v>
       </c>
       <c r="R63" t="n">
-        <v>6882360</v>
+        <v>6882265</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -8442,7 +8358,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8452,12 +8368,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Färska hackmärken på grov gammal gran i barrnaturskog. Avverkningsanmäld skog.</t>
+          <t>Färska hackmärken på gran i barrnaturskog som är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8476,7 +8392,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Barrnatursk. Fjällnära</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8493,13 +8409,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119170</t>
+          <t>https://artportalen.se/Sighting/118118863</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118119483</v>
+        <v>118118905</v>
       </c>
       <c r="B64" t="n">
         <v>57953</v>
@@ -8532,7 +8448,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -8542,10 +8458,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>362284</v>
+        <v>362338</v>
       </c>
       <c r="R64" t="n">
-        <v>6882318</v>
+        <v>6882298</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8577,7 +8493,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8587,12 +8503,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i barrnaturskog.</t>
+          <t>Hackmärken på gran i barrnaturskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8628,13 +8544,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119483</t>
+          <t>https://artportalen.se/Sighting/118118905</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118119653</v>
+        <v>118119133</v>
       </c>
       <c r="B65" t="n">
         <v>57953</v>
@@ -8667,7 +8583,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -8677,10 +8593,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>362269</v>
+        <v>362371</v>
       </c>
       <c r="R65" t="n">
-        <v>6882324</v>
+        <v>6882362</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8712,7 +8628,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8722,12 +8638,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Hackmärken på grov gran intill skidspår som går genom barrnaturskogen. Avverkningsanmäld skog.</t>
+          <t>Färska hackmärken på grov gammal gran. i barrnaturskog som är hotad av avverkning.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8763,13 +8679,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119653</t>
+          <t>https://artportalen.se/Sighting/118119133</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118119701</v>
+        <v>118119170</v>
       </c>
       <c r="B66" t="n">
         <v>57953</v>
@@ -8812,10 +8728,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>362279</v>
+        <v>362327</v>
       </c>
       <c r="R66" t="n">
-        <v>6882363</v>
+        <v>6882360</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8847,7 +8763,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8857,12 +8773,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i barrnaturskog som hotas av avverkning</t>
+          <t>Färska hackmärken på grov gammal gran i barrnaturskog. Avverkningsanmäld skog.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8881,7 +8797,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnatursk. Fjällnära</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8898,13 +8814,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119701</t>
+          <t>https://artportalen.se/Sighting/118119170</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118119770</v>
+        <v>118119483</v>
       </c>
       <c r="B67" t="n">
         <v>57953</v>
@@ -8947,10 +8863,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>362240</v>
+        <v>362284</v>
       </c>
       <c r="R67" t="n">
-        <v>6882345</v>
+        <v>6882318</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8982,7 +8898,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8992,12 +8908,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gammal gran i barrnaturskog.</t>
+          <t>Färska hackmärken på gran i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9033,13 +8949,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119770</t>
+          <t>https://artportalen.se/Sighting/118119483</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118119872</v>
+        <v>118119653</v>
       </c>
       <c r="B68" t="n">
         <v>57953</v>
@@ -9082,10 +8998,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>362230</v>
+        <v>362269</v>
       </c>
       <c r="R68" t="n">
-        <v>6882332</v>
+        <v>6882324</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -9117,7 +9033,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9127,7 +9043,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Hackmärken på grov gran intill skidspår som går genom barrnaturskogen. Avverkningsanmäld skog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9163,13 +9084,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119872</t>
+          <t>https://artportalen.se/Sighting/118119653</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118120074</v>
+        <v>118119701</v>
       </c>
       <c r="B69" t="n">
         <v>57953</v>
@@ -9212,10 +9133,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>362243</v>
+        <v>362279</v>
       </c>
       <c r="R69" t="n">
-        <v>6882254</v>
+        <v>6882363</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -9247,7 +9168,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9257,12 +9178,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Färska och äldre hackmärken på gammal gran i barrnatuskog.</t>
+          <t>Färska hackmärken på gran i barrnaturskog som hotas av avverkning</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9298,13 +9219,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120074</t>
+          <t>https://artportalen.se/Sighting/118119701</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118120164</v>
+        <v>118119770</v>
       </c>
       <c r="B70" t="n">
         <v>57953</v>
@@ -9347,10 +9268,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>362252</v>
+        <v>362240</v>
       </c>
       <c r="R70" t="n">
-        <v>6882248</v>
+        <v>6882345</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9382,7 +9303,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9392,12 +9313,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran in barrnaturskog.</t>
+          <t>Färska hackmärken på gammal gran i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9433,13 +9354,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120164</t>
+          <t>https://artportalen.se/Sighting/118119770</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118120248</v>
+        <v>118119872</v>
       </c>
       <c r="B71" t="n">
         <v>57953</v>
@@ -9472,7 +9393,7 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -9482,10 +9403,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>362267</v>
+        <v>362230</v>
       </c>
       <c r="R71" t="n">
-        <v>6882224</v>
+        <v>6882332</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9517,7 +9438,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9527,12 +9448,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Färska hackmärken i ett granbestånd. I avverkningsanmält skogsområe</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9568,13 +9484,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120248</t>
+          <t>https://artportalen.se/Sighting/118119872</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118120388</v>
+        <v>118120074</v>
       </c>
       <c r="B72" t="n">
         <v>57953</v>
@@ -9607,7 +9523,7 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -9617,10 +9533,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>362196</v>
+        <v>362243</v>
       </c>
       <c r="R72" t="n">
-        <v>6882301</v>
+        <v>6882254</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9652,7 +9568,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9662,7 +9578,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken på gammal gran i barrnatuskog.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9681,7 +9602,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9698,13 +9619,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120388</t>
+          <t>https://artportalen.se/Sighting/118120074</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118120447</v>
+        <v>118120164</v>
       </c>
       <c r="B73" t="n">
         <v>57953</v>
@@ -9747,10 +9668,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>362200</v>
+        <v>362252</v>
       </c>
       <c r="R73" t="n">
-        <v>6882350</v>
+        <v>6882248</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9782,7 +9703,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9792,12 +9713,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Färska och äldre hackmärken på grov gran i barrnaturskog.</t>
+          <t>Färska hackmärken på gran in barrnaturskog.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9833,13 +9754,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120447</t>
+          <t>https://artportalen.se/Sighting/118120164</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118120506</v>
+        <v>118120248</v>
       </c>
       <c r="B74" t="n">
         <v>57953</v>
@@ -9872,7 +9793,7 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -9882,10 +9803,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>362168</v>
+        <v>362267</v>
       </c>
       <c r="R74" t="n">
-        <v>6882359</v>
+        <v>6882224</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9917,7 +9838,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9927,12 +9848,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Äldre hackmärken på gammal gran med garnlav. I avverkningsanmäld barrnaturskog</t>
+          <t>Färska hackmärken i ett granbestånd. I avverkningsanmält skogsområe</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9951,7 +9872,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>Barrnaturskog.</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9968,13 +9889,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120506</t>
+          <t>https://artportalen.se/Sighting/118120248</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118122341</v>
+        <v>118120388</v>
       </c>
       <c r="B75" t="n">
         <v>57953</v>
@@ -10007,20 +9928,20 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>362247</v>
+        <v>362196</v>
       </c>
       <c r="R75" t="n">
-        <v>6882178</v>
+        <v>6882301</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -10047,27 +9968,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Hackmärken på tall i barrnaturskog.</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10103,13 +10019,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122341</t>
+          <t>https://artportalen.se/Sighting/118120388</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118122435</v>
+        <v>118120447</v>
       </c>
       <c r="B76" t="n">
         <v>57953</v>
@@ -10148,14 +10064,14 @@
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>362276</v>
+        <v>362200</v>
       </c>
       <c r="R76" t="n">
-        <v>6882136</v>
+        <v>6882350</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -10182,27 +10098,27 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i barrnaturskog</t>
+          <t>Färska och äldre hackmärken på grov gran i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10221,7 +10137,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10238,13 +10154,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122435</t>
+          <t>https://artportalen.se/Sighting/118120447</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118122458</v>
+        <v>118120506</v>
       </c>
       <c r="B77" t="n">
         <v>57953</v>
@@ -10277,20 +10193,20 @@
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>362281</v>
+        <v>362168</v>
       </c>
       <c r="R77" t="n">
-        <v>6882135</v>
+        <v>6882359</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -10317,27 +10233,27 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i fin barrnaturskog som är avverkningsanmäld</t>
+          <t>Äldre hackmärken på gammal gran med garnlav. I avverkningsanmäld barrnaturskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10356,7 +10272,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Barrnaturskog.</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10373,13 +10289,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122458</t>
+          <t>https://artportalen.se/Sighting/118120506</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118122497</v>
+        <v>118122341</v>
       </c>
       <c r="B78" t="n">
         <v>57953</v>
@@ -10422,10 +10338,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>362283</v>
+        <v>362247</v>
       </c>
       <c r="R78" t="n">
-        <v>6882105</v>
+        <v>6882178</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -10457,7 +10373,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10467,12 +10383,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i avverkningsanmäld barrnaturskog</t>
+          <t>Hackmärken på tall i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10508,13 +10424,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122497</t>
+          <t>https://artportalen.se/Sighting/118122341</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118340481</v>
+        <v>118122435</v>
       </c>
       <c r="B79" t="n">
         <v>57953</v>
@@ -10557,10 +10473,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>362275</v>
+        <v>362276</v>
       </c>
       <c r="R79" t="n">
-        <v>6882133</v>
+        <v>6882136</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -10587,27 +10503,27 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i fjällnära skog.</t>
+          <t>Färska hackmärken på gran i barrnaturskog</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10626,7 +10542,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10643,13 +10559,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340481</t>
+          <t>https://artportalen.se/Sighting/118122435</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118340595</v>
+        <v>118122458</v>
       </c>
       <c r="B80" t="n">
         <v>57953</v>
@@ -10695,7 +10611,7 @@
         <v>362281</v>
       </c>
       <c r="R80" t="n">
-        <v>6882106</v>
+        <v>6882135</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10722,27 +10638,27 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>färska hackmärken på gatan. Fjällnära skog</t>
+          <t>Färska hackmärken på gran i fin barrnaturskog som är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10761,7 +10677,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10778,13 +10694,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340595</t>
+          <t>https://artportalen.se/Sighting/118122458</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118340691</v>
+        <v>118122497</v>
       </c>
       <c r="B81" t="n">
         <v>57953</v>
@@ -10827,13 +10743,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>362270</v>
+        <v>362283</v>
       </c>
       <c r="R81" t="n">
-        <v>6882100</v>
+        <v>6882105</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10857,27 +10773,27 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i fjällnära skog</t>
+          <t>Färska hackmärken på gran i avverkningsanmäld barrnaturskog</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10896,7 +10812,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10913,13 +10829,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340691</t>
+          <t>https://artportalen.se/Sighting/118122497</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118340748</v>
+        <v>118340481</v>
       </c>
       <c r="B82" t="n">
         <v>57953</v>
@@ -10962,10 +10878,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>362272</v>
+        <v>362275</v>
       </c>
       <c r="R82" t="n">
-        <v>6882086</v>
+        <v>6882133</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -11012,7 +10928,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>färska hackmnärken på gran i naturskog. Fjällnära</t>
+          <t>Färska hackmärken på gran i fjällnära skog.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11048,13 +10964,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340748</t>
+          <t>https://artportalen.se/Sighting/118340481</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118340920</v>
+        <v>118340595</v>
       </c>
       <c r="B83" t="n">
         <v>57953</v>
@@ -11093,14 +11009,14 @@
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>362284</v>
+        <v>362281</v>
       </c>
       <c r="R83" t="n">
-        <v>6882361</v>
+        <v>6882106</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -11147,7 +11063,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Färska och äldre hackmärken. Skogen är avverkningsanmäld. Gran med hackmärken inom anmälan. Se bild</t>
+          <t>färska hackmärken på gatan. Fjällnära skog</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11166,7 +11082,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11183,13 +11099,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340920</t>
+          <t>https://artportalen.se/Sighting/118340595</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121206319</v>
+        <v>118340691</v>
       </c>
       <c r="B84" t="n">
         <v>57953</v>
@@ -11218,16 +11134,24 @@
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>363246</v>
+        <v>362270</v>
       </c>
       <c r="R84" t="n">
-        <v>6883004</v>
+        <v>6882100</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11254,22 +11178,27 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på gran i fjällnära skog</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11280,28 +11209,38 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121206319</t>
+          <t>https://artportalen.se/Sighting/118340691</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127170971</v>
+        <v>118340748</v>
       </c>
       <c r="B85" t="n">
         <v>57953</v>
@@ -11329,32 +11268,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>363315</v>
+        <v>362272</v>
       </c>
       <c r="R85" t="n">
-        <v>6882898</v>
+        <v>6882086</v>
       </c>
       <c r="S85" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -11378,22 +11313,27 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>färska hackmnärken på gran i naturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11404,6 +11344,16 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -11419,13 +11369,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170971</t>
+          <t>https://artportalen.se/Sighting/118340748</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127172142</v>
+        <v>118340920</v>
       </c>
       <c r="B86" t="n">
         <v>57953</v>
@@ -11453,11 +11403,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
@@ -11468,17 +11414,17 @@
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>363196</v>
+        <v>362284</v>
       </c>
       <c r="R86" t="n">
-        <v>6882950</v>
+        <v>6882361</v>
       </c>
       <c r="S86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -11502,27 +11448,27 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Färska och äldre hackmärken.</t>
+          <t>Färska och äldre hackmärken. Skogen är avverkningsanmäld. Gran med hackmärken inom anmälan. Se bild</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11533,6 +11479,16 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>barrnaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -11548,13 +11504,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172142</t>
+          <t>https://artportalen.se/Sighting/118340920</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127172737</v>
+        <v>121206319</v>
       </c>
       <c r="B87" t="n">
         <v>57953</v>
@@ -11582,32 +11538,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>363143</v>
+        <v>363246</v>
       </c>
       <c r="R87" t="n">
-        <v>6882797</v>
+        <v>6883004</v>
       </c>
       <c r="S87" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11631,22 +11575,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11661,24 +11605,24 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172737</t>
+          <t>https://artportalen.se/Sighting/121206319</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127172795</v>
+        <v>127170971</v>
       </c>
       <c r="B88" t="n">
         <v>57953</v>
@@ -11715,7 +11659,7 @@
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
@@ -11725,13 +11669,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>363188</v>
+        <v>363315</v>
       </c>
       <c r="R88" t="n">
-        <v>6882809</v>
+        <v>6882898</v>
       </c>
       <c r="S88" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11760,7 +11704,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11770,12 +11714,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackmärken</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11801,13 +11740,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172795</t>
+          <t>https://artportalen.se/Sighting/127170971</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127172899</v>
+        <v>127172142</v>
       </c>
       <c r="B89" t="n">
         <v>57953</v>
@@ -11844,7 +11783,7 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -11854,13 +11793,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>363234</v>
+        <v>363196</v>
       </c>
       <c r="R89" t="n">
-        <v>6882800</v>
+        <v>6882950</v>
       </c>
       <c r="S89" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11889,7 +11828,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11899,7 +11838,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11925,13 +11869,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172899</t>
+          <t>https://artportalen.se/Sighting/127172142</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127315676</v>
+        <v>127172737</v>
       </c>
       <c r="B90" t="n">
         <v>57953</v>
@@ -11961,42 +11905,30 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>363122</v>
+        <v>363143</v>
       </c>
       <c r="R90" t="n">
-        <v>6882946</v>
+        <v>6882797</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -12020,22 +11952,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -12050,24 +11982,24 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127315676</t>
+          <t>https://artportalen.se/Sighting/127172737</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128822185</v>
+        <v>127172795</v>
       </c>
       <c r="B91" t="n">
         <v>57953</v>
@@ -12104,27 +12036,23 @@
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>362326</v>
+        <v>363188</v>
       </c>
       <c r="R91" t="n">
-        <v>6882768</v>
+        <v>6882809</v>
       </c>
       <c r="S91" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -12148,22 +12076,27 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12189,13 +12122,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128822185</t>
+          <t>https://artportalen.se/Sighting/127172795</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128822490</v>
+        <v>127172899</v>
       </c>
       <c r="B92" t="n">
         <v>57953</v>
@@ -12235,24 +12168,20 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>362260</v>
+        <v>363234</v>
       </c>
       <c r="R92" t="n">
-        <v>6882421</v>
+        <v>6882800</v>
       </c>
       <c r="S92" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -12276,22 +12205,22 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12317,13 +12246,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128822490</t>
+          <t>https://artportalen.se/Sighting/127172899</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128822499</v>
+        <v>127315676</v>
       </c>
       <c r="B93" t="n">
         <v>57953</v>
@@ -12353,30 +12282,42 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>362273</v>
+        <v>363122</v>
       </c>
       <c r="R93" t="n">
-        <v>6882421</v>
+        <v>6882946</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -12400,22 +12341,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12430,74 +12371,81 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Marcus Hansson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Marcus Hansson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128822499</t>
+          <t>https://artportalen.se/Sighting/127315676</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118122325</v>
+        <v>128822185</v>
       </c>
       <c r="B94" t="n">
-        <v>5179</v>
+        <v>57953</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>362234</v>
+        <v>362326</v>
       </c>
       <c r="R94" t="n">
-        <v>6882185</v>
+        <v>6882768</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12521,27 +12469,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>På torrgran vid myrknat intill barrnaturskog</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12550,19 +12493,8 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>Myrmark intill barrnaturskog</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -12578,16 +12510,16 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122325</t>
+          <t>https://artportalen.se/Sighting/128822185</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127315773</v>
+        <v>128822490</v>
       </c>
       <c r="B95" t="n">
-        <v>58057</v>
+        <v>57953</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12595,16 +12527,16 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -12614,17 +12546,14 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -12634,17 +12563,17 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>363120</v>
+        <v>362260</v>
       </c>
       <c r="R95" t="n">
-        <v>6882934</v>
+        <v>6882421</v>
       </c>
       <c r="S95" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12668,22 +12597,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12698,27 +12627,27 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127315773</t>
+          <t>https://artportalen.se/Sighting/128822490</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128820534</v>
+        <v>128822499</v>
       </c>
       <c r="B96" t="n">
-        <v>58057</v>
+        <v>57953</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12726,16 +12655,16 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -12752,7 +12681,7 @@
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -12762,13 +12691,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>362267</v>
+        <v>362273</v>
       </c>
       <c r="R96" t="n">
-        <v>6882595</v>
+        <v>6882421</v>
       </c>
       <c r="S96" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12797,7 +12726,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12807,7 +12736,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12833,16 +12762,16 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128820534</t>
+          <t>https://artportalen.se/Sighting/128822499</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118122289</v>
+        <v>118122325</v>
       </c>
       <c r="B97" t="n">
-        <v>99035</v>
+        <v>5179</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12850,27 +12779,32 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>219790</v>
+        <v>100526</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -12878,10 +12812,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>362232</v>
+        <v>362234</v>
       </c>
       <c r="R97" t="n">
-        <v>6882193</v>
+        <v>6882185</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -12926,6 +12860,11 @@
           <t>17:00</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>På torrgran vid myrknat intill barrnaturskog</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -12943,7 +12882,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>Barrnaturskog vid myrkant</t>
+          <t>Myrmark intill barrnaturskog</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -12960,58 +12899,73 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122289</t>
+          <t>https://artportalen.se/Sighting/118122325</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118118517</v>
+        <v>127315773</v>
       </c>
       <c r="B98" t="n">
-        <v>97983</v>
+        <v>58057</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221945</v>
+        <v>103031</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>362380</v>
+        <v>363120</v>
       </c>
       <c r="R98" t="n">
-        <v>6882294</v>
+        <v>6882934</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -13035,27 +12989,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Växer under gamla granar i barrnaturskog. Fuktig miljö.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13064,86 +13013,83 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Marcus Hansson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Marcus Hansson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118517</t>
+          <t>https://artportalen.se/Sighting/127315773</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118118821</v>
+        <v>128820534</v>
       </c>
       <c r="B99" t="n">
-        <v>97983</v>
+        <v>58057</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221945</v>
+        <v>103031</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>362339</v>
+        <v>362267</v>
       </c>
       <c r="R99" t="n">
-        <v>6882268</v>
+        <v>6882595</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -13167,27 +13113,22 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Växer på en stor yta under gamla granar i barrnaturskog</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13196,19 +13137,8 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>Barrnaturskog. Fjällnära</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -13224,16 +13154,16 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118821</t>
+          <t>https://artportalen.se/Sighting/128820534</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118119084</v>
+        <v>118122289</v>
       </c>
       <c r="B100" t="n">
-        <v>97983</v>
+        <v>99035</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13241,21 +13171,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -13269,10 +13199,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>362369</v>
+        <v>362232</v>
       </c>
       <c r="R100" t="n">
-        <v>6882345</v>
+        <v>6882193</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -13299,22 +13229,22 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13334,7 +13264,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>Grannaturskog. Fjällnära</t>
+          <t>Barrnaturskog vid myrkant</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -13351,13 +13281,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119084</t>
+          <t>https://artportalen.se/Sighting/118122289</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127171558</v>
+        <v>118118517</v>
       </c>
       <c r="B101" t="n">
         <v>97983</v>
@@ -13392,17 +13322,17 @@
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>363325</v>
+        <v>362380</v>
       </c>
       <c r="R101" t="n">
-        <v>6882909</v>
+        <v>6882294</v>
       </c>
       <c r="S101" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -13426,22 +13356,27 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Växer under gamla granar i barrnaturskog. Fuktig miljö.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13450,8 +13385,19 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -13467,13 +13413,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127171558</t>
+          <t>https://artportalen.se/Sighting/118118517</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127172203</v>
+        <v>118118821</v>
       </c>
       <c r="B102" t="n">
         <v>97983</v>
@@ -13508,17 +13454,17 @@
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>363195</v>
+        <v>362339</v>
       </c>
       <c r="R102" t="n">
-        <v>6882944</v>
+        <v>6882268</v>
       </c>
       <c r="S102" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -13542,22 +13488,27 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Växer på en stor yta under gamla granar i barrnaturskog</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13566,8 +13517,19 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -13583,13 +13545,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172203</t>
+          <t>https://artportalen.se/Sighting/118118821</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127172331</v>
+        <v>118119084</v>
       </c>
       <c r="B103" t="n">
         <v>97983</v>
@@ -13624,17 +13586,17 @@
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>363170</v>
+        <v>362369</v>
       </c>
       <c r="R103" t="n">
-        <v>6882973</v>
+        <v>6882345</v>
       </c>
       <c r="S103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13658,22 +13620,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13682,8 +13644,19 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>Grannaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -13699,13 +13672,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172331</t>
+          <t>https://artportalen.se/Sighting/118119084</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128820515</v>
+        <v>127171558</v>
       </c>
       <c r="B104" t="n">
         <v>97983</v>
@@ -13737,21 +13710,17 @@
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>362287</v>
+        <v>363325</v>
       </c>
       <c r="R104" t="n">
-        <v>6882523</v>
+        <v>6882909</v>
       </c>
       <c r="S104" t="n">
         <v>4</v>
@@ -13778,22 +13747,22 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13818,6 +13787,358 @@
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127171558</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>127172203</v>
+      </c>
+      <c r="B105" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Kerstibygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>363195</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6882944</v>
+      </c>
+      <c r="S105" t="n">
+        <v>4</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172203</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>127172331</v>
+      </c>
+      <c r="B106" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Kerstibygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>363170</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6882973</v>
+      </c>
+      <c r="S106" t="n">
+        <v>4</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172331</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>128820515</v>
+      </c>
+      <c r="B107" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Kokällmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>362287</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6882523</v>
+      </c>
+      <c r="S107" t="n">
+        <v>4</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128820515</t>
         </is>
@@ -13928,6 +14249,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -2202,7 +2202,7 @@
         <v>136420582</v>
       </c>
       <c r="B15" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>135621229</v>
       </c>
       <c r="B20" t="n">
-        <v>92440</v>
+        <v>92441</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -1866,7 +1866,7 @@
         <v>135621366</v>
       </c>
       <c r="B12" t="n">
-        <v>79539</v>
+        <v>79552</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>136420582</v>
       </c>
       <c r="B15" t="n">
-        <v>92102</v>
+        <v>92115</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>135621229</v>
       </c>
       <c r="B20" t="n">
-        <v>92441</v>
+        <v>92454</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>136420049</v>
       </c>
       <c r="B49" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>136420324</v>
       </c>
       <c r="B50" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -1866,7 +1866,7 @@
         <v>135621366</v>
       </c>
       <c r="B12" t="n">
-        <v>79552</v>
+        <v>79553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>136420582</v>
       </c>
       <c r="B15" t="n">
-        <v>92115</v>
+        <v>92116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>135621229</v>
       </c>
       <c r="B20" t="n">
-        <v>92454</v>
+        <v>92455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>136420049</v>
       </c>
       <c r="B49" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>136420324</v>
       </c>
       <c r="B50" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
